--- a/data/sheet-export/ff14-contents-template.xlsx
+++ b/data/sheet-export/ff14-contents-template.xlsx
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'contents'!$A$1:$F$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'phases'!$A$1:$E$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'phases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'videos'!$A$1:$E$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'mitigations'!$A$1:$E$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'strategies'!$A$1:$E$90</definedName>
@@ -1511,14 +1511,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1544,6 +1545,11 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>popular_strategy</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
@@ -1570,6 +1576,11 @@
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>新みんとっと / H3構成 / 拘束具逆▽ (3 つの拘束具を逆三角形配置)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">開幕フェーズ。
 主要ギミック: 拘束具 (Liquid Hell)、神鳥の魔印 (Magnetism)、Plummet、
@@ -1602,6 +1613,11 @@
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>新みんとっと / カータTLB (カータライズで タンクLB3 を発動)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引用詠唱 (Quote) に応じて配置を変える「コール戦」フェーズ。
 主要ギミック: サンダーストラック (青雷)、レイヴンダイブ (TB)、
@@ -1636,6 +1652,11 @@
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>新みんとっと / 進軍十字 / 連撃V字 / 群竜TLB</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">最長フェーズ。プライム / ネール / ツインタニアの 3 体が「三重奏 (Trio)」として
 同時にギミックを行う。Trio 構成 (野良主流呼称):
@@ -1673,7 +1694,8 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ツインタニアとネールの 2 体フェーズ (Trinity)。
 P1 と P2 のギミックが同時進行する短いフェーズ。
@@ -1707,6 +1729,11 @@
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ボス足元集合のスタック処理 + アク・モーン 無敵切替</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">最終フェーズ。Golden Bahamut Prime (金色のバハムート) が登場する DPS チェック。
 主要ギミック: メガフレア (リミットカット連続)、
@@ -1742,6 +1769,11 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
+          <t>ドーム処理(低気圧)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">開幕フェーズ。スリップストリーム、ミストラルソング、フェザーレイン、サーマルロウ、
 メソハイ、ウィキッドウィール、ウィキッドトルネード、低気圧(ドーム処理)など。
 所要時間 約2分43秒。
@@ -1773,6 +1805,11 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
+          <t>楔:逆Z</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">クリムゾンサイクロン、レイディアントプルーム、エラプション、炎獄の楔、灼熱の咆哮など。
 所要時間 約2分37秒。
 野良主流は「楔:逆Z」処理。①D1 ②D2 ③D3 ④D4 の順で楔を破壊。
@@ -1802,6 +1839,11 @@
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>ジェイル自滅式 (重み2回目で ST/メレー/レンジが被弾死)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ジオクラッシュ、ロックバスター、マウンテンバスター、大地の重み、ランドスライド、
 グラナイトジェイル、タムルトなど。タイタン討伐後、ヘイブンスインビョクスから
@@ -1836,6 +1878,11 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>十字無視法</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">アルテマウェポン本体フェーズの前半。誘導レーザー(吸着爆雷)、激震、
 フェザーレイン、ジェイル、十字範囲など。所要時間 約1分38秒。
 野良主流は「十字無視法」(十字範囲を安置判定で無視して位置取り)。
@@ -1866,6 +1913,11 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t>3111 (緑玉3-1-1-1配分)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">アルテマウェポン本体フェーズの中盤。緑玉(エメラルドレディアンス)、
 ノックバック、メソハイ、灼熱など。所要時間 約58秒。
 野良主流は「3111 (緑玉3-1-1-1配分)」処理。
@@ -1895,6 +1947,11 @@
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>乱撃TLB (タンクLB3顔面受け)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">アルテマウェポン本体フェーズの終盤。乱撃 (タンクLB3 ※顔面受け)、
 アルテマ詠唱、エーテル波動、紫玉(パープルレディアンス)、そして
@@ -1928,6 +1985,11 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>ヤークト無視 (20秒バースト) + サイコロ 1211</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">開幕フェーズ。リビングリキッド (本体) と頭手 (Liquid Hand / Hand of Prayer/Parting) を相手取る。
 主要ギミック: プロティアンウェイブ、ハンドオブペイン、ジャグドール、ドレナージ、
 圧壊 (Pressurize/Embolus)、スプラッシュ、スルース、サイコロ (Throttle - 1/2/3/4 番号デバフ)。
@@ -1959,6 +2021,11 @@
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>ヒラ先 (Healer-priority Nisi渡し) + サイコロ番号配置</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ジャスティス＋チェイサーの2体フェーズ。間に Limit Cut (アルファソード / スーパーブラスティチャージ /
 ホークブラスター) を挟む。
@@ -1993,6 +2060,11 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>ぬけまる/ハムカツ式 34固定 + 時間停止 脳死法</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">アレキサンダー・プライム単体の準ラスフェーズ。
 主要ギミック: チャステイニングヒート (Chastening Heat / TB)、ディヴァインスピア、
 メガホーリー、時間停止 (Temporal Stasis)、時空潜航のマーチ (Inception)、
@@ -2024,6 +2096,11 @@
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>ぬけまる式 + 未来観測 北/南頭割り</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">最終フェーズ。3体融合したパーフェクト・アレキサンダー。
 主要ギミック: 確定判決 (The Final Word)、運命の輪 (Ordained Motion / Stillness)、
@@ -2056,7 +2133,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ボス完結型。鎖と監獄の魔王によるギミック。
 主要ギミック:
@@ -2092,7 +2170,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ボス完結型。水の創造生物ヒッポカムポスによる頭割り＋ノックバック特化フェーズ。
 主要ギミック:
@@ -2129,7 +2208,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フェニックス前半フェーズ。鳥雑魚 + 闇の炎 + 突進 + 線取り。
 主要技:
@@ -2165,7 +2245,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">後半フェーズ。魔力錬成 (闇)、霊泉フェーズ、辺獄シリーズ。
 主要技:
@@ -2202,7 +2283,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 1 (前半)。ピナクス・毒線・緑玉ギミック中心。
 主要技:
@@ -2239,7 +2321,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 2 (後半)。序幕 → 第二幕 → 第三幕 → 第四幕 → 終幕 → カーテンコールの
 「劇」演出形式で進行。最終ギミック「カーテンコール」が時間切れ判定。
@@ -2278,6 +2361,11 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
+          <t>MTアデル / STグリノー / 線ST無敵 / 沈黙 MT→レンジ→MT</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">開幕フェーズ。蒼天騎士団3名（聖騎士アデルフェル / グリノー / シャリベル）と戦う。
 ハイパーディメンション、プレステ散開（◯×△□マーカー）、光翼閃、
 ホーリーブレードダンス（線処理）、ホリエストブレッシング（沈黙）など。
@@ -2309,6 +2397,11 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t>ゼフィラン基準散開 / 隕石ハムカツ式</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">雷槍、聖杖、隕石（ホーリーコメット）など。
 野良主流は「ゼフィラン基準散開 / 隕石ハムカツ式」。
 雷槍はスパイラルスラスト＋百雷、聖杖はゼフィラン基準でペア調整（MTST/H1H2/D1D2/D3D4）。
@@ -2340,6 +2433,11 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t>①②③ イル↓D・スパ↑B 固定 / 4塔近接調整</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">サイコロ（堕天のドラゴンダイブ）、4塔（ジオーガとゲイルスコグル）、
 ソウルテザー、アイ・オブ・タイラント、牙尾/尾牙の連旋などのギミック。
 野良主流は「①②③ イル↓D・スパ↑B 固定 / 4塔近接調整」。
@@ -2369,6 +2467,11 @@
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>近接青眼寄せ / ミラージュダイブ交代固定</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">邪竜の目（左眼 / 右眼）を破壊する短いフェーズ。
 赤線/青線の交換による眼への攻撃、ミラージュダイブ（複数回の円形範囲）など。
@@ -2402,6 +2505,11 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t>こまぞう式改</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">偽典トールダン戦。「至天の陣:風槍」と「至天の陣:死刻」の 2 大ギミック。
 死刻は絶竜詩最大の山場とも言われる複雑なギミックで、
 死の宣告デバフ + ツイスター + ヘヴィインパクトを直線移動で処理する。
@@ -2433,6 +2541,11 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t>おこめ式息吹1 / 脳死息吹2 / 南三角</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ニーズヘッグ（D側）とフレースヴェルグ（B側）の 2 体戦。
 聖竜/邪竜の息吹（線処理）、滅殺の誓い（DPS リレー）、
 アク・アファー（ヒラ起点頭割り）、邪念の炎、カータライズなどのギミック。
@@ -2464,6 +2577,11 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t>アクモーン2回目 TLB3</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">最終フェーズ。騎竜剣エクサフレア、トリニティ（オートアタック）、
 騎竜剣アク・モーン、騎竜剣ギガフレア、騎竜剣モーン・アファー（時間切れ攻撃）の連続。
 「エクサ→アクモーン→ギガフレア」のサイクルを 3 週繰り返して時間切れに到達する設計。
@@ -2493,7 +2611,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ライオン型「創造の継承者」プロトカーバンクル戦。1ボス完結型。
 主要ギミック:
@@ -2534,7 +2653,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">白蛇人型「半神の継承者」ヘーゲモネ戦。1ボス完結型。
 主要ギミック:
@@ -2574,7 +2694,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">巨大樹「半神の継承者」アグディスティス戦。1ボス完結型、アド管理が肝。
 主要ギミック:
@@ -2616,7 +2737,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 1 (前半)。ヘファイストス第1形態。創獣 (ケンタウロス/蛇) ギミックがメイン。
 主要技:
@@ -2656,7 +2778,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 2 (後半)。第2形態ヘファイストス。概念ギミック (High Concept) がメイン。
 最終的に「万象灰燼」(Ego Death) を生存するため、概念デバフ合成 (Immortal Conception)
@@ -2699,6 +2822,11 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">南集合・北11.5時から時計回り (H1MTSTD1D2D3D4H2) </t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">開幕フェーズ。ビートル形態のオメガ。
 主要ギミック: サークルプログラム (塔踏み・線とり・線捨て)、
 パントクラトル (ミサイル/頭割り)、波動砲 (T無敵 / 7方向散開)、
@@ -2731,6 +2859,11 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
+          <t>下から調整・男三人基準で左右組振り分け</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">男女形態フェーズ。
 主要ギミック: ファイアウォール、連携プログラム (PT / LB)、
 プレイステーション (ミドル/ファー)、4:4吹き飛ばし、
@@ -2763,6 +2896,11 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">優先TDH (検知式波動砲) / ファー→ニアー線渡し (ハロワ) </t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">強化版オメガ単体フェーズ。
 主要ギミック: コロッサスブロー、ハローワールド (Hello, World)、
 検知式波動砲 (Oversampled Wave Cannon)、Ion Efflux (時間切れ)。
@@ -2794,6 +2932,11 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
+          <t>下調整・D1D2人数調整</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ダメージを受けた状態のオメガ。
 主要ギミック: 波動砲 (3 iterations)、Wave Repeater、
 ブルースクリーン (DPSチェック付き時間切れ)。
@@ -2824,6 +2967,11 @@
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>デルタ：ハムカツ式 / シグマ：りょんめ式 (塔Wingwan) / オメガ：ぬけまる式</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">オメガM/オメガFの2体ディナミスフェーズ。
 コード「＊＊＊ミ＊」の3パターン (デルタ / シグマ / オメガ) を順次処理。
@@ -2856,7 +3004,8 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">最終フェーズ。Quickening Dynamis スタック3個必須。
 主要ギミック: コスモメモリー (タンクLB3)、フラッシュゲイル、
@@ -2888,7 +3037,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パンデモニウム戦。1ボス完結型。クモ・ウェブ系のギミックがメイン。
 主要技:
@@ -2926,7 +3076,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">テミス戦。1ボス完結型。光と闇の対比、魔法陣・戒律など秩序系ギミックがメイン。
 主要技:
@@ -2966,7 +3117,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 1 (前半)。「アテナ」戦。パラデイグマ系のギミックが軸。
 主要技:
@@ -3005,7 +3157,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 2 (後半)。「パラス・アテナ」戦。神格融合形態。
 Idol of Darkness 系・カロリック系・パンゲネシスが軸。
@@ -3047,7 +3200,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コキュートス戦。1ボス完結型 (フェーズ分けはしないが、内部的に「メイジ」「マーシャリスト」
 「キメラ」「ビースト」の魂を取り込んで姿を変える展開)。
@@ -3088,7 +3242,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ディスコ/ダンスモチーフの「パーティー野郎」ダンシング・グリーン戦。1ボス完結型。
 主要ギミック:
@@ -3129,7 +3284,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">シュガーライオット 前半。スプレーガンで描いたアートを具現化させる戦闘。
 主要技:
@@ -3166,7 +3322,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">雑魚フェーズ後の後半。山川 (山と川のフィールド) ギミック。
 主要技:
@@ -3201,7 +3358,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ブルートアボミネーター前半フェーズ。
 主要技:
@@ -3238,7 +3396,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">後半フェーズ。石化視線ギミックと2体ボス処理。
 主要技:
@@ -3273,7 +3432,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 1 (前半)。土と風のフェンリルを操る戦闘。
 主要技:
@@ -3312,7 +3472,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 2 (後半)。土と風のフェンリルの力を全て取り込み巨大化したハウリングブレード戦。
 主要技:
@@ -3348,7 +3509,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">レッドホット (赤、火属性) 単独フェーズ。
 主要技:
@@ -3383,7 +3545,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ディープブルー (青、水属性) 単独フェーズ。
 主要技:
@@ -3419,7 +3582,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">赤青2体同時相手にする合流フェーズ。
 主要技:
@@ -3455,7 +3619,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">開幕〜中盤フェーズ。
 主要技:
@@ -3495,7 +3660,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">後半フェーズ。チャンピオンズ・メテオから始まり、メテオスタンピード、
 最終的にハートブレイクキック (時間切れ) で終了。
@@ -3530,7 +3696,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 1 (前半)。細胞付着ギミックがメイン。
 主要技:
@@ -3566,7 +3733,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 2 (後半)。リンドブルム・メテオから始まり、フィールドが浮島×2に変化。
 4 色の塔 (赤/黄/紫/緑) ギミック → アルカディアンドリーム (3 分以上の大ギミック)
@@ -3605,7 +3773,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">コウモリモチーフの「魔性の処刑人」ヴァンプ・ファタール戦。1ボス完結型。
 主要ギミック:
@@ -3642,7 +3811,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">黒猫モチーフの「爪研ぐ猫魂」ブラックキャット戦。1ボス完結型。
 主要ギミック:
@@ -3683,7 +3853,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">「劇毒の愛」ハニーB・ラブリー戦。1ボス完結型。
 主要ギミック:
@@ -3724,7 +3895,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">「爆ぜる悪意」ブルートボンバー戦。1ボス完結型 (途中分身追加あり)。
 主要ギミック:
@@ -3762,7 +3934,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 1 (前半)。雷魔女モチーフのウィケッドサンダー前半フェーズ。
 主要技:
@@ -3800,7 +3973,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Part 2 (後半)。クロステイル・スペシャル (タンク LB3 推奨) からスタートし、
 ブラックサバト 3 連 (日没・夜半・日出) を経て剣の舞 (時間切れ) で終了。
@@ -3845,6 +4019,11 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
+          <t>優先HTD / STD4入替 / 塔キャス固定</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">開幕フェーズ。サイクロニックブレイク、楽園絶技、転輪召、シンソイルセヴァー、塔踏み（バーンストライク）など。
 野良主流は「優先HTD / STD4入替 / 塔キャス固定」。
 </t>
@@ -3873,6 +4052,11 @@
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>基本イディル / 暴走HT / ノクバマカ色＆バニシュガ2ペア変更</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ダイアモンドダスト、鏡の国、光の暴走など。
 Intermission として「Ice Veil (氷帝)」破壊フェーズが直後にある。
@@ -3904,6 +4088,11 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
+          <t>跡部王国改（ポネコニさん版）</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">究極幻想（時間圧縮・絶）、アポカリプス、頭割り、塔など。
 野良主流は「跡部王国改（ポネコニさん版）」での時間圧縮処理 + アポカリ「最初の安置基準」または「アポカリ基準」。
 </t>
@@ -3932,6 +4121,11 @@
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>扇前調整 / アクモーン1:7 / 赤爆走アムレンY字 / attack me マクロ</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ミトロンと闇の巫女の2体フェーズ。
 アークライ、光と闇の竜詩、アク・モーン、モーン・アファー、時間結晶など。
@@ -3962,7 +4156,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">最終フェーズ。光塵の剣（Fulgent Blade）、パラダイスリゲインド、星霊の剣など。
 野良主流はぬけまる式。アクモーンはボス基準で MT組左/ST組右。
@@ -3991,7 +4186,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ケフカ第1形態。詳細は未公開 (リリース 2026-06-02 予定)。
 # Source: 要追加調査
@@ -4000,7 +4196,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E71"/>
+  <autoFilter ref="A1:F71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/sheet-export/ff14-contents-template.xlsx
+++ b/data/sheet-export/ff14-contents-template.xlsx
@@ -18,11 +18,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="references" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'contents'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'contents'!$A$1:$M$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'phases'!$A$1:$F$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'videos'!$A$1:$E$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'mitigations'!$A$1:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'strategies'!$A$1:$E$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'strategies'!$A$1:$F$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'tips'!$A$1:$C$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'macros'!$A$1:$D$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'templates'!$A$1:$C$32</definedName>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -473,6 +473,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -506,6 +513,41 @@
           <t>references_primary</t>
         </is>
       </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>overview_main_strategy</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>overview_playlist_title</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>overview_playlist_url</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>overview_playlist_author</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>overview_macro_source</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>overview_macro_url</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>overview_macro_text</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -538,6 +580,13 @@
           <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
         </is>
       </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -570,6 +619,13 @@
           <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
         </is>
       </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -602,6 +658,13 @@
           <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
         </is>
       </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -634,6 +697,13 @@
           <t>Game8 (ゲームエイト) - 辺獄編零式1層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -666,6 +736,13 @@
           <t>Game8 (ゲームエイト) - 辺獄編零式2層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -698,6 +775,13 @@
           <t>Game8 (ゲームエイト) - 辺獄編零式3層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -730,6 +814,13 @@
           <t>Game8 (ゲームエイト) - 辺獄編零式4層前半/後半 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -762,6 +853,13 @@
           <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
         </is>
       </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -794,6 +892,13 @@
           <t>Game8 (ゲームエイト) - 煉獄編零式1層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -826,6 +931,13 @@
           <t>Game8 (ゲームエイト) - 煉獄編零式2層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -858,6 +970,13 @@
           <t>Game8 (ゲームエイト) - 煉獄編零式3層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -890,6 +1009,13 @@
           <t>Game8 (ゲームエイト) - 煉獄編零式4層前半/後半 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -922,6 +1048,13 @@
           <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
         </is>
       </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -954,6 +1087,13 @@
           <t>Game8 (ゲームエイト) - 天獄編零式2層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -986,6 +1126,13 @@
           <t>Game8 (ゲームエイト) - 天獄編零式3層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1018,6 +1165,13 @@
           <t>Game8 (ゲームエイト) - 天獄編零式4層前半/後半 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1050,6 +1204,13 @@
           <t>Game8 (ゲームエイト) - 天獄編零式1層 攻略丨マクロ Ver1.1</t>
         </is>
       </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1082,6 +1243,13 @@
           <t>Game8 (ゲームエイト) - クルーザー級零式1層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1114,6 +1282,13 @@
           <t>Game8 (ゲームエイト) - クルーザー級零式2層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1146,6 +1321,13 @@
           <t>Game8 (ゲームエイト) - クルーザー級零式3層 攻略丨マクロ (さり式)</t>
         </is>
       </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1178,6 +1360,13 @@
           <t>Game8 (ゲームエイト) - クルーザー級零式4層前半/後半 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1210,6 +1399,13 @@
           <t>Game8 (ゲームエイト) - ヘビー級零式2層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1242,6 +1438,13 @@
           <t>Game8 (ゲームエイト) - ヘビー級零式3層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1274,6 +1477,13 @@
           <t>Game8 (ゲームエイト) - ヘビー級零式4層前半/後半 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1306,6 +1516,13 @@
           <t>Game8 (ゲームエイト) - ヘビー級零式1層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1338,6 +1555,13 @@
           <t>Game8 (ゲームエイト) - アルカディア零式1層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1370,6 +1594,13 @@
           <t>Game8 (ゲームエイト) - アルカディア零式2層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1402,6 +1633,13 @@
           <t>Game8 (ゲームエイト) - アルカディア零式3層 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1434,6 +1672,13 @@
           <t>Game8 (ゲームエイト) - アルカディア零式4層前半/後半 攻略丨マクロ</t>
         </is>
       </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1466,6 +1711,13 @@
           <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
         </is>
       </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1498,9 +1750,16 @@
           <t>Consolegameswiki</t>
         </is>
       </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F32"/>
+  <autoFilter ref="A1:M32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8195,14 +8454,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -8228,6 +8488,11 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>popular</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
@@ -8254,6 +8519,11 @@
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-09 にりりーどーる Lodestone マクロが「みんとっと → 新みんとっと」へ
 切替わったタイミングで野良主流が刷新された。
@@ -8285,6 +8555,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">実装初期からの「みんとっと」(タンク 3) 構成。
 現在も一部固定で採用される代替流派。
 # 出典: https://na.finalfantasyxiv.com/lodestone/character/18500174/blog/4804267/
@@ -8315,6 +8590,11 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">カータライズ (Cauterize / 直線ダイブ) のタイミングで タンク LB3 を発動し
 パーティ全体のダメージを軽減する野良主流処理。
 </t>
@@ -8344,6 +8624,11 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">進軍の三重奏 (Quickmarch Trio) の野良主流処理。
 十字状の配置でアースシェイカー / メテオストリーム / Dive を捌く。
 </t>
@@ -8372,6 +8657,11 @@
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">連撃の三重奏 (Tenstrike Trio) の野良主流処理。
 魔力錬成 (Generate) 対象 3 名を V 字に配置して拘束具誘導 + 散開を両立。
@@ -8402,6 +8692,11 @@
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">群竜の八重奏 (Grand Octet) の最終ギミック。
 メガフレアダイブのタイミングでタンク LB3 を発動し、頭割りマーカーを無視できる
@@ -8434,6 +8729,11 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">モーン・アファーはボス足元集合で全員均等に受ける。
 アク・モーンは MT/ST 無敵切替で対応。
 エクサフレアの安置 (8 方向ランダム) は床マーカーをパーティで分担コールする。
@@ -8464,6 +8764,11 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">低気圧 (サーマルロウ/メソハイ) の被弾優先度を「ST &gt; ST/H1/H2/D3/D4 &gt; D1 &gt; D2」で
 回す野良主流処理法。初動 ST 受けで誘導距離を最小化する。
 </t>
@@ -8493,6 +8798,11 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">メソハイ線取りを D 側に D4、B 側に MT (キャスター MT 想定) で取る流派。
 みんとっと動画準拠で野良主流。
 </t>
@@ -8521,6 +8831,11 @@
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">炎獄の楔を逆 Z 字配置で①〜④の順に破壊する流派。
 ①D1 / ②D2 / ③D3 / ④D4 が担当。
@@ -8551,6 +8866,11 @@
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">重み 2 回目で ST/D1/D2/D3 が自滅して人数を減らし、
 3 連ジェイル + 4 連ジェイルを処理する野良主流。
@@ -8584,6 +8904,11 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">十字範囲攻撃を安置判定で無視して位置取りを最適化する流派。
 フェザーレイン回避方向は ★ -&gt; A -&gt; D。
 ジェイル破壊はフェザーレイン回避時にターゲット可能。
@@ -8614,6 +8939,11 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">緑玉(エメラルドレディアンス)を 3-1-1-1 で配分する野良主流。
 1 回目は MT/ST/D1 / 2-4 回目は MT が処理。
 爆撃 P メソハイは 1 回目 D3 / 2 回目 灼熱ヒラ。
@@ -8644,6 +8974,11 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">乱撃を ST のタンク LB3 (顔面受け) で処理する野良主流。
 D マーカー誘導 -&gt; 外周避け + ST メソハイ -&gt; D 集合。
 MT がアルテマ詠唱 LB3、ST がエーテル波動 LB1 を担当。
@@ -8673,6 +9008,11 @@
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">最終三蛮神はガルーダ/イフリート/タイタンのスタートがランダム。
 ①ガルーダスタート (イフ→タコ)
@@ -8706,6 +9046,11 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">リキッドフェーズ 2分20秒の時間切れを 1分9秒以内に本体だけ全力で殴り切る手法。
 HP均等化を行わず、ペイン大ダメージを軽減とバリアで耐える。
 ふうcだよが図解＋解説動画でまとめている派生も含む。野良の現在主流。
@@ -8736,6 +9081,11 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">サイコロ (Throttle) 1番→2番→1番→1番 の順で爆発位置を踏み替えていく処理。
 東西スタートの場合は東側優先。1211式 = 最初の爆発中心を通る線を0本目として、
 1本先 / その2本先 / さらに1本先 / さらに1本先で処理する命名。
@@ -8766,6 +9116,11 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ぬけまる「リキッドセパレ式」動画で解説される 4:4 分割の派生処理。
 1211 より遭遇率は低いが固定で採用するケースあり。
 </t>
@@ -8794,6 +9149,11 @@
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ナイサイ (Judgment Nisi) 受け渡しを「ヒラが先に渡してから DPS が処理」する流派。
 1回目DPS反時計受け渡し、3回目は一列 (A｝MT・D1・D3・D4・D2・ST｛C)、
@@ -8825,6 +9185,11 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">スーパージャンプ誘導を D3 が担当する標準処理。地雷は D3:5時 / ST:6時 配置。
 </t>
         </is>
@@ -8852,6 +9217,11 @@
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">時間停止 (Temporal Stasis) を「無印→左側ロボ、緑線→右側ロボ、青線TH左/青線D右、
 雷→ジャスの側面」で機械的に処理する脳死法。
@@ -8883,6 +9253,11 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">次元断絶のマーチを「ハムカツさん34固定方式」で処理する流派。
 ぬけまる「ハムカツさん34固定方式 各視点有」動画で詳細解説。
 懴悔順は 5,6 → 7,8 → 1,2。
@@ -8913,6 +9288,11 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">未来観測 α/β を「黄親→北頭割り / 紫親→南頭割り」で処理する流派。
 α: ボス側安置=名誉罰 / 対面側安置=左集団罰+他, 右加重罰。
 β: 接触保護(黄親)→北寄り北西, 接触禁止(黄子)→2左上, 等の細かい配置あり。
@@ -8943,6 +9323,11 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">確定判決を「黄親→4 / 紫親→2 / 他6人→2左側」で処理。
 頭割り TH北/DPS南、散開は MT ST / H1 H2 / D3 D1 D2 D4 配置。
 </t>
@@ -8971,6 +9356,11 @@
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 が公式採用している野良主流処理法。
 - 結呪調整ペア: MTD4 / H2D2 / STD1 / H1D3 (マーカー色基準)
@@ -9005,6 +9395,11 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 が公式採用している野良主流処理法。
 - ショックウェーブ: MT 組 (MT/H1/D1/D2) ボス下 / ST 組 (ST/H2/D3/D4) 通路
 - チャネリングフロウ: 十字配置で TH/DPS 互い違い
@@ -9037,6 +9432,11 @@
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 採用流派。複数の野良流派を融合した形。
 - 4:4 分け: MT 組 (MTH1D1D3) / ST 組 (STH2D2D4)
@@ -9074,6 +9474,11 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 採用流派。
 - 基本散開: 標準 8 人配置
 - 毒線 YPP 式: TH 北 / DPS 南、塔線時計回り (線ぐるぐる)
@@ -9108,6 +9513,11 @@
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 採用流派。第三幕アースシェイカー誘導に「犬丸式」を採用。
 - 序幕: 標準散開 (D3/D4 北、MT/ST 中段、D1/D2 / H1/H2 南)
@@ -9145,6 +9555,11 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 ページ上で犬丸式と並列掲載されている別流派。
 主に第三幕の処理が異なる。詳細はぬけまる動画参照。
 </t>
@@ -9173,6 +9588,11 @@
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">りりーどーる版野良主流。
 - MTアデルフェル / STグリノー固定
@@ -9206,6 +9626,11 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">りりーどーる版野良主流。
 - 雷槍: MT組 D-1 / ST組 B-3 で扇配置
 - 聖杖: ゼフィラン基準でペア (MTST/H1H2/D1D2/D3D4) を組み、剣1+MT組はゼフィラン対角、剣2+ST組はゼフィラン後ろ
@@ -9236,6 +9661,11 @@
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">サイコロ番号と塔配置を固定する野良主流。
 - イルーシブジャンプ↓: D ライン担当
@@ -9269,6 +9699,11 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ぬけまる動画準拠の処理法。サイコロ全パターンの視点動画あり。
 固定の流派として選ばれることもある。
 </t>
@@ -9297,6 +9732,11 @@
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">近接ジョブが青眼に寄って効率的にダメージを与える野良主流。
 - 黄玉: DPS / 青玉: TH 担当
@@ -9330,6 +9770,11 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">現在もっとも採用されている主流処理法。
 イディル式とこまぞう式のハイブリッドで、基本動作はこまぞう式、
 散開座標はイディル式を採用。
@@ -9362,6 +9807,11 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">オリジナル「こまぞう式」。W3rd クリアチームの流派。
 散開優先度は D4MTSTD1D2D3H1H2 系統。
 </t>
@@ -9391,6 +9841,11 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">旧主流処理法。現在は「こまぞう式改」に取って代わられているが
 固定によっては依然採用されることもある。
 </t>
@@ -9419,6 +9874,11 @@
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">野良主流の二天竜処理。
 - ニーズ担当: MT H1 D1 D3 / フレース担当: ST H2 D2 D4
@@ -9455,6 +9915,11 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">野良主流の最終フェーズ処理。
 - アクモーン2回目で タンク LB3 を発動
 - エクサ→アクモーン→ギガフレア の 3 周構成（3 周目はギガフレアなし）
@@ -9486,6 +9951,11 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ARUTORA 推奨のエクサフレア処理法。
 ボスを北または南に向けた状態で、最初の爆発後に中心に移動、
 その後ひし形の床模様の頂点へ移動する縦避け方式。
@@ -9515,6 +9985,11 @@
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 が採用しているぬけまる氏解説に準拠した処理法 (マクロVer2)。
 - 基本散開: 北 D3/MT/D4、中央 H1/H2、南 D1/ST/D2
@@ -9549,6 +10024,11 @@
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 が採用しているぬけまる氏解説に準拠した処理法 (マクロVer1)。
 - MT組: MTH1D1D3 / ST組: STH2D2D4
@@ -9586,6 +10066,11 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 が採用しているぬけまる氏解説に準拠した処理法 (マクロVer1.5)。
 - MT組: MTH1D1D3 / ST組: STH2D2D4
 - 基本散開: 北 MT/D1, ST/D2 / 南 H1/D3, H2/D4 / 中央 ★
@@ -9622,6 +10107,11 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 が採用しているぬけまる氏解説 + 野良標準「FFO式」処理法 (マクロVer1)。
 - 基本散開: 北 D3 MT D4 / 中 H1(H2) ST / 南 D1 H2 D2
 - テトラオクタ/誘導/蛇2: MT/D3 → ST/D4 / H1/D1 ← H2/D2 の4方向誘導
@@ -9657,6 +10147,11 @@
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 が採用しているぬけまる氏解説 + ビジョン式「万象灰燼処理法」(マクロVer1)。
 - 術式1回目: 頭割りは西、紫 ST、★中央 / D1 MT D2 / H1 H2 / D3 ST D4
@@ -9699,6 +10194,11 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">サークルプログラムは南集合、北11.5時を基準に時計回りで
 H1MTSTD1D2D3D4H2 の順で塔踏み・線処理。
 パンクラは北(東)→南(西)へ H1MTSTD1D2D3D4H2 で並ぶ。
@@ -9730,6 +10230,11 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">連携プログラムPTは全て下から調整。
 4:4 吹き飛ばしは男三人を基準に西を左組、南or東を右組として
 右組が調整役を担当。
@@ -9761,6 +10266,11 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">P3 検知式波動砲の野良主流処理。
 優先順位は ①❶＞MTSTD1234H12＞❸⑤ で組分け、AC縦列はボスモニター無い方へ。
 </t>
@@ -9790,6 +10300,11 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">十字状の配置で安置を作る代替流派。ぬけまる「P3 検知式波動砲 十字式イメトレ」動画で解説。
 </t>
         </is>
@@ -9817,6 +10332,11 @@
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">塔組外側・線組内側ルートで移動。
 塔は早い者勝ち、線受け渡しは貰いに行く、
@@ -9848,6 +10368,11 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">MT/ST 上、D3/D4 左右、H1/H2 中段、D1/D2 下段、
 頭割りは下調整、人数調整は D1D2 が担当。
 </t>
@@ -9876,6 +10401,11 @@
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">P5 デルタの主流処理。ロケパンは内側調整、❶❷ニア / ①②ファー。
 線切りタイミング、アーム/バッシュ誘導、ハロワ散開も含む。
@@ -9907,6 +10437,11 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">P5 シグマの塔踏み処理は「りょんめ式 (塔Wingwan)」が野良主流。
 # 出典: 要調査 (Hanabi note より名称のみ抽出 / 詳細マクロは要手動補完)
 </t>
@@ -9935,6 +10470,11 @@
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">P5 オメガの野良主流処理。ボス検知＆虫オメガ北基準で配置。
 マーカー付与の優先順位：1回目 II+ディナミス2&gt;ディナミス2&gt;ディナミス1、
@@ -9966,6 +10506,11 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">P6 コスモアロー波動砲処理。
 Hanabi note (note.com/hana25o) で「安定する」と評される野良主流。
 </t>
@@ -9995,6 +10540,11 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ぬけまる P6 解説動画準拠の処理。コスモダイブ・波動砲・コスモメテオ・
 マジックナンバーを含む最終フェーズ全般の流派。
 </t>
@@ -10023,6 +10573,11 @@
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 が採用している犬丸様の攻略動画ベースの処理法。
 - 尖脚: 左 MT / 右 ST
@@ -10063,6 +10618,11 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">魔殿の震撃ボンドの処理法だけ別解として記載されているもの。
 - ダブル(22) MT組:ST組: D1 MT ST D2 / D3 H1 H2 D4
 - クアドラ(44) TH組:DPS組: MT ST D1 D2 / H1 H2 D3 D4
@@ -10092,6 +10652,11 @@
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 採用流派。基本散開・配置はハムカツ様準拠。光と闇の調停はジジー式。
 - ボスを見る場合以外は北 (A) 基準で散開
@@ -10136,6 +10701,11 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">アップヘルド闇の処理で十字 (ハムカツ式) ではなく X字を採用する流派。
 Game8 ページに「別解」として注記あり。詳細は動画予習推奨。
 </t>
@@ -10164,6 +10734,11 @@
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 採用流派。「パラ1無敵 / パラ2十字 / パラ3イディル / サイコロネバラン」。
 - パラデイグマ 1回目: タンク無敵で処理
@@ -10208,6 +10783,11 @@
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 採用流派。パラスレイは X処理メイン (1回目は K処理することも多い)。
 - パラスの手: T:西 / 他:東
@@ -10256,6 +10836,11 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">パラスレイの 1回目を K処理で行うバリアント。Game8 マクロは X処理だが
 「1回目は K処理することも多い」と注記あり。PT 募集時に必ず流派確認すること。
 詳細処理は ぬけまる別解動画 / Lodestone 等で要確認。
@@ -10285,6 +10870,11 @@
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 が採用しているぬけまる動画ベースの処理法。「無職マラソン式」
 (jobless marathon) と呼ばれる。
@@ -10326,6 +10916,11 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説に準拠した処理法。
 - ジングル予約 A/B: ジングルがランダムに A or B を詠唱するが、固定流派では
   散開を一貫させるため位置固定で処理。
@@ -10359,6 +10954,11 @@
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Yuna'' Kanon' (FFO) 氏が公開した新FFO式マクロを Game8 が採用。
 - 基本散開: ねばねば北基準、Tボス下。
@@ -10397,6 +10997,11 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">さり氏 (Asche Okumura, note.com/srm_br) が考案、Game8 採用流派。
 - いしあ式よりも後出しGCDを多く回せる処理法 (火力寄り)。
 - 移動がシビアで P3 ストーンウェポンでスプリント必須。
@@ -10429,6 +11034,11 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 が代替として掲載しているもうひとつの処理法。
 ソーンデスマッチ・ビルディングを別アプローチで処理する。詳細は Game8 ページ参照。
 # Source: https://game8.jp/ff14/681274
@@ -10458,6 +11068,11 @@
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ぬけまる様 + イディルシャイア居住区様の土修正版を融合した流派。
 - 土の魔技: MTD4 / D3 / H1 / D1ST / H2 / D2 の配置。
@@ -10495,6 +11110,11 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 採用流派。
 - 風震の魔印: 正規処理 (頭割りは風撃タンク隣島)。
 - 双牙撃: 西島=MT / 東島=ST。
@@ -10530,6 +11150,11 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">犬丸様の攻略をベースに、家無しララ様の野良準拠解法を融合した処理法。
 - 水牢: ヒーラー入り
 - 炎: AC (近接) 担当
@@ -10560,6 +11185,11 @@
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 採用流派。
 - 基本: ルクレ (基本散開)
@@ -10594,6 +11224,11 @@
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ぬけまる様 + イディル様の解説をベースにした処理法。
 - リーサルスカージ: D側 MT組 / B側 ST組
@@ -10630,6 +11265,11 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 が採用しているハイブリッド流派。
 - レプリケーション: 位置固定式
 - 模倣細胞: 牛子式
@@ -10661,6 +11301,11 @@
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sr Odin 氏が公開した「ヘビー級零式4層後半 アルカディアンドリーム用 ぬけまる改良版」。
 ぬけまる動画 (修正版) で追加された
@@ -10697,6 +11342,11 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説に準拠した処理法。
 - ヴァンプストンプ: 近接 (D1/D2) はコウモリ1の背後に寄り、TH+遠は前散開。
 - エーテルレッティング: 最外周扇範囲を捨てて中央集合。
@@ -10730,6 +11380,11 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 が公式採用している犬丸氏解説に準拠した処理法。
 - クアドラプルネイル: 十字固定 (先 TH / 後 DPS)
 - レイニングキャッツ: タンク無敵で 2 連処理
@@ -10761,6 +11416,11 @@
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説に準拠した処理法。
 - 基本散開: D3 MT D4 / H1 ☆ H2 / D1 ST D2
@@ -10795,6 +11455,11 @@
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説の改訂版 (Ver.2.0)。
 - 基本散開: D3 MT D4 / H1 ★ H2 / D1 ST D2
@@ -10831,6 +11496,11 @@
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Game8 が公式採用しているぬけまる氏動画 (最終改定版) + DN 式円輪/輪円処理法。
 - 縦散開: D3 D4 / MT ST / D1 D2 / H1 H2
@@ -10871,6 +11541,11 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説に準拠した処理法。
 - クロステイル・スペシャル: タンク LB3 で凌ぐ
 - ウィケッドブレイズ: 西 MT 組 / 東 ST 組
@@ -10908,6 +11583,11 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
           <t>野良主流。STとD4が入替、塔をキャスター固定で処理する流派。</t>
         </is>
       </c>
@@ -10934,6 +11614,11 @@
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">りりーどーるの「基本イディル」処理法。
 DD（ダイアモンドダスト）は基本散開から時計回り調整、
@@ -10965,6 +11650,11 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ポネコニさんが派生させた跡部王国改版。
 P3野良主流の時間圧縮処理。X投稿 (PoneKoni) に詳細図あり。
 </t>
@@ -10994,6 +11684,11 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">TH 赤紫マーカー / DPS 黄青マーカーで、最初の安置を基準にアポカリ処理。
 固定での採用が主流。遠隔組の移動距離が少ない。
 </t>
@@ -11023,6 +11718,11 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">アポカリの出現位置を見て安置を決定する流派。
 ぬけまる動画 (P3-2) で詳細解説。
 </t>
@@ -11051,6 +11751,11 @@
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">P4-P5 野良主流。
 - 扇前調整: ウォタガ扇前調整
@@ -11084,13 +11789,18 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">P5 野良主流。光塵の剣、アクモーン、パラダイスリゲインド、星霊の剣をぬけまる解説動画準拠で処理。
 </t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E90"/>
+  <autoFilter ref="A1:F90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/sheet-export/ff14-contents-template.xlsx
+++ b/data/sheet-export/ff14-contents-template.xlsx
@@ -15,8 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="strategies" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="macros" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="templates" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="references" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tips" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -598,22 +597,10 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>references</t>
+          <t>tips</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>🔗 (deprecated) 参照 URL — 新 content は overview_guide_url を使う</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>tips</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>💡 攻略 tips (近日削除予定 — PR #82)</t>
         </is>
@@ -690,3357 +677,6 @@
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t>📚 詳しい使い方: docs/content-sheet-edit-guide.md</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C196"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>content_id</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>phase_id</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>tip</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Twister の捨て位置は近接組がボスクリーブ内に置くと安定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>拘束具 (Liquid Hell) は▽逆三角に置いて第7霊災のハッチ位置を見やすくする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Death Sentence (タンクバスター) は MT 側 CD or ST スイッチで受ける。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>コール (引用詠唱) のパターンを覚えるのが攻略のメイン。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>サンダーストラック (青雷) 付与者は声で大きくコールする慣習。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>ダイブマーカーは雷ターゲットを参考に配置を判断する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>三重奏は全て『プライム + ネール + ツインタニアの 3 体が同時にギミックを実行する』構造。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Trio 順: 進軍 → 黒炎 → 災厄 → 天地 → 連撃 → 八重奏 (Grand Octet) の 6 段階。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>八重奏のマラソン方向はプライム/ネール出現位置で時計/反時計を判断する (要事前合意)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>群竜のメガフレアダイブで TLB3 を打つので、ST タンク無敵タイミングと衝突しないこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>2 体の HP は同期して削るのが鉄則 (片方を先に倒すと残った方が enrage)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>P1 / P2 のギミックを混合処理するため、配置・コールはパーティ事前合意必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>常時移動が必要 (Twister 回避)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>エクサフレアの安置察知が最大の難所。フェニックスの加護 (リレイズ) を失わないよう優先処理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>モーン・アファーはボス足元スタック (8人分散)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>アク・モーン は連続 3〜6 回、MT/ST 無敵 (リビデ/インビン) を交互に使用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>ヒーラー軽減はパーティ全体攻撃に合わせて使用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>覚醒バフは BH &gt; D4 &gt; D1 の順で取得。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>ミストラルソングは MT B&gt;A&gt;C / ST D&gt;C&gt;A の順で誘導。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>インシネレートは 1 回目 ST 無敵 / 2 回目 MT 無敵 (ナイト MT なら 1 回目無敵)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>楔配置: 上段に ③ ④、下段に D3 ① ② D4 (逆 Z 字)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>エラプ誘導は D3D4 が担当した後に楔処理へ移行。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>ジェイル位置: ボス D4 / H1 / H2。ランスラ斜め誘導。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>マウンテンバスター 1回目&amp;3回目は MT バフ / 2回目は ST バフ(orかばう)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>アルテマ履行 LB 使用順: D4 -&gt; H2 -&gt; D1 -&gt; MT。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>吸着爆雷(ヘイト1位)は MT 無敵 -&gt; 激震後半で ST 挑発。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>誘導レーザー(ヘイト2位)は追撃中は MT 無敵 / 爆撃中は ST 無敵。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>緑玉 1 回目は MT/ST/D1 の 3 人で処理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>灼熱はヒラがメソハイ線取り (2 回目)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>乱撃顔面受けは ST が LB3。ヒラは堅実魔で詠唱中断回避。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>紫玉散開: MT AB間-&gt;AD間 / ST BC間 / その他 CD間。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>最終三蛮神の移動ルートはパターン分岐。事前にホットバーカンペ準備推奨。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>ヤークト無視はペインのダメージ大かつブレが大きいので、軽減を絶対切らさない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>可視扇 (プロティアン) は D3 が誘導、不可視扇は D4 担当が標準。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>サイコロ 1211 は中央ピザ (フィールド8等分) を踏み替えていくため自分の番号位置を即座に判断。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>サイコロ番号順に散開 (西H1 → 西D3D4D2D1東) で雷散開を綺麗に作る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>ヒラ先渡しは1回目 DPS が反時計で受け渡す手順を体に覚えさせる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Limit Cut (P1とP2の間) は数字順にスタンを撃ち抜くシンプル処理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>時空潜航のマーチ: ラピス 1→①, 2→②, 3→③, 4→④。火炎放射は プライム側6人/中央MT/真心側ST。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>次元断絶のマーチ: マップ基準A北で 北MTST / H1H2南、北←D1D2D3D4→南 (デバフ無DPSは抜ける)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>プライムフェーズはバーストとタイムライン暗記が要。固定でPTメンバーごとの担当を明文化。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>確定判決はデバフの色 (黄/紫) と親/子の判別を最優先。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>未来観測 β は配置パターンが多いので、自分のデバフごとの安置を事前にカンペ化。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>Wave Cannon (光学式波動砲) との重複処理あり。タイムラインで先回り。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>p1s</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>結呪調整ペアの位置はマーカー色基準。マクロ図の左右を要確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>p1s</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>氷火の侵食 3 回目は調整役 (MT/D3) が前 2 回の属性を見て決定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>p1s</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>時限の魔鎖は対象者デバフを見て光/火を分担。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>p2s</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>ショックウェーブの頭割り分散は『MT 組ボス下 / ST 組通路』の二分法。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>p2s</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>多重刻印は 1 回目と 2 回目で T/DPS 役割が入れ替わる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>p2s</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>カンペオスハルマの青サイコロは奇偶 (1・3 / 2・4) で配置が変わる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>p3s</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>魔力錬成・闇は近接組 (MTSTD1D2) 北 / 遠隔組 (H1H2D3D4) 南で安置取り。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>p3s</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>霊泉フェーズ塔踏み AoE: MT 組 北/西スタート、ST 組 南/東スタート (時計回り)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>p3s</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>AoE ペア: MT/ST → D1/D2 → D3/D4。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>p3s</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>辺獄黒竜巻ノックバックは黒竜巻に向かって近接が左へ、遠隔が右へ吹き飛び安置確保。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>p4s</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>後半は『劇』演出形式で時間軸が長め。各幕の入りタイミングをコールするのが安定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>p4s</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>カーテンコールは最終ギミック。TH/D で切る秒数が違うので秒数を覚える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>p4s</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>第二幕のダージャ切りは方角ベース、第三幕は犬丸式で誘導役固定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>ハイパーディメンションは北捨て→南捨ての順で処理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>プレステ散開はロール固定で簡略化できるが、後半（P5死刻）に備え位置パターンの理解も必要。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>光翼閃の捨て位置は安置横にペア（H1H2 / D34 / MTST / D12）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>トールダン位置は蒼天騎士団の出現時点で予測可能。誰かがコールすると効率的。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>ヘヴィインパクト（ドーナツ型攻撃）は中心に寄って回避。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>ディメンションクラッシュ後はエリアが分断され、6本の塔処理が必要。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>MTはボスをA（北）に向け続ける。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>ソウルテザーはタンク2名で線処理（無敵活用推奨）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>時間調整: 最期の咆哮までに削り切る必要があるため、火力管理が必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>赤線と青線は接触することで交換できる。これを利用して効率的に削る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>右眼を優先破壊、その後左眼を処理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>P4 後の P4-2「教皇庁②」では タンク LB3 を シャリベル HP 29% で使用、光翼閃② は P1 と同様。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>フィールドマーカー設置（1234マーカーは斜め内側 / ABCDは外周金リング接触）が必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>風槍: スパイラルピアス対象者は対角側へ線を伸ばし、青玉対象は北西へ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>死刻: 北西→南東に斜め8人並び、ゲリック出現位置を北として認識。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>死刻処理は固定向け（複数の流派融合のため複雑）。野良では「こまぞう式改」が主流。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>息吹は線を伸ばし過ぎて反対側の即死範囲に入らないよう注意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>アク・アファー: ヒーラー2名を起点とした頭割り、HP均等化が必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>カータライズ: MT/ST はタッチダウン A 集合、滅殺持ち近接と D3 は A に残る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>1234マーカーは「絶対的な安地」として機能。設置精度が攻略成否を分ける。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>タンクはミスが許されない（向き調整 / ヘイトコントロールの失敗は即ワイプ）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>タンク以外がダイナモ/チャリオットのコールを担当して負担軽減。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>ギガフレア: 1発目の予兆を見たら対角へ、着弾後は直線スプリント移動。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>アクモーン: 連続頭割り＋塔出現、方向は「MT組、ST組、タンク」で分散。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>p5s</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>毒石ペアは時計/反時計の方向ミスでパーティ事故になりやすい。マクロ表記を必ず読み合わせる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>p5s</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>8連噛みつき (Starving Stampede) は青マーカー順を覚えれば回避は機械的。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>p5s</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>トパーズクラスターは結晶落下順をボイチャでコールするのが安定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>p6s</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>サイコロは数字を見落とすと即死級の事故になる。声出しコールが安全。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>p6s</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>カヘキシーは外周AoE +  頭割り + デバフ位置調整の複合。マクロを読み込んでから動画予習推奨。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>p6s</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t>寄生 (ケロモーフ/グロソモーフ) は前後の扇方向に注意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>p7s</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>【凶】無敵式は無敵CDをきっちり管理。MT/ST が必ず受ける役割なのでマクロで明示。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>p7s</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>生命の果実の3種判別 (牛/鳥/ミノタウロス) を最初に覚えるとギミック流れが理解しやすい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>p7s</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>魔印創成【獄】は西島/東島で4箇所ずつの塔配置になる。Consomme Mkll の動く図解 Toolbox が予習に便利。</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>p8s</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>前半は変身ギミックを覚えれば事故りにくい。動画予習推奨。</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>p8s</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>四重炎嵐は縦横/角の判別を早く。マクロの図を覚える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>p8s</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr">
-        <is>
-          <t>幻影創造の竜竜/フェニ判別を間違えると壊滅するため、声出しコール推奨。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>p8s</t>
-        </is>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>概念支配 (High Concept) は煉獄編最難ギミック。デバフ合成を間違えるとパーティ壊滅。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>p8s</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr">
-        <is>
-          <t>万象灰燼 (Ego Death) は Immortal Conception (3デバフ合成) で生存。1人でもミスすると壊滅。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>p8s</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr">
-        <is>
-          <t>はいじあ式 / ビジョン式 / リシュア式 など流派が複数存在。Game8 採用はぬけまる版のはいじあ/ビジョン式。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>p8s</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>煉獄編クリア時の Top 50 マウント (タイマット) 報酬対象だったが、配布は終了済み。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>パンクラ：ミサイルを捨てに行くときは内周を通り、戻るときは外周から合流。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t>波動砲はタンク無敵で受け、7方向散開で AoE 処理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t>ACが綺麗に潰れたときのみ東西配置を使用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr">
-        <is>
-          <t>連携プログラムLB は線取り (MT→西/ST→東) → 時計回り処理 → 弓LBは全員でボス南誘導。</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t>シールドバッシュ&amp;フレアは盾誘導以外の7人で中央集合して頭割り。</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C104" s="8" t="inlineStr">
-        <is>
-          <t>コロッサスブロー：❶①&gt;H1MTSTD1D2D3D4H2&gt;②❹ の優先度。白＋無職→①②、紫→❶❷❸❹。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>検知式波動砲：ボス検知が逆の場合は左右反転。AC縦列(①④⑤)はボスモニターの無い方へ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr">
-        <is>
-          <t>P4 は短いがDPSチェックがシビア。バフ回しと軽減を P3 から準備しておく。</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>実質 P4 はブルースクリーン耐えのフェーズ。タンクLBやヒーラーLBの可能性も考慮。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>P5 デルタ：散開位置は言語化して共有、移動タイミングはデバフの数字で判断。</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>P5 シグマ：塔の多いほうを北として、散開時の自分のマーカー位置の塔に入る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>P5 オメガ：オメガFを基準として、③④★は回転方向で左右反転あり。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>コスモメモリー：LB3 は ST が打つ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>1回目波動砲：中央集合→1回目エクサフレア安置側マーカーに向かって AoE 捨て。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>マジックナンバー：LB3 順は MT→H1→ST→H2。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t>コスモメテオ：頭割り基本A集合、D3フレア時はC集合。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>p10s</t>
-        </is>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>パンデモニックタレットの3番レーザーは、4番タレットに向けて角度調整する必要あり。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>p10s</t>
-        </is>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>魔殿の震撃でタッチダウン発動時は西島に8人集合して処理 (Game8 主流)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t>p10s</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>ヘビーウェブの線処理は『線クロスしない』が鉄則。位置確定後に動かない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>p11s</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>アップヘルド闇は十字 (ハムカツ) と X字 (しのしょー) で野良マクロが分かれるため、募集時に流派確認必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t>p11s</t>
-        </is>
-      </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>魔法陣ディスミサル闇 / 戒律闇ディバイドは『ボスを見て』判定なのでカメラ向き重要。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>p11s</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>光と闇の調停はジジー式 (光:TH西/DPS東、闇:TH東/DPS西) が Game8 採用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>p11s</t>
-        </is>
-      </c>
-      <c r="B121" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t>ダークストリームは MT組北西 / ST組南東、内側に近接・外側に遠隔。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
-        <is>
-          <t>パラデイグマ1回目はタンク無敵処理が前提。タンクの無敵スキル管理 (リプ含む) 必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t>スーパーチェイン I/II は『8方向 → ペア → ペア半面 → ビーム誘導 → 4:4 → 塔/天火散開』の連続。</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="inlineStr">
-        <is>
-          <t>サイコロネバランは 2/4 が頭割り、ビーム順番要暗記 (5,7→6,8→1,3→2,4)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B125" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr">
-        <is>
-          <t>パラスレイは X処理 (Game8 マクロ) と K処理 (1回目バリアント) があるので募集確認必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
-        <is>
-          <t>カロリック1 (もちべ式) は風炎 ABCD の時計回り順序を厳守 (MTSTH1H2D1D2D3D4)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B127" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C127" s="8" t="inlineStr">
-        <is>
-          <t>パンゲネシスで無職スライムは 西:1マーカー / 東:2マーカー に分かれる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
-        <is>
-          <t>カロリック2 はマーカーが MT と交代になる点が 1 回目との違い。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C129" s="8" t="inlineStr">
-        <is>
-          <t>最終サモンダークネス線処理は MT/D1 ST/D2 H1/D3 H2/D4 のペアを崩さない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="inlineStr">
-        <is>
-          <t>ジャンブルコンボ (無職マラソン) はフィールド全体を活用するため、開幕の散開位置・デバフ確認が最重要。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="inlineStr">
-        <is>
-          <t>古式破砕拳の 4:4 頭割りは西/東に分かれる。クロスしないよう先に立ち位置を決める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="inlineStr">
-        <is>
-          <t>ビーストフェーズの扇誘導は TH→D 順、毒は DPS が先。両者の優先度が逆なので要意識。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B133" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C133" s="8" t="inlineStr">
-        <is>
-          <t>PERFECT GROOVE×2 で LB1 ゲージ獲得が組み込まれた火力設計。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B134" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C134" s="8" t="inlineStr">
-        <is>
-          <t>ディスコインファーナルは内外配置を間違えると死亡しやすい (Game8 マクロ図要参照)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C135" s="8" t="inlineStr">
-        <is>
-          <t>ジングル A/B はランダム選択だが、固定では同じ予約位置を使うため流派で動きが変わらない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="inlineStr">
-        <is>
-          <t>p1-front</t>
-        </is>
-      </c>
-      <c r="C136" s="8" t="inlineStr">
-        <is>
-          <t>雑魚フェーズが本層最大の難所。情報不足だと野良では事故りやすい (さり氏談)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>p1-front</t>
-        </is>
-      </c>
-      <c r="C137" s="8" t="inlineStr">
-        <is>
-          <t>ねばねば配置は北基準。Tがボス下なので、誤って T も外周に行くと事故。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>p1-front</t>
-        </is>
-      </c>
-      <c r="C138" s="8" t="inlineStr">
-        <is>
-          <t>PT構成: 赤魔→賢者、ヴァイパー導入で雑魚フェーズ対応が安定 (さり氏 活動録より)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="inlineStr">
-        <is>
-          <t>p2-back</t>
-        </is>
-      </c>
-      <c r="C139" s="8" t="inlineStr">
-        <is>
-          <t>山川火: 内側 MTH1D1D2 / 外側 STH2D3D4。</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>p2-back</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="inlineStr">
-        <is>
-          <t>雷雲: 雷雲を見て、TH 左 / 他DPS 右に散開。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B141" s="8" t="inlineStr">
-        <is>
-          <t>p2-back</t>
-        </is>
-      </c>
-      <c r="C141" s="8" t="inlineStr">
-        <is>
-          <t>塔2回目は 4・2・2 配置 (近接4人基準で時計/反時計) or 南8塔。マクロ図参照。</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C142" s="8" t="inlineStr">
-        <is>
-          <t>ビルディング処理が攻略のキー (さり氏 活動録: 7割の準備時間をここに費やした)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C143" s="8" t="inlineStr">
-        <is>
-          <t>P3 ストーンウェポンでは複数回スプリント必須。クールダウン管理を徹底。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="inlineStr">
-        <is>
-          <t>地下マーカーをマップ上に置く前提のマクロ運用 (ぬけまる固定 Lodestone 参照)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C145" s="8" t="inlineStr">
-        <is>
-          <t>ストーンウェポン: ツインは石化視線+8方向直線+ブルートスイング+ツインの複合。</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="inlineStr">
-        <is>
-          <t>ウェポンツイン+ブロウシード 1回目: MT/D3 北西、ST/D4 北東。</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B147" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C147" s="8" t="inlineStr">
-        <is>
-          <t>ウェポンツイン+ブロウシード 2回目: MT/D1 北西、ST/D2 北東、H1/D3 南西、H2/D4 南東。</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B148" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C148" s="8" t="inlineStr">
-        <is>
-          <t>前半最大の山場は『薙/廻の群狼剣』+『千年の風化』複合。</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B149" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C149" s="8" t="inlineStr">
-        <is>
-          <t>幻狼招来は『分身を見て避ける派』が多数派 (さり氏 活動録)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B150" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C150" s="8" t="inlineStr">
-        <is>
-          <t>土修正と風化IQ6000は独立する処理法だが、Game8 はこの組合せを採用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B151" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="inlineStr">
-        <is>
-          <t>後半は通し戦闘でスピード感重視 (さり氏談)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B152" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C152" s="8" t="inlineStr">
-        <is>
-          <t>孤狼の呪いは複数流派 (Alice式 / イディル式等) があるが、Game8 は Alice式を採用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B153" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C153" s="8" t="inlineStr">
-        <is>
-          <t>八連光弾の無敵タイミングは固定。MT2=2発目, ST3=3発目, T2人フルバフ=4発目。</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="inlineStr">
-        <is>
-          <t>p1-fire</t>
-        </is>
-      </c>
-      <c r="C154" s="8" t="inlineStr">
-        <is>
-          <t>フレイムフローター1回目はボス見て右上→左上の交互で逆Z字描き。</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B155" s="8" t="inlineStr">
-        <is>
-          <t>p1-fire</t>
-        </is>
-      </c>
-      <c r="C155" s="8" t="inlineStr">
-        <is>
-          <t>インセインエアー扇誘導は中央から左&gt;遠D H T 近D&gt;右。</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B156" s="8" t="inlineStr">
-        <is>
-          <t>p2-water</t>
-        </is>
-      </c>
-      <c r="C156" s="8" t="inlineStr">
-        <is>
-          <t>水牢ギミック: 赤線は A/C 方向へ伸ばし往復、青線は出現位置から縦方向へ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B157" s="8" t="inlineStr">
-        <is>
-          <t>p2-water</t>
-        </is>
-      </c>
-      <c r="C157" s="8" t="inlineStr">
-        <is>
-          <t>ハイドロバリエルはデバフ色で半面を見分ける。</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B158" s="8" t="inlineStr">
-        <is>
-          <t>p3-merge</t>
-        </is>
-      </c>
-      <c r="C158" s="8" t="inlineStr">
-        <is>
-          <t>分断フェーズ後の頭割りは H&gt;T、強攻撃は T。</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B159" s="8" t="inlineStr">
-        <is>
-          <t>p3-merge</t>
-        </is>
-      </c>
-      <c r="C159" s="8" t="inlineStr">
-        <is>
-          <t>青+赤アリウープ: 強攻撃は青タゲ持ちが離れる、頭割りは青直下から中央へ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B160" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C160" s="8" t="inlineStr">
-        <is>
-          <t>コメットレインはボス背面から時計回りで誘導。</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B161" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C161" s="8" t="inlineStr">
-        <is>
-          <t>ドミネーションは安置を北に見て、H1D3/H2D4/MTD1/STD2 で配置。</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C162" s="8" t="inlineStr">
-        <is>
-          <t>メテオレインでタンク線取りは隕石基準、MT: 23マカ、ST: 4マカ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B163" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C163" s="8" t="inlineStr">
-        <is>
-          <t>チャンピオンズ・メテオ 塔踏み1回目: 範囲捨てボス下から割れ目沿い南北。</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B164" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C164" s="8" t="inlineStr">
-        <is>
-          <t>塔踏み2回目: 1回目処理位置近くに同じペアで入る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B165" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C165" s="8" t="inlineStr">
-        <is>
-          <t>メテオスタンピード沼捨て: 北 H1D3 / 南 H2D4 (D 調整)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B166" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C166" s="8" t="inlineStr">
-        <is>
-          <t>線持ちは穴を背にして右前に伸ばす。</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C167" s="8" t="inlineStr">
-        <is>
-          <t>細胞付着 前期で線切は北から MT/D1 &gt; ST/D2 &gt; H1/D3 &gt; H2/D4 の優先度。</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="inlineStr">
-        <is>
-          <t>細胞付着 終期の線処理は中央集合→TH:西、D:東。</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B169" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C169" s="8" t="inlineStr">
-        <is>
-          <t>スローターシェッド散会組は H1MT/MTH1, D3D1/D1D3 ペアで処理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B170" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C170" s="8" t="inlineStr">
-        <is>
-          <t>リンドブルム・メテオは全体大ダメージ。詠唱完了時ボスHPが37%以下なら時間切れ突破可能の火力目安。</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B171" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C171" s="8" t="inlineStr">
-        <is>
-          <t>アルカディアンドリームは3分かけて処理するが、2分は後出し提示で実質覚えるべきは少ない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C172" s="8" t="inlineStr">
-        <is>
-          <t>Game8 4層後半ページにはマクロ本文非掲載 (2026-03-12 時点)。ぬけまる動画 or Lodestone からコピーすること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B173" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C173" s="8" t="inlineStr">
-        <is>
-          <t>/p マクロより /e (emote) のコールマクロが採用される傾向 (Sr Odin 版参照)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="inlineStr">
-        <is>
-          <t>ヴァンプストンプの近接寄りはコウモリ追従基準。HT/遠はその逆方向散開。</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B175" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C175" s="8" t="inlineStr">
-        <is>
-          <t>茨塔はロール側と頭割り側で位置が分かれる。マクロ図の左/右を要確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B176" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C176" s="8" t="inlineStr">
-        <is>
-          <t>バット・デスマッチでコウモリの誘導距離を取り過ぎると、次ギミックの本体位置調整が遅れる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B177" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C177" s="8" t="inlineStr">
-        <is>
-          <t>クアドラプルネイルのペア割は扇誘導位置から反時計回りに動く。</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B178" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C178" s="8" t="inlineStr">
-        <is>
-          <t>レイニングキャッツは MT 無敵 → MT 無敵 → D1 (南側タゲサ: H1D1D2) の順。ST 側も対称。</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B179" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C179" s="8" t="inlineStr">
-        <is>
-          <t>野良では『game8』『線とりたけし』の表記でマクロ流派が示されることが多い。</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C180" s="8" t="inlineStr">
-        <is>
-          <t>スプレッドネイルは T - D - H の 3 方向散開、ボス位置基準。</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C181" s="8" t="inlineStr">
-        <is>
-          <t>ハニー・B・ライヴ各回で「♡ハート数」によって塔位置と頭割り位置が分岐する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B182" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C182" s="8" t="inlineStr">
-        <is>
-          <t>アラームフェロモン 1 回目は外周蜂からの直線範囲、各人が個別にケアする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B183" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C183" s="8" t="inlineStr">
-        <is>
-          <t>ブラックハート後の中央集合は『早い人ペア順』。HP回復タイミングを意識する必要がある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C184" s="8" t="inlineStr">
-        <is>
-          <t>野良では『お知らせマクロ』(◯◯ Rain or Drop で次に来るギミックを宣言する) も併用される。</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B185" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C185" s="8" t="inlineStr">
-        <is>
-          <t>4 or 8 ウェイ・ダブルラリアットは『繋がれているブルートボンバーを 1 つ受ける』のが鉄則。</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B186" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C186" s="8" t="inlineStr">
-        <is>
-          <t>ボンバリアンボム 2 塔目はボス向き基準の左右なので、ボス位置確認が必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B187" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C187" s="8" t="inlineStr">
-        <is>
-          <t>零式フューズボムは『単体長ボムを北に見る』で配置確定。短/長の判定に注意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B188" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C188" s="8" t="inlineStr">
-        <is>
-          <t>極盛り式スピニングファイヤーはアタッチ (細胞付着) ギミック。基本散開と同じ位置で受ける。</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B189" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C189" s="8" t="inlineStr">
-        <is>
-          <t>円輪/輪円は『DN 式』と呼ばれる Game8 採用の位置法。動画予習必須。</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B190" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C190" s="8" t="inlineStr">
-        <is>
-          <t>エレクトロープ 2 回目はシャインスパーク被撃回数で『多/少』が決まる。22 秒/42 秒の判定タイミングを把握する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B191" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C191" s="8" t="inlineStr">
-        <is>
-          <t>エレクトロンストリームは『TH 外側 / DPS 内側』が基本。デバフ色で逆方向に受ける。</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B192" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C192" s="8" t="inlineStr">
-        <is>
-          <t>前半のタイムラインは 0 秒〜6 分 26 秒。Game8 ページに秒単位の予兆と対応が記載されている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B193" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C193" s="8" t="inlineStr">
-        <is>
-          <t>クロステイル・スペシャルでタンク LB3 を撃つのが標準。LB3 がない場合は壊滅リスク大。</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B194" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C194" s="8" t="inlineStr">
-        <is>
-          <t>マスタードボムのデバフ受取順は MT 側と ST 側で対称。順番を覚えること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B195" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C195" s="8" t="inlineStr">
-        <is>
-          <t>ブラックサバト【日出】は塔と誘導の両方を担当する役割割振りが複雑。</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B196" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C196" s="8" t="inlineStr">
-        <is>
-          <t>剣の舞 (時間切れ) 前の DPS チェックがソフト時間切れになる傾向。</t>
         </is>
       </c>
     </row>
@@ -4055,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4063,16 +699,15 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4103,50 +738,45 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>references_primary</t>
+          <t>overview_main_strategy</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>overview_main_strategy</t>
+          <t>overview_playlist_title</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
         <is>
-          <t>overview_playlist_title</t>
+          <t>overview_playlist_url</t>
         </is>
       </c>
       <c r="I1" s="7" t="inlineStr">
         <is>
-          <t>overview_playlist_url</t>
+          <t>overview_playlist_author</t>
         </is>
       </c>
       <c r="J1" s="7" t="inlineStr">
         <is>
-          <t>overview_playlist_author</t>
+          <t>overview_macro_source</t>
         </is>
       </c>
       <c r="K1" s="7" t="inlineStr">
         <is>
-          <t>overview_macro_source</t>
+          <t>overview_macro_url</t>
         </is>
       </c>
       <c r="L1" s="7" t="inlineStr">
         <is>
-          <t>overview_macro_url</t>
+          <t>overview_macro_text</t>
         </is>
       </c>
       <c r="M1" s="7" t="inlineStr">
         <is>
-          <t>overview_macro_text</t>
+          <t>overview_guide_url</t>
         </is>
       </c>
       <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>overview_guide_url</t>
-        </is>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>overview_bis_url</t>
         </is>
@@ -4178,11 +808,7 @@
           <t>4.11</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
-        </is>
-      </c>
+      <c r="F2" s="8" t="inlineStr"/>
       <c r="G2" s="8" t="inlineStr"/>
       <c r="H2" s="8" t="inlineStr"/>
       <c r="I2" s="8" t="inlineStr"/>
@@ -4191,7 +817,6 @@
       <c r="L2" s="8" t="inlineStr"/>
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -4219,11 +844,7 @@
           <t>4.31</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
-        </is>
-      </c>
+      <c r="F3" s="8" t="inlineStr"/>
       <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
@@ -4232,7 +853,6 @@
       <c r="L3" s="8" t="inlineStr"/>
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -4260,11 +880,7 @@
           <t>5.11</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
-        </is>
-      </c>
+      <c r="F4" s="8" t="inlineStr"/>
       <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" s="8" t="inlineStr"/>
@@ -4273,7 +889,6 @@
       <c r="L4" s="8" t="inlineStr"/>
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -4301,11 +916,7 @@
           <t>6.05</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 辺獄編零式1層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
@@ -4314,7 +925,6 @@
       <c r="L5" s="8" t="inlineStr"/>
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -4342,11 +952,7 @@
           <t>6.05</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 辺獄編零式2層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F6" s="8" t="inlineStr"/>
       <c r="G6" s="8" t="inlineStr"/>
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
@@ -4355,7 +961,6 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -4383,11 +988,7 @@
           <t>6.05</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 辺獄編零式3層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F7" s="8" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr"/>
@@ -4396,7 +997,6 @@
       <c r="L7" s="8" t="inlineStr"/>
       <c r="M7" s="8" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -4424,11 +1024,7 @@
           <t>6.05</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 辺獄編零式4層前半/後半 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr"/>
       <c r="H8" s="8" t="inlineStr"/>
       <c r="I8" s="8" t="inlineStr"/>
@@ -4437,7 +1033,6 @@
       <c r="L8" s="8" t="inlineStr"/>
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -4465,11 +1060,7 @@
           <t>6.11</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
-        </is>
-      </c>
+      <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr"/>
@@ -4478,7 +1069,6 @@
       <c r="L9" s="8" t="inlineStr"/>
       <c r="M9" s="8" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -4506,11 +1096,7 @@
           <t>6.21</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 煉獄編零式1層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="8" t="inlineStr"/>
       <c r="H10" s="8" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr"/>
@@ -4519,7 +1105,6 @@
       <c r="L10" s="8" t="inlineStr"/>
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -4547,11 +1132,7 @@
           <t>6.21</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 煉獄編零式2層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F11" s="8" t="inlineStr"/>
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="8" t="inlineStr"/>
@@ -4560,7 +1141,6 @@
       <c r="L11" s="8" t="inlineStr"/>
       <c r="M11" s="8" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -4588,11 +1168,7 @@
           <t>6.21</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 煉獄編零式3層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F12" s="8" t="inlineStr"/>
       <c r="G12" s="8" t="inlineStr"/>
       <c r="H12" s="8" t="inlineStr"/>
       <c r="I12" s="8" t="inlineStr"/>
@@ -4601,7 +1177,6 @@
       <c r="L12" s="8" t="inlineStr"/>
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -4629,11 +1204,7 @@
           <t>6.21</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 煉獄編零式4層前半/後半 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F13" s="8" t="inlineStr"/>
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="8" t="inlineStr"/>
@@ -4642,7 +1213,6 @@
       <c r="L13" s="8" t="inlineStr"/>
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -4670,11 +1240,7 @@
           <t>6.31</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
-        </is>
-      </c>
+      <c r="F14" s="8" t="inlineStr"/>
       <c r="G14" s="8" t="inlineStr"/>
       <c r="H14" s="8" t="inlineStr"/>
       <c r="I14" s="8" t="inlineStr"/>
@@ -4683,7 +1249,6 @@
       <c r="L14" s="8" t="inlineStr"/>
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -4711,11 +1276,7 @@
           <t>6.41</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 天獄編零式2層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F15" s="8" t="inlineStr"/>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="8" t="inlineStr"/>
       <c r="I15" s="8" t="inlineStr"/>
@@ -4724,7 +1285,6 @@
       <c r="L15" s="8" t="inlineStr"/>
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -4752,11 +1312,7 @@
           <t>6.41</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 天獄編零式3層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F16" s="8" t="inlineStr"/>
       <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="8" t="inlineStr"/>
       <c r="I16" s="8" t="inlineStr"/>
@@ -4765,7 +1321,6 @@
       <c r="L16" s="8" t="inlineStr"/>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
-      <c r="O16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -4793,11 +1348,7 @@
           <t>6.41</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 天獄編零式4層前半/後半 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F17" s="8" t="inlineStr"/>
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="8" t="inlineStr"/>
       <c r="I17" s="8" t="inlineStr"/>
@@ -4806,7 +1357,6 @@
       <c r="L17" s="8" t="inlineStr"/>
       <c r="M17" s="8" t="inlineStr"/>
       <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -4834,11 +1384,7 @@
           <t>6.41</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - 天獄編零式1層 攻略丨マクロ Ver1.1</t>
-        </is>
-      </c>
+      <c r="F18" s="8" t="inlineStr"/>
       <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="8" t="inlineStr"/>
       <c r="I18" s="8" t="inlineStr"/>
@@ -4847,7 +1393,6 @@
       <c r="L18" s="8" t="inlineStr"/>
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr"/>
-      <c r="O18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -4875,11 +1420,7 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - クルーザー級零式1層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
       <c r="I19" s="8" t="inlineStr"/>
@@ -4888,7 +1429,6 @@
       <c r="L19" s="8" t="inlineStr"/>
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -4916,11 +1456,7 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - クルーザー級零式2層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="inlineStr"/>
       <c r="G20" s="8" t="inlineStr"/>
       <c r="H20" s="8" t="inlineStr"/>
       <c r="I20" s="8" t="inlineStr"/>
@@ -4929,7 +1465,6 @@
       <c r="L20" s="8" t="inlineStr"/>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -4957,11 +1492,7 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - クルーザー級零式3層 攻略丨マクロ (さり式)</t>
-        </is>
-      </c>
+      <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="8" t="inlineStr"/>
       <c r="I21" s="8" t="inlineStr"/>
@@ -4970,7 +1501,6 @@
       <c r="L21" s="8" t="inlineStr"/>
       <c r="M21" s="8" t="inlineStr"/>
       <c r="N21" s="8" t="inlineStr"/>
-      <c r="O21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -4998,11 +1528,7 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - クルーザー級零式4層前半/後半 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F22" s="8" t="inlineStr"/>
       <c r="G22" s="8" t="inlineStr"/>
       <c r="H22" s="8" t="inlineStr"/>
       <c r="I22" s="8" t="inlineStr"/>
@@ -5011,7 +1537,6 @@
       <c r="L22" s="8" t="inlineStr"/>
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
-      <c r="O22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -5039,11 +1564,7 @@
           <t>7.4</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - ヘビー級零式2層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="8" t="inlineStr"/>
       <c r="I23" s="8" t="inlineStr"/>
@@ -5052,7 +1573,6 @@
       <c r="L23" s="8" t="inlineStr"/>
       <c r="M23" s="8" t="inlineStr"/>
       <c r="N23" s="8" t="inlineStr"/>
-      <c r="O23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -5080,11 +1600,7 @@
           <t>7.4</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - ヘビー級零式3層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F24" s="8" t="inlineStr"/>
       <c r="G24" s="8" t="inlineStr"/>
       <c r="H24" s="8" t="inlineStr"/>
       <c r="I24" s="8" t="inlineStr"/>
@@ -5093,7 +1609,6 @@
       <c r="L24" s="8" t="inlineStr"/>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="8" t="inlineStr"/>
-      <c r="O24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -5121,11 +1636,7 @@
           <t>7.4</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - ヘビー級零式4層前半/後半 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="inlineStr"/>
       <c r="G25" s="8" t="inlineStr"/>
       <c r="H25" s="8" t="inlineStr"/>
       <c r="I25" s="8" t="inlineStr"/>
@@ -5134,7 +1645,6 @@
       <c r="L25" s="8" t="inlineStr"/>
       <c r="M25" s="8" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -5162,11 +1672,7 @@
           <t>7.4</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - ヘビー級零式1層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F26" s="8" t="inlineStr"/>
       <c r="G26" s="8" t="inlineStr"/>
       <c r="H26" s="8" t="inlineStr"/>
       <c r="I26" s="8" t="inlineStr"/>
@@ -5175,7 +1681,6 @@
       <c r="L26" s="8" t="inlineStr"/>
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
-      <c r="O26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -5203,11 +1708,7 @@
           <t>7.05</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - アルカディア零式1層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F27" s="8" t="inlineStr"/>
       <c r="G27" s="8" t="inlineStr"/>
       <c r="H27" s="8" t="inlineStr"/>
       <c r="I27" s="8" t="inlineStr"/>
@@ -5216,7 +1717,6 @@
       <c r="L27" s="8" t="inlineStr"/>
       <c r="M27" s="8" t="inlineStr"/>
       <c r="N27" s="8" t="inlineStr"/>
-      <c r="O27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -5244,11 +1744,7 @@
           <t>7.05</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - アルカディア零式2層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F28" s="8" t="inlineStr"/>
       <c r="G28" s="8" t="inlineStr"/>
       <c r="H28" s="8" t="inlineStr"/>
       <c r="I28" s="8" t="inlineStr"/>
@@ -5257,7 +1753,6 @@
       <c r="L28" s="8" t="inlineStr"/>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="8" t="inlineStr"/>
-      <c r="O28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -5285,11 +1780,7 @@
           <t>7.05</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - アルカディア零式3層 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F29" s="8" t="inlineStr"/>
       <c r="G29" s="8" t="inlineStr"/>
       <c r="H29" s="8" t="inlineStr"/>
       <c r="I29" s="8" t="inlineStr"/>
@@ -5298,7 +1789,6 @@
       <c r="L29" s="8" t="inlineStr"/>
       <c r="M29" s="8" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
-      <c r="O29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -5326,11 +1816,7 @@
           <t>7.05</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Game8 (ゲームエイト) - アルカディア零式4層前半/後半 攻略丨マクロ</t>
-        </is>
-      </c>
+      <c r="F30" s="8" t="inlineStr"/>
       <c r="G30" s="8" t="inlineStr"/>
       <c r="H30" s="8" t="inlineStr"/>
       <c r="I30" s="8" t="inlineStr"/>
@@ -5339,7 +1825,6 @@
       <c r="L30" s="8" t="inlineStr"/>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="8" t="inlineStr"/>
-      <c r="O30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -5367,11 +1852,7 @@
           <t>7.11</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>りりーどーる (Lily Doll) - Lodestone 日記</t>
-        </is>
-      </c>
+      <c r="F31" s="8" t="inlineStr"/>
       <c r="G31" s="8" t="inlineStr"/>
       <c r="H31" s="8" t="inlineStr"/>
       <c r="I31" s="8" t="inlineStr"/>
@@ -5380,7 +1861,6 @@
       <c r="L31" s="8" t="inlineStr"/>
       <c r="M31" s="8" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
-      <c r="O31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -5408,11 +1888,7 @@
           <t>7.51</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>Consolegameswiki</t>
-        </is>
-      </c>
+      <c r="F32" s="8" t="inlineStr"/>
       <c r="G32" s="8" t="inlineStr"/>
       <c r="H32" s="8" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr"/>
@@ -5421,7 +1897,6 @@
       <c r="L32" s="8" t="inlineStr"/>
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="8" t="inlineStr"/>
-      <c r="O32" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -19629,11 +16104,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:C196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -19644,7 +16120,12 @@
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>phase_id</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>tip</t>
         </is>
       </c>
     </row>
@@ -19656,7 +16137,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Unending_Coil_of_Bahamut_(Ultimate)</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Twister の捨て位置は近接組がボスクリーブ内に置くと安定する。</t>
         </is>
       </c>
     </row>
@@ -19668,7 +16154,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>https://finalfantasy.fandom.com/wiki/The_Unending_Coil_of_Bahamut</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>拘束具 (Liquid Hell) は▽逆三角に置いて第7霊災のハッチ位置を見やすくする。</t>
         </is>
       </c>
     </row>
@@ -19680,7 +16171,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5248067/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Death Sentence (タンクバスター) は MT 側 CD or ST スイッチで受ける。</t>
         </is>
       </c>
     </row>
@@ -19692,7 +16188,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/48995158/blog/5388500/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>コール (引用詠唱) のパターンを覚えるのが攻略のメイン。</t>
         </is>
       </c>
     </row>
@@ -19704,7 +16205,12 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRfzohN1djyZuQiDfalhXeg</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>サンダーストラック (青雷) 付与者は声で大きくコールする慣習。</t>
         </is>
       </c>
     </row>
@@ -19716,7 +16222,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/playlist?list=PL2Hitw4uipFQGxLqqfHSCxwRO5svpC7Q9</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>ダイブマーカーは雷ターゲットを参考に配置を判断する。</t>
         </is>
       </c>
     </row>
@@ -19728,7 +16239,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/playlist?list=PL2Hitw4uipFQt5qLdT6wi8BS2h_iUdOv2</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>三重奏は全て『プライム + ネール + ツインタニアの 3 体が同時にギミックを実行する』構造。</t>
         </is>
       </c>
     </row>
@@ -19740,7 +16256,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>https://asellog.com/bahamut-ultimate/</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Trio 順: 進軍 → 黒炎 → 災厄 → 天地 → 連撃 → 八重奏 (Grand Octet) の 6 段階。</t>
         </is>
       </c>
     </row>
@@ -19752,7 +16273,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>https://asellog.com/bahamut-p1/</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>八重奏のマラソン方向はプライム/ネール出現位置で時計/反時計を判断する (要事前合意)。</t>
         </is>
       </c>
     </row>
@@ -19764,7 +16290,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>https://asellog.com/bahamut-p2/</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>群竜のメガフレアダイブで TLB3 を打つので、ST タンク無敵タイミングと衝突しないこと。</t>
         </is>
       </c>
     </row>
@@ -19776,7 +16307,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>https://asellog.com/bahamut-p3tl3/</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>2 体の HP は同期して削るのが鉄則 (片方を先に倒すと残った方が enrage)。</t>
         </is>
       </c>
     </row>
@@ -19788,7 +16324,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>https://asellog.com/bahamut-p5/</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>P1 / P2 のギミックを混合処理するため、配置・コールはパーティ事前合意必須。</t>
         </is>
       </c>
     </row>
@@ -19800,7 +16341,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5186770/</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>常時移動が必要 (Twister 回避)。</t>
         </is>
       </c>
     </row>
@@ -19812,7 +16358,12 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1pOQ3sMSUQx-E-zFJSFv5BbHIq27tASgH14WhM02k4NI/edit?usp=sharing</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>エクサフレアの安置察知が最大の難所。フェニックスの加護 (リレイズ) を失わないよう優先処理。</t>
         </is>
       </c>
     </row>
@@ -19824,7 +16375,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>http://laytina14.com/archives/14617575.html</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>モーン・アファーはボス足元スタック (8人分散)。</t>
         </is>
       </c>
     </row>
@@ -19836,7 +16392,12 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>http://laytina14.com/archives/13711663.html</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>アク・モーン は連続 3〜6 回、MT/ST 無敵 (リビデ/インビン) を交互に使用。</t>
         </is>
       </c>
     </row>
@@ -19848,163 +16409,233 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/mimichoco_33/n/n1d5a37c5ff5a</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>ヒーラー軽減はパーティ全体攻撃に合わせて使用。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>https://www.nonbiri.blog/ultimate-bahamut/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>覚醒バフは BH &gt; D4 &gt; D1 の順で取得。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>https://www.tawakemonoga.com/archives/5043</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>ミストラルソングは MT B&gt;A&gt;C / ST D&gt;C&gt;A の順で誘導。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>https://blog.sheeva.me/entry/ucob-clear-report</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>インシネレートは 1 回目 ST 無敵 / 2 回目 MT 無敵 (ナイト MT なら 1 回目無敵)。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/jiojio1020/n/n23c45fbaeb3e</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>楔配置: 上段に ③ ④、下段に D3 ① ② D4 (逆 Z 字)。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>https://overpower.hateblo.jp/entry/2023/04/09/182139</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>エラプ誘導は D3D4 が担当した後に楔処理へ移行。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/moka_melon/n/n11039606e6c9</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>ジェイル位置: ボス D4 / H1 / H2。ランスラ斜め誘導。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>https://github.com/akitoki/FF14_docs/blob/master/%E7%B5%B6%E3%83%90%E3%83%8F_%E3%83%9E%E3%82%AF%E3%83%AD.txt</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>マウンテンバスター 1回目&amp;3回目は MT バフ / 2回目は ST バフ(orかばう)。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/bright_murre577/n/nbd626a0969d9</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>アルテマ履行 LB 使用順: D4 -&gt; H2 -&gt; D1 -&gt; MT。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>https://www.icy-veins.com/ffxiv/the-unending-coil-of-bahamut-ultimate-guides-twintania</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>吸着爆雷(ヘイト1位)は MT 無敵 -&gt; 激震後半で ST 挑発。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>https://www.icy-veins.com/ffxiv/the-unending-coil-of-bahamut-ultimate-guides-nael-deus-darnus</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>誘導レーザー(ヘイト2位)は追撃中は MT 無敵 / 爆撃中は ST 無敵。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>https://www.icy-veins.com/ffxiv/the-unending-coil-of-bahamut-ultimate-guides-bahamut-prime</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>緑玉 1 回目は MT/ST/D1 の 3 人で処理。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>https://naurffxiv.com/ultimate/ucob</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>灼熱はヒラがメソハイ線取り (2 回目)。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>ucob</t>
+          <t>uwu</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>https://novacrystallis.com/2017/11/group-including-ex-lucrezia-players-claims-world-first-clear-unending-coil-bahamut-raid/</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>乱撃顔面受けは ST が LB3。ヒラは堅実魔で詠唱中断回避。</t>
         </is>
       </c>
     </row>
@@ -20016,7 +16647,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Weapon%27s_Refrain_(Ultimate)</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>紫玉散開: MT AB間-&gt;AD間 / ST BC間 / その他 CD間。</t>
         </is>
       </c>
     </row>
@@ -20028,139 +16664,199 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>https://jp.finalfantasyxiv.com/lodestone/character/34120564/blog/5248065/</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>最終三蛮神の移動ルートはパターン分岐。事前にホットバーカンペ準備推奨。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5248065</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>ヤークト無視はペインのダメージ大かつブレが大きいので、軽減を絶対切らさない。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>https://asellog.com/uwu/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>可視扇 (プロティアン) は D3 が誘導、不可視扇は D4 担当が標準。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/mozuzuzu/n/nd4fb5fff75ab</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>サイコロ 1211 は中央ピザ (フィールド8等分) を踏み替えていくため自分の番号位置を即座に判断。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/16539</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>サイコロ番号順に散開 (西H1 → 西D3D4D2D1東) で雷散開を綺麗に作る。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/16288</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>ヒラ先渡しは1回目 DPS が反時計で受け渡す手順を体に覚えさせる。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@aomintotto</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Limit Cut (P1とP2の間) は数字順にスタンを撃ち抜くシンプル処理。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/playlist?list=PL2Hitw4uipFQQ8svogk788A9eWSPtz33M</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>時空潜航のマーチ: ラピス 1→①, 2→②, 3→③, 4→④。火炎放射は プライム側6人/中央MT/真心側ST。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1C73RrIVV6sUoTxwUSiifMp_oktkxeOAWn9RbwbVrUOk/edit?usp=sharing</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>次元断絶のマーチ: マップ基準A北で 北MTST / H1H2南、北←D1D2D3D4→南 (デバフ無DPSは抜ける)。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/lastagous/n/ncfcb027117fd</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>プライムフェーズはバーストとタイムライン暗記が要。固定でPTメンバーごとの担当を明文化。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>https://rentry.co/ultimate_weapon_lodestone_plan</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>確定判決はデバフの色 (黄/紫) と親/子の判別を最優先。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/19924564/blog/4695414/</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>未来観測 β は配置パターンが多いので、自分のデバフごとの安置を事前にカンペ化。</t>
         </is>
       </c>
     </row>
@@ -20172,3403 +16868,2579 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Epic_of_Alexander_(Ultimate)</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Wave Cannon (光学式波動砲) との重複処理あり。タイムラインで先回り。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p1s</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5274750/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>結呪調整ペアの位置はマーカー色基準。マクロ図の左右を要確認。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p1s</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCnqM3_n_pUJjno0iG_5-RcQ</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>氷火の侵食 3 回目は調整役 (MT/D3) が前 2 回の属性を見て決定する。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p1s</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/playlist?list=PLsiXqXniAzw6lp6zd5uwSsRbkmbPNTfWd</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>時限の魔鎖は対象者デバフを見て光/火を分担。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p2s</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>https://fuucdayo.com/battle/4046/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>ショックウェーブの頭割り分散は『MT 組ボス下 / ST 組通路』の二分法。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p2s</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>https://fuucdayo.com/battle/3685/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>多重刻印は 1 回目と 2 回目で T/DPS 役割が入れ替わる。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p2s</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>https://asellog.com/alexander-syncgear/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>カンペオスハルマの青サイコロは奇偶 (1・3 / 2・4) で配置が変わる。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p3s</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5186772/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>魔力錬成・闇は近接組 (MTSTD1D2) 北 / 遠隔組 (H1H2D3D4) 南で安置取り。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p3s</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1B2hdvvofSn2oEKHygcEU7Knsf3bdq93jUIuyQDyhvQ0/edit?usp=sharing</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>霊泉フェーズ塔踏み AoE: MT 組 北/西スタート、ST 組 南/東スタート (時計回り)。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p3s</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>https://automaton-media.com/articles/newsjp/20191118-106564/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>AoE ペア: MT/ST → D1/D2 → D3/D4。</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p3s</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>https://www.nonbiri.blog/ultimate-alexander/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>辺獄黒竜巻ノックバックは黒竜巻に向かって近接が左へ、遠隔が右へ吹き飛び安置確保。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p4s</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>https://risinghisa.com/theepicofalexanderultimate/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>後半は『劇』演出形式で時間軸が長め。各幕の入りタイミングをコールするのが安定。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p4s</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/29855765/blog/5390102/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>カーテンコールは最終ギミック。TH/D で切る秒数が違うので秒数を覚える。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p4s</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/30534036/blog/5531134/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>第二幕のダージャ切りは方角ベース、第三幕は犬丸式で誘導役固定。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/hur57/n/na21845e7e767</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>ハイパーディメンションは北捨て→南捨ての順で処理。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/mimichoco_33/n/n9ab4e7001ef2</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>プレステ散開はロール固定で簡略化できるが、後半（P5死刻）に備え位置パターンの理解も必要。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>https://blog.sheeva.me/ult-alexander-statics</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>光翼閃の捨て位置は安置横にペア（H1H2 / D34 / MTST / D12）。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>p1s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/421207</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>トールダン位置は蒼天騎士団の出現時点で予測可能。誰かがコールすると効率的。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>p1s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/23752</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>ヘヴィインパクト（ドーナツ型攻撃）は中心に寄って回避。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>p1s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>https://final-fantasy.cc/14/id/8/pan_hen_r1.php</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>ディメンションクラッシュ後はエリアが分断され、6本の塔処理が必要。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>p1s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Asphodelos:_The_First_Circle_(Savage)</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>MTはボスをA（北）に向け続ける。</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>p1s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>https://www.akhmorning.com/raids/p1s/</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>ソウルテザーはタンク2名で線処理（無敵活用推奨）。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>p1s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eGJ5eRvRzK8</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>時間調整: 最期の咆哮までに削り切る必要があるため、火力管理が必須。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>p2s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/365105</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>赤線と青線は接触することで交換できる。これを利用して効率的に削る。</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>p2s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>https://final-fantasy.cc/14/id/8/pan_hen_r2.php</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>右眼を優先破壊、その後左眼を処理。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>p2s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>https://closedalpha.com/ffxiv-guide/ffxiv-required-dps-hippokampos/</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>P4 後の P4-2「教皇庁②」では タンク LB3 を シャリベル HP 29% で使用、光翼閃② は P1 と同様。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>p2s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>https://www.mtgames.jp/contents/FF14-RAID-002-PANDEMONIUM-1-2.html</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>フィールドマーカー設置（1234マーカーは斜め内側 / ABCDは外周金リング接触）が必須。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>p2s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>https://www.aquacat.work/entry/2022/01/05/055406</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>風槍: スパイラルピアス対象者は対角側へ線を伸ばし、青玉対象は北西へ。</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>p2s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Asphodelos:_The_Second_Circle_(Savage)</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>死刻: 北西→南東に斜め8人並び、ゲリック出現位置を北として認識。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>p3s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/421350</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>死刻処理は固定向け（複数の流派融合のため複雑）。野良では「こまぞう式改」が主流。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>p3s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/23996</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>息吹は線を伸ばし過ぎて反対側の即死範囲に入らないよう注意。</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>p3s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>https://www.sunny-stronger.com/entry/2022/01/25/180000</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>アク・アファー: ヒーラー2名を起点とした頭割り、HP均等化が必須。</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>p3s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/29214030/blog/4957280/</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>カータライズ: MT/ST はタッチダウン A 集合、滅殺持ち近接と D3 は A に残る。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>p3s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Asphodelos:_The_Third_Circle_(Savage)</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>1234マーカーは「絶対的な安地」として機能。設置精度が攻略成否を分ける。</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/421733</t>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>タンクはミスが許されない（向き調整 / ヘイトコントロールの失敗は即ワイプ）。</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/422515</t>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>タンク以外がダイナモ/チャリオットのコールを担当して負担軽減。</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/23843</t>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>ギガフレア: 1発目の予兆を見たら対角へ、着弾後は直線スプリント移動。</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>https://final-fantasy.cc/14/id/8/pan_hen_n4.php</t>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>アクモーン: 連続頭割り＋塔出現、方向は「MT組、ST組、タンク」で分散。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>p5s</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>https://closedalpha.com/ffxiv-guide/ffxiv-pandemonium-fourth-circle-part1-dps/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>毒石ペアは時計/反時計の方向ミスでパーティ事故になりやすい。マクロ表記を必ず読み合わせる。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>p5s</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>https://www.mtgames.jp/contents/FF14-RAID-002-PANDEMONIUM-1-4.html</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>8連噛みつき (Starving Stampede) は青マーカー順を覚えれば回避は機械的。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>p5s</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>https://www.aquacat.work/entry/2022/01/08/032112</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>トパーズクラスターは結晶落下順をボイチャでコールするのが安定。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>p6s</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>https://bunchiry.com/p4s-review/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>サイコロは数字を見落とすと即死級の事故になる。声出しコールが安全。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>p6s</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>https://ameblo.jp/ff14rensyubu/entry-12735791846.html</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>カヘキシーは外周AoE +  頭割り + デバフ位置調整の複合。マクロを読み込んでから動画予習推奨。</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>p6s</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AH0mRxuJx7c</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>寄生 (ケロモーフ/グロソモーフ) は前後の扇方向に注意。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>p7s</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GYCDnITC_jc</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>【凶】無敵式は無敵CDをきっちり管理。MT/ST が必ず受ける役割なのでマクロで明示。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>p7s</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Asphodelos:_The_Fourth_Circle_(Savage)</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>生命の果実の3種判別 (牛/鳥/ミノタウロス) を最初に覚えるとギミック流れが理解しやすい。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p7s</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Dragonsong%27s_Reprise_(Ultimate)</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>魔印創成【獄】は西島/東島で4箇所ずつの塔配置になる。Consomme Mkll の動く図解 Toolbox が予習に便利。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>https://jp.finalfantasyxiv.com/lodestone/character/34120564/blog/5178834/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>前半は変身ギミックを覚えれば事故りにくい。動画予習推奨。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>四重炎嵐は縦横/角の判別を早く。マクロの図を覚える。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NIroKcIHpnI</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>幻影創造の竜竜/フェニ判別を間違えると壊滅するため、声出しコール推奨。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3yJpWHmKjpg</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>概念支配 (High Concept) は煉獄編最難ギミック。デバフ合成を間違えるとパーティ壊滅。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1fsbzkZsWUE</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>万象灰燼 (Ego Death) は Immortal Conception (3デバフ合成) で生存。1人でもミスすると壊滅。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mxeQNCgHI7Y</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>はいじあ式 / ビジョン式 / リシュア式 など流派が複数存在。Game8 採用はぬけまる版のはいじあ/ビジョン式。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>https://fuucdayo.com/battle/3414/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>煉獄編クリア時の Top 50 マウント (タイマット) 報酬対象だったが、配布は終了済み。</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24113</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>パンクラ：ミサイルを捨てに行くときは内周を通り、戻るときは外周から合流。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24197</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>波動砲はタンク無敵で受け、7方向散開で AoE 処理。</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24296</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>ACが綺麗に潰れたときのみ東西配置を使用する。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24357</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>連携プログラムLB は線取り (MT→西/ST→東) → 時計回り処理 → 弓LBは全員でボス南誘導。</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24400</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>シールドバッシュ&amp;フレアは盾誘導以外の7人で中央集合して頭割り。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24419</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>コロッサスブロー：❶①&gt;H1MTSTD1D2D3D4H2&gt;②❹ の優先度。白＋無職→①②、紫→❶❷❸❹。</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24493</t>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>検知式波動砲：ボス検知が逆の場合は左右反転。AC縦列(①④⑤)はボスモニターの無い方へ。</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24559</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>P4 は短いがDPSチェックがシビア。バフ回しと軽減を P3 から準備しておく。</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24254</t>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>実質 P4 はブルースクリーン耐えのフェーズ。タンクLBやヒーラーLBの可能性も考慮。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>https://automaton-media.com/articles/newsjp/20220503-201287/</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>P5 デルタ：散開位置は言語化して共有、移動タイミングはデバフの数字で判断。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5006460/</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>P5 シグマ：塔の多いほうを北として、散開時の自分のマーカー位置の塔に入る。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1mvMEPv8BkWObs1z37AeOZ41u0dHV5RpA8_Sbzd3x84Y/edit?usp=sharing</t>
+          <t>p5</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>P5 オメガ：オメガFを基準として、③④★は回転方向で左右反転あり。</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/26040845/blog/5034036/</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>コスモメモリー：LB3 は ST が打つ。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/26041085/blog/5023548/</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>1回目波動砲：中央集合→1回目エクサフレア安置側マーカーに向かって AoE 捨て。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>https://meilog-ff14.com/sikoku-kaisetsu/</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>マジックナンバー：LB3 順は MT→H1→ST→H2。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/36315484/blog/5022452/</t>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>コスモメテオ：頭割り基本A集合、D3フレア時はC集合。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p10s</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>http://laytina14.com/archives/30475371.html</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>パンデモニックタレットの3番レーザーは、4番タレットに向けて角度調整する必要あり。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p10s</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Tsune/ryushi</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>魔殿の震撃でタッチダウン発動時は西島に8人集合して処理 (Game8 主流)。</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p10s</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/464675</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>ヘビーウェブの線処理は『線クロスしない』が鉄則。位置確定後に動かない。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p11s</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Abyssos:_The_Fifth_Circle_(Savage)</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>アップヘルド闇は十字 (ハムカツ) と X字 (しのしょー) で野良マクロが分かれるため、募集時に流派確認必須。</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p11s</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/3285757/blog/5089241/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>魔法陣ディスミサル闇 / 戒律闇ディバイドは『ボスを見て』判定なのでカメラ向き重要。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p11s</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/30439801/blog/5088900/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>光と闇の調停はジジー式 (光:TH西/DPS東、闇:TH東/DPS西) が Game8 採用。</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p11s</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/20369220/blog/5088849/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>ダークストリームは MT組北西 / ST組南東、内側に近接・外側に遠隔。</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/2342662/blog/4929308</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>パラデイグマ1回目はタンク無敵処理が前提。タンクの無敵スキル管理 (リプ含む) 必須。</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>https://next-innovation-fuk.com/2022/08/20/ff14-%E3%83%91%E3%83%83%E3%83%816-2x-%E3%80%8C%E9%9B%B6%E5%BC%8F%E3%80%8D%E4%B8%87%E9%AD%94%E6%AE%BF%E3%83%91%E3%83%B3%E3%83%87%E3%83%A2%E3%83%8B%E3%82%A6%E3%83%A0%EF%BC%9A%E7%85%89%E7%8D%84%E7%B7%A8/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>スーパーチェイン I/II は『8方向 → ペア → ペア半面 → ビーム誘導 → 4:4 → 塔/天火散開』の連続。</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/24597</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>サイコロネバランは 2/4 が頭割り、ビーム順番要暗記 (5,7→6,8→1,3→2,4)。</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>パラスレイは X処理 (Game8 マクロ) と K処理 (1回目バリアント) があるので募集確認必須。</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>https://monoqloblog.com/pandaemoniumpurgatoryff14/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>カロリック1 (もちべ式) は風炎 ABCD の時計回り順序を厳守 (MTSTH1H2D1D2D3D4)。</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/479307</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>パンゲネシスで無職スライムは 西:1マーカー / 東:2マーカー に分かれる。</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Abyssos:_The_Sixth_Circle_(Savage)</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>カロリック2 はマーカーが MT と交代になる点が 1 回目との違い。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>https://www.icy-veins.com/ffxiv/the-sixth-circle-savage-raid-guide</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>最終サモンダークネス線処理は MT/D1 ST/D2 H1/D3 H2/D4 のペアを崩さない。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>p9s</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>https://www.fanbyte.com/ffxiv/guides/ffxiv-p6s-guide-cachexia</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>ジャンブルコンボ (無職マラソン) はフィールド全体を活用するため、開幕の散開位置・デバフ確認が最重要。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>p9s</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/3285757/blog/5089241/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>古式破砕拳の 4:4 頭割りは西/東に分かれる。クロスしないよう先に立ち位置を決める。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>p9s</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/7053586/blog/5108897/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>ビーストフェーズの扇誘導は TH→D 順、毒は DPS が先。両者の優先度が逆なので要意識。</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>m5s</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>https://closedalpha.com/ffxiv-guide/ffxiv-pandemonium-p6s-dps/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>PERFECT GROOVE×2 で LB1 ゲージ獲得が組み込まれた火力設計。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>m5s</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>ディスコインファーナルは内外配置を間違えると死亡しやすい (Game8 マクロ図要参照)。</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>m5s</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>https://monoqloblog.com/pandaemoniumpurgatoryff14/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>ジングル A/B はランダム選択だが、固定では同じ予約位置を使うため流派で動きが変わらない。</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m6s</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/479465</t>
+          <t>p1-front</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>雑魚フェーズが本層最大の難所。情報不足だと野良では事故りやすい (さり氏談)。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m6s</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Abyssos:_The_Seventh_Circle_(Savage)</t>
+          <t>p1-front</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>ねばねば配置は北基準。Tがボス下なので、誤って T も外周に行くと事故。</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m6s</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>https://www.icy-veins.com/ffxiv/the-seventh-circle-savage-raid-guide</t>
+          <t>p1-front</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>PT構成: 赤魔→賢者、ヴァイパー導入で雑魚フェーズ対応が安定 (さり氏 活動録より)。</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m6s</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>https://www.fanbyte.com/ffxiv/guides/abyssos-the-seventh-circle-raid-guide-pandaemonium-ffxiv-patch-6-2</t>
+          <t>p2-back</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>山川火: 内側 MTH1D1D2 / 外側 STH2D3D4。</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m6s</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/3285757/blog/5089241/</t>
+          <t>p2-back</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>雷雲: 雷雲を見て、TH 左 / 他DPS 右に散開。</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m6s</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/8075024/blog/5094303/</t>
+          <t>p2-back</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>塔2回目は 4・2・2 配置 (近接4人基準で時計/反時計) or 南8塔。マクロ図参照。</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m7s</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/33856878/blog/5091223/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t>ビルディング処理が攻略のキー (さり氏 活動録: 7割の準備時間をここに費やした)。</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m7s</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>https://gamerescape.com/2022/08/25/ffxiv-endwalker-guide-abyssos-the-seventh-circle/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>P3 ストーンウェポンでは複数回スプリント必須。クールダウン管理を徹底。</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m7s</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t>地下マーカーをマップ上に置く前提のマクロ運用 (ぬけまる固定 Lodestone 参照)。</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>m7s</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>https://monoqloblog.com/pandaemoniumpurgatoryff14/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>ストーンウェポン: ツインは石化視線+8方向直線+ブルートスイング+ツインの複合。</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m7s</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/480095</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>ウェポンツイン+ブロウシード 1回目: MT/D3 北西、ST/D4 北東。</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m7s</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/480771</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>ウェポンツイン+ブロウシード 2回目: MT/D1 北西、ST/D2 北東、H1/D3 南西、H2/D4 南東。</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m8s</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Abyssos:_The_Eighth_Circle_(Savage)</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>前半最大の山場は『薙/廻の群狼剣』+『千年の風化』複合。</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m8s</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/3285757/blog/5089241/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>幻狼招来は『分身を見て避ける派』が多数派 (さり氏 活動録)。</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m8s</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/33856878/blog/5100712/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>土修正と風化IQ6000は独立する処理法だが、Game8 はこの組合せを採用。</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m8s</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>https://neko14.com/2022/10/24/post-4715/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>後半は通し戦闘でスピード感重視 (さり氏談)。</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m8s</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>https://ameblo.jp/angelo-ff14/entry-12761214317.html</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C152" s="8" t="inlineStr">
+        <is>
+          <t>孤狼の呪いは複数流派 (Alice式 / イディル式等) があるが、Game8 は Alice式を採用。</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m8s</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>https://gamixor.com/%E4%B8%87%E9%AD%94%E6%AE%BF%E3%83%91%E3%83%B3%E3%83%87%E3%83%A2%E3%83%8B%E3%82%A6%E3%83%A0%E9%9B%B6%E5%BC%8F%E3%80%80%E7%85%89%E7%8D%84%E7%B7%A8%E3%80%80%E6%94%BB%E7%95%A5%E3%80%80lv90/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>八連光弾の無敵タイミングは固定。MT2=2発目, ST3=3発目, T2人フルバフ=4発目。</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m10s</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
+          <t>p1-fire</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>フレイムフローター1回目はボス見て右上→左上の交互で逆Z字描き。</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>m10s</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>https://monoqloblog.com/pandaemoniumpurgatoryff14/</t>
+          <t>p1-fire</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>インセインエアー扇誘導は中央から左&gt;遠D H T 近D&gt;右。</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m10s</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Omega_Protocol_(Ultimate)</t>
+          <t>p2-water</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>水牢ギミック: 赤線は A/C 方向へ伸ばし往復、青線は出現位置から縦方向へ。</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m10s</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>https://finalfantasy.fandom.com/wiki/The_Omega_Protocol_(Final_Fantasy_XIV)</t>
+          <t>p2-water</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>ハイドロバリエルはデバフ色で半面を見分ける。</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m10s</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5178791/</t>
+          <t>p3-merge</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t>分断フェーズ後の頭割りは H&gt;T、強攻撃は T。</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m10s</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>https://jp.finalfantasyxiv.com/lodestone/character/5417527/blog/5181737/</t>
+          <t>p3-merge</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>青+赤アリウープ: 強攻撃は青タゲ持ちが離れる、頭割りは青直下から中央へ。</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m11s</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t>コメットレインはボス背面から時計回りで誘導。</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m11s</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/playlist?list=PLsiXqXniAzw4uAquherI4CsrvISvIeIFN</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>ドミネーションは安置を北に見て、H1D3/H2D4/MTD1/STD2 で配置。</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m11s</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TeamLucrezia</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t>メテオレインでタンク線取りは隕石基準、MT: 23マカ、ST: 4マカ。</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m11s</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>https://fuucdayo.com/battle/3831/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>チャンピオンズ・メテオ 塔踏み1回目: 範囲捨てボス下から割れ目沿い南北。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m11s</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>https://asellog.com/omega-raidrace/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t>塔踏み2回目: 1回目処理位置近くに同じペアで入る。</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m11s</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>https://game.watch.impress.co.jp/docs/news/1475183.html</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>メテオスタンピード沼捨て: 北 H1D3 / 南 H2D4 (D 調整)。</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m11s</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5168136/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t>線持ちは穴を背にして右前に伸ばす。</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>https://docs.google.com/spreadsheets/d/1G10SCv2lJ-42k0bnTduYnBRnOQ5pj9xLs-qMSqJBYb8/edit?usp=sharing</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>細胞付着 前期で線切は北から MT/D1 &gt; ST/D2 &gt; H1/D3 &gt; H2/D4 の優先度。</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/8075024/blog/5173660/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>細胞付着 終期の線処理は中央集合→TH:西、D:東。</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/44887504/blog/5210462/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>スローターシェッド散会組は H1MT/MTH1, D3D1/D1D3 ペアで処理。</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/hana25o/n/nca4c23b5904e</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>リンドブルム・メテオは全体大ダメージ。詠唱完了時ボスHPが37%以下なら時間切れ突破可能の火力目安。</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>https://sarachantubuyaki.jp/finalfantasyxiv/run-dynamis/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>アルカディアンドリームは3分かけて処理するが、2分は後出し提示で実質覚えるべきは少ない。</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/36478083/blog/5321725/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t>Game8 4層後半ページにはマクロ本文非掲載 (2026-03-12 時点)。ぬけまる動画 or Lodestone からコピーすること。</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/36478083/blog/5318815/</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>/p マクロより /e (emote) のコールマクロが採用される傾向 (Sr Odin 版参照)。</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m9s</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/topics/detail/eb629fcb7ef6a1317bb1957f1b5cdc144ef1fb6f</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t>ヴァンプストンプの近接寄りはコウモリ追従基準。HT/遠はその逆方向散開。</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>p10s</t>
+          <t>m9s</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/532718</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>茨塔はロール側と頭割り側で位置が分かれる。マクロ図の左/右を要確認。</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>p10s</t>
+          <t>m9s</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Anabaseios:_The_Tenth_Circle_(Savage)</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t>バット・デスマッチでコウモリの誘導距離を取り過ぎると、次ギミックの本体位置調整が遅れる。</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t>p10s</t>
+          <t>m1s</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/29231383/blog/5231433</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>クアドラプルネイルのペア割は扇誘導位置から反時計回りに動く。</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="8" t="inlineStr">
         <is>
-          <t>p10s</t>
+          <t>m1s</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C178" s="8" t="inlineStr">
+        <is>
+          <t>レイニングキャッツは MT 無敵 → MT 無敵 → D1 (南側タゲサ: H1D1D2) の順。ST 側も対称。</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="8" t="inlineStr">
         <is>
-          <t>p10s</t>
+          <t>m1s</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>https://next-innovation-fuk.com/2023/05/29/ff14-%E3%83%91%E3%83%83%E3%83%816-4x-%E3%80%8C%E9%9B%B6%E5%BC%8F%E3%80%8D%E4%B8%87%E9%AD%94%E6%AE%BF%E3%83%91%E3%83%B3%E3%83%87%E3%83%A2%E3%83%8B%E3%82%A6%E3%83%A0%E9%9B%B6%E5%BC%8F%EF%BC%9A%E5%A4%A9/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>野良では『game8』『線とりたけし』の表記でマクロ流派が示されることが多い。</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m1s</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/532825</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>スプレッドネイルは T - D - H の 3 方向散開、ボス位置基準。</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m2s</t>
         </is>
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Anabaseios:_The_Eleventh_Circle_(Savage)</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>ハニー・B・ライヴ各回で「♡ハート数」によって塔位置と頭割り位置が分岐する。</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m2s</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/29231383/blog/5231433</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>アラームフェロモン 1 回目は外周蜂からの直線範囲、各人が個別にケアする。</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m2s</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>https://jp.finalfantasyxiv.com/lodestone/character/32180468/blog/5233886/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>ブラックハート後の中央集合は『早い人ペア順』。HP回復タイミングを意識する必要がある。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m2s</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AsS4R1qYbGM</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C184" s="8" t="inlineStr">
+        <is>
+          <t>野良では『お知らせマクロ』(◯◯ Rain or Drop で次に来るギミックを宣言する) も併用される。</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m3s</t>
         </is>
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>https://nukemarugames.com/2023/06/03/%E2%80%BB%E6%94%BB%E7%95%A5%E3%83%A1%E3%83%A2%E6%BA%96%E5%82%99%E4%B8%AD%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E5%A4%A9%E7%8D%84%E7%B7%A8%E9%9B%B6%E5%BC%8F3%E5%B1%A4-%E3%81%95%E3%82%89%E3%81%A3/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>4 or 8 ウェイ・ダブルラリアットは『繋がれているブルートボンバーを 1 つ受ける』のが鉄則。</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m3s</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-EM-XR6qocU</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>ボンバリアンボム 2 塔目はボス向き基準の左右なので、ボス位置確認が必須。</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m3s</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>https://neko14.com/2023/06/12/post-5861/</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>零式フューズボムは『単体長ボムを北に見る』で配置確定。短/長の判定に注意。</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m3s</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/534748</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C188" s="8" t="inlineStr">
+        <is>
+          <t>極盛り式スピニングファイヤーはアタッチ (細胞付着) ギミック。基本散開と同じ位置で受ける。</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/535668</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>円輪/輪円は『DN 式』と呼ばれる Game8 採用の位置法。動画予習必須。</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Anabaseios:_The_Twelfth_Circle_(Savage)</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>エレクトロープ 2 回目はシャインスパーク被撃回数で『多/少』が決まる。22 秒/42 秒の判定タイミングを把握する。</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/29231383/blog/5231433</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>エレクトロンストリームは『TH 外側 / DPS 内側』が基本。デバフ色で逆方向に受ける。</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>https://www.thepfstrat.com/p12s</t>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>前半のタイムラインは 0 秒〜6 分 26 秒。Game8 ページに秒単位の予兆と対応が記載されている。</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/26312</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>クロステイル・スペシャルでタンク LB3 を撃つのが標準。LB3 がない場合は壊滅リスク大。</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>https://arutora.com/26427</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>マスタードボムのデバフ受取順は MT 側と ST 側で対称。順番を覚えること。</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>ブラックサバト【日出】は塔と誘導の両方を担当する役割割振りが複雑。</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="8" t="inlineStr">
         <is>
-          <t>p9s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>https://game8.jp/ff14/532345</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B197" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Anabaseios:_The_Ninth_Circle_(Savage)</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B198" s="8" t="inlineStr">
-        <is>
-          <t>https://finalfantasy.fandom.com/wiki/Anabaseios:_The_Ninth_Circle</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B199" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/29231383/blog/5231433</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B200" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=rnKHQtYCuAk</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B201" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B202" s="8" t="inlineStr">
-        <is>
-          <t>https://next-innovation-fuk.com/2023/05/29/ff14-%E3%83%91%E3%83%83%E3%83%816-4x-%E3%80%8C%E9%9B%B6%E5%BC%8F%E3%80%8D%E4%B8%87%E9%AD%94%E6%AE%BF%E3%83%91%E3%83%B3%E3%83%87%E3%83%A2%E3%83%8B%E3%82%A6%E3%83%A0%E9%9B%B6%E5%BC%8F%EF%BC%9A%E5%A4%A9/</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B203" s="8" t="inlineStr">
-        <is>
-          <t>https://www.icy-veins.com/ffxiv/the-ninth-circle-savage-raid-guide</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B204" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/680424</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B205" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5540581/</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B206" s="8" t="inlineStr">
-        <is>
-          <t>https://www.famitsu.com/article/202505/42745</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B207" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B208" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B209" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/srm_br/n/n942f8c325c9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B210" s="8" t="inlineStr">
-        <is>
-          <t>https://nizusiro.com/ff14/cruisers1/</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B211" s="8" t="inlineStr">
-        <is>
-          <t>https://www.ersharifst.com/2025/04/07/fsaasfgew/</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B212" s="8" t="inlineStr">
-        <is>
-          <t>https://hkn-hkg2021.hatenablog.com/entry/2025/03/18/</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B213" s="8" t="inlineStr">
-        <is>
-          <t>https://www.famitsu.com/article/202503/36584</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B214" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/681086</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B215" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5540581/</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B216" s="8" t="inlineStr">
-        <is>
-          <t>https://jp.finalfantasyxiv.com/lodestone/character/11516239/blog/5542931/</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B217" s="8" t="inlineStr">
-        <is>
-          <t>https://www.famitsu.com/article/202505/42745</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B218" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B219" s="8" t="inlineStr">
-        <is>
-          <t>https://toramemoblog.com/cr2-woops</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B220" s="8" t="inlineStr">
-        <is>
-          <t>https://ff14net.2chblog.jp/archives/62265631.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B221" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/srm_br/n/n942f8c325c9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B222" s="8" t="inlineStr">
-        <is>
-          <t>https://www.ersharifst.com/2025/04/07/fsaasfgew/</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B223" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/35880736/blog/5544069/</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B224" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B225" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/681274</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B226" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/13307902/blog/5542016/</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B227" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5540581/</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B228" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/srm_br/n/n942f8c325c9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B229" s="8" t="inlineStr">
-        <is>
-          <t>https://www.famitsu.com/article/202505/42745</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B230" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B231" s="8" t="inlineStr">
-        <is>
-          <t>https://neko14.com/2025/04/24/post-10653/</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B232" s="8" t="inlineStr">
-        <is>
-          <t>https://u1f.blogspot.com/2025/05/ff14-3.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B233" s="8" t="inlineStr">
-        <is>
-          <t>https://www.ersharifst.com/2025/04/15/htxrmkhjf/</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B234" s="8" t="inlineStr">
-        <is>
-          <t>http://kanatan.info/archives/39556778.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B235" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/681843</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B237" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/681846</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B238" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5540581/</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B239" s="8" t="inlineStr">
-        <is>
-          <t>https://www.famitsu.com/article/202505/42745</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B240" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B241" s="8" t="inlineStr">
-        <is>
-          <t>https://ff14wiki.info/?%E8%87%B3%E5%A4%A9%E3%81%AE%E5%BA%A7%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%EF%BC%9A%E3%82%AF%E3%83%AB%E3%83%BC%E3%82%B6%E3%83%BC%E7%B4%9A</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B242" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/srm_br/n/n942f8c325c9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B243" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/feenal/n/n30ea48699717</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B244" s="8" t="inlineStr">
-        <is>
-          <t>https://www.ersharifst.com/2025/05/04/uogihjk/</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B245" s="8" t="inlineStr">
-        <is>
-          <t>https://closedalpha.com/ffxiv-guide/aac-cruiserweight-m8s-dps/</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B246" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/46506043/blog/5548854/</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B247" s="8" t="inlineStr">
-        <is>
-          <t>https://u1f.blogspot.com/2025/06/ff14-4.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B248" s="8" t="inlineStr">
-        <is>
-          <t>https://neko14.com/2025/05/16/post-10844/</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B249" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B250" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/755672</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B251" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/34025302/blog/5645093/</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B252" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5642585/</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B253" s="8" t="inlineStr">
-        <is>
-          <t>https://www.ersharifst.com/2026/01/14/shendv/</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B254" s="8" t="inlineStr">
-        <is>
-          <t>https://jp.finalfantasy.com/news/5854</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B255" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B256" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B257" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/755154</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B258" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/34025302/blog/5645096</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B259" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5642585/</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B260" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/liroom/n/n348fbf3a5a30</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B261" s="8" t="inlineStr">
-        <is>
-          <t>https://jp.finalfantasy.com/news/5854</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B262" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B263" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B264" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/756439</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B265" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/757988</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B266" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5642585/</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B267" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/39631700/blog/5649775/</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B268" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/22717408/blog/5651169/</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B269" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/46506043/blog/5653108/</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B270" s="8" t="inlineStr">
-        <is>
-          <t>https://nizusiro.com/ff14/heavy-raid-4s/</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B271" s="8" t="inlineStr">
-        <is>
-          <t>https://www.ersharifst.com/2026/02/08/fdsgfea/</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B272" s="8" t="inlineStr">
-        <is>
-          <t>https://jp.finalfantasy.com/news/5854</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B273" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B274" s="8" t="inlineStr">
-        <is>
-          <t>https://www.icy-veins.com/ffxiv/aac-heavyweight-m4-final-boss-savage-raid-guide</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B275" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B276" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/754895</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B277" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/34025302/blog/5645091/</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B278" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/12440293/blog/5642585/</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B279" s="8" t="inlineStr">
-        <is>
-          <t>https://jp.finalfantasy.com/news/5854</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B280" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B281" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B282" s="8" t="inlineStr">
-        <is>
-          <t>https://next-innovation-fuk.com/2026/01/06/ff14-%E3%83%91%E3%83%83%E3%83%817-4-%E8%87%B3%E5%A4%A9%E3%81%AE%E5%BA%A7%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F/</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B283" s="8" t="inlineStr">
-        <is>
-          <t>https://asellog.com/il776-788/</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B284" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/630292</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B285" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/26820312/blog/5431856/</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B286" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/lastagous/n/ncfcb027117fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B287" s="8" t="inlineStr">
-        <is>
-          <t>https://www.famitsu.com/article/202505/42743</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B288" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/AAC_Light-heavyweight_M1_(Savage)</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B289" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B290" s="8" t="inlineStr">
-        <is>
-          <t>https://nukemarugames.com/2024/07/31/%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A%E9%9B%B6-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B291" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B292" s="8" t="inlineStr">
-        <is>
-          <t>https://next-innovation-fuk.com/2024/07/16/ff14-7-01-%E8%87%B3%E5%A4%A9%E3%81%AE%E5%BA%A7%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A-%E9%96%8B%E6%94%BE/</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B293" s="8" t="inlineStr">
-        <is>
-          <t>https://gutsdawn.com/2024/08/13/%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8Flh%E7%B4%9A%EF%BC%91%E5%B1%A4/ff14/</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B294" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/630353</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B295" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/26820312/blog/5431856/</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B296" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/lastagous/n/ncfcb027117fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B297" s="8" t="inlineStr">
-        <is>
-          <t>https://www.famitsu.com/article/202505/42743</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B298" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B299" s="8" t="inlineStr">
-        <is>
-          <t>https://nukemarugames.com/2024/07/31/%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A%E9%9B%B6/</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B300" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B301" s="8" t="inlineStr">
-        <is>
-          <t>https://gutsdawn.com/2024/08/18/%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8Flh%E7%B4%9A%EF%BC%92%E5%B1%A4/ff14/</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B302" s="8" t="inlineStr">
-        <is>
-          <t>https://neko14.com/2024/08/04/post-8662/</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B303" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/630870</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B304" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/26820312/blog/5431856/</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B305" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/lastagous/n/ncfcb027117fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B306" s="8" t="inlineStr">
-        <is>
-          <t>https://www.famitsu.com/article/202505/42743</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B307" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B308" s="8" t="inlineStr">
-        <is>
-          <t>https://nukemarugames.com/2024/08/01/%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A%E9%9B%B6-3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B309" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B310" s="8" t="inlineStr">
-        <is>
-          <t>https://neko14.com/2024/08/10/post-8721/</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B311" s="8" t="inlineStr">
-        <is>
-          <t>https://www.sunny-stronger.com/entry/2024/08/02/120726</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B312" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/631136</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B313" s="8" t="inlineStr">
-        <is>
-          <t>https://game8.jp/ff14/631340</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B314" s="8" t="inlineStr">
-        <is>
-          <t>https://na.finalfantasyxiv.com/lodestone/character/26820312/blog/5431856/</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B315" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/lastagous/n/ncfcb027117fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B316" s="8" t="inlineStr">
-        <is>
-          <t>https://www.famitsu.com/article/202505/42743</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B317" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/The_Arcadion</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B318" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B319" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/mokatamk/n/n92368fe90e97</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B320" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/feenal/n/nb25383cb791d</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B321" s="8" t="inlineStr">
-        <is>
-          <t>https://gutsdawn.com/2024/09/20/%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8Flh%E7%B4%9A%EF%BC%94%E5%B1%A4%E5%89%8D%E5%8D%8A/ff14/</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B322" s="8" t="inlineStr">
-        <is>
-          <t>https://gutsdawn.com/2024/09/20/%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8Flh%E7%B4%9A%EF%BC%94%E5%B1%A4%E5%BE%8C%E5%8D%8A/ff14/</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B323" s="8" t="inlineStr">
-        <is>
-          <t>https://neko14.com/2024/08/25/post-8845/</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B324" s="8" t="inlineStr">
-        <is>
-          <t>https://jp.finalfantasyxiv.com/lodestone/character/34120564/blog/5500375/</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B325" s="8" t="inlineStr">
-        <is>
-          <t>https://fuucdayo.com/battle/6772/</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="8" t="inlineStr">
-        <is>
-          <t>dmu</t>
-        </is>
-      </c>
-      <c r="B326" s="8" t="inlineStr">
-        <is>
-          <t>https://ffxiv.consolegameswiki.com/wiki/Dancing_Mad_(Ultimate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="8" t="inlineStr">
-        <is>
-          <t>dmu</t>
-        </is>
-      </c>
-      <c r="B327" s="8" t="inlineStr">
-        <is>
-          <t>https://www.icy-veins.com/ffxiv/dancing-mad-ultimate-guide-and-overview</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="8" t="inlineStr">
-        <is>
-          <t>dmu</t>
-        </is>
-      </c>
-      <c r="B328" s="8" t="inlineStr">
-        <is>
-          <t>https://www.shacknews.com/article/148845/final-fantasy-14-online-kefka-raid</t>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C196" s="8" t="inlineStr">
+        <is>
+          <t>剣の舞 (時間切れ) 前の DPS チェックがソフト時間切れになる傾向。</t>
         </is>
       </c>
     </row>

--- a/data/sheet-export/ff14-contents-template.xlsx
+++ b/data/sheet-export/ff14-contents-template.xlsx
@@ -1985,12 +1985,11 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">開幕フェーズ。
+          <t>開幕フェーズ。
 主要ギミック: 拘束具 (Liquid Hell)、神鳥の魔印 (Magnetism)、Plummet、
 Conflag Strike、Twister (DPSチェック前の即死誘発)、Death Sentence (TB)、
 磁力 (引き寄せ/反発の◯×振り分け)、第7霊災 (Hatch + Liquid Hell)。
-野良主流は「新みんとっと / H3構成 / 拘束具逆▽ (3 つの拘束具を逆三角形配置)」。
-</t>
+野良主流は「新みんとっと / H3構成 / 拘束具逆▽ (3 つの拘束具を逆三角形配置)」。</t>
         </is>
       </c>
     </row>
@@ -2022,14 +2021,13 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">引用詠唱 (Quote) に応じて配置を変える「コール戦」フェーズ。
+          <t>引用詠唱 (Quote) に応じて配置を変える「コール戦」フェーズ。
 主要ギミック: サンダーストラック (青雷)、レイヴンダイブ (TB)、
 バハムートクロウ、ラヴァディープ (赤デバフ)、ハイパーノヴァ (氷)、
 カータライズ (Cauterize / 直線ダイブ)、ヘヴンスフォール、
 メテオストリーム、メテオ (ドラゴン add)、フィエリディスパッチ (頭割り)、
 ダブルアスペクト (二重デバフ詠唱)。
-野良主流は「新みんとっと / カータTLB (カータライズで タンクLB3 を発動)」。
-</t>
+野良主流は「新みんとっと / カータTLB (カータライズで タンクLB3 を発動)」。</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2059,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最長フェーズ。プライム / ネール / ツインタニアの 3 体が「三重奏 (Trio)」として
+          <t>最長フェーズ。プライム / ネール / ツインタニアの 3 体が「三重奏 (Trio)」として
 同時にギミックを行う。Trio 構成 (野良主流呼称):
   1. 進軍の三重奏 (Quickmarch Trio)   ← 進軍十字
   2. 黒炎の三重奏 (Blackfire Trio)
@@ -2071,8 +2069,7 @@
   6. 群竜の八重奏 (Grand Octet)        ← 群竜TLB
 主要ギミック: メガフレア、Twister、アースシェイカー、Liquid Hell、
 タワー処理、フレア (Flatten)、Hypernova、Dive、ドラゴン add 制御。
-野良主流は「新みんとっと / 進軍十字 / 連撃V字 / 群竜TLB」。
-</t>
+野良主流は「新みんとっと / 進軍十字 / 連撃V字 / 群竜TLB」。</t>
         </is>
       </c>
     </row>
@@ -2100,13 +2097,12 @@
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ツインタニアとネールの 2 体フェーズ (Trinity)。
+          <t>ツインタニアとネールの 2 体フェーズ (Trinity)。
 P1 と P2 のギミックが同時進行する短いフェーズ。
 主要ギミック: 拘束具 (Liquid Hell)、Twister、Death Sentence、
 サンダーストラック (青雷)、レイヴンダイブ、ラヴァディープ、
 ハイパーノヴァ、Doom デバフ、Earthshaker。
-HP 同期処理 (2 体の HP を揃えて削る) が必須。
-</t>
+HP 同期処理 (2 体の HP を揃えて削る) が必須。</t>
         </is>
       </c>
     </row>
@@ -2138,14 +2134,13 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最終フェーズ。Golden Bahamut Prime (金色のバハムート) が登場する DPS チェック。
+          <t>最終フェーズ。Golden Bahamut Prime (金色のバハムート) が登場する DPS チェック。
 主要ギミック: メガフレア (リミットカット連続)、
 ギガフレア (DPS チェック頭割り)、テラフレア (時間切れ)、
 エクサフレア (移動型 AoE、8 方向ランダム)、
 モーン・アファー (Morn Afar / 大ダメージ範囲、ボス足元集合)、
 アク・モーン (Akh Morn / 3〜6 連続範囲ダメージ、敵視 1 位)。
-野良主流は「ボス足元集合のスタック処理 + アク・モーン 無敵切替」。
-</t>
+野良主流は「ボス足元集合のスタック処理 + アク・モーン 無敵切替」。</t>
         </is>
       </c>
     </row>
@@ -2170,18 +2165,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>ドーム処理(低気圧)</t>
-        </is>
-      </c>
+      <c r="E7" s="8" t="inlineStr"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">開幕フェーズ。スリップストリーム、ミストラルソング、フェザーレイン、サーマルロウ、
-メソハイ、ウィキッドウィール、ウィキッドトルネード、低気圧(ドーム処理)など。
-所要時間 約2分43秒。
-野良主流は「ドーム処理(低気圧)」+「メソハイMTキャス」+「インシネレート1回目ST/2回目MT」。
-</t>
+          <t>スリップストリーム、ミストラルソング、フェザーレイン、メソハイ、低気圧(ドーム処理)など。
+野良主流は「ドーム処理(低気圧)」+「メソハイMTキャス」</t>
         </is>
       </c>
     </row>
@@ -2213,10 +2201,9 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">クリムゾンサイクロン、レイディアントプルーム、エラプション、炎獄の楔、灼熱の咆哮など。
-所要時間 約2分37秒。
-野良主流は「楔:逆Z」処理。①D1 ②D2 ③D3 ④D4 の順で楔を破壊。
-</t>
+          <t>クリムゾンサイクロン、エラプション、炎獄の楔、灼熱の咆哮など。
+「インシネレート1回目ST/2回目MT」。
+野良主流は「楔:逆Z」処理。①D1 ②D2 ③D3 ④D4 の順で楔を破壊。</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2220,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>P3 タイタン + アルテマ履行LB (Titan + Limit Break Phase)</t>
+          <t>P3 タイタン + アルテマ履行LB</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -2248,13 +2235,10 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ジオクラッシュ、ロックバスター、マウンテンバスター、大地の重み、ランドスライド、
-グラナイトジェイル、タムルトなど。タイタン討伐後、ヘイブンスインビョクスから
+          <t>大地の重み、ランドスライド、グラナイトジェイル。
 アルテマ履行(LB3)フェーズへ繋がる。
-所要時間 約4分27秒 (タイタン本体)。
 野良主流は「ジェイル自滅式 (重み2回目で ST/メレー/レンジが被弾死)」+
-「マウンテンバスター 1回目 MT / 2回目 ST(かばう) / 3回目 MT」。
-</t>
+「マウンテンバスター 1回目 MT / 2回目 ST(かばう) / 3回目 MT」。</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2255,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>P4 追撃の究極幻想 (Annihilation - Predation)</t>
+          <t>P4 追撃の究極幻想</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -2286,10 +2270,9 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">アルテマウェポン本体フェーズの前半。誘導レーザー(吸着爆雷)、激震、
-フェザーレイン、ジェイル、十字範囲など。所要時間 約1分38秒。
-野良主流は「十字無視法」(十字範囲を安置判定で無視して位置取り)。
-</t>
+          <t>アルテマウェポン本体フェーズの前半。
+誘導レーザー(吸着爆雷)、激震、フェザーレイン、ジェイル、十字範囲など。
+野良主流は「十字無視法」(十字範囲を安置判定で無視して位置取り)。</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2289,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>P5 爆撃の究極幻想 (Annihilation - Bombardment)</t>
+          <t>P5 爆撃の究極幻想</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -2321,10 +2304,9 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">アルテマウェポン本体フェーズの中盤。緑玉(エメラルドレディアンス)、
-ノックバック、メソハイ、灼熱など。所要時間 約58秒。
-野良主流は「3111 (緑玉3-1-1-1配分)」処理。
-</t>
+          <t>アルテマウェポン本体フェーズの中盤。
+緑玉、メソハイ、灼熱など。
+野良主流は「3111 (緑玉3-1-1-1配分)」処理。</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2323,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>P6 乱撃+最終三蛮神 (Annihilation - Final + Primal Roulette)</t>
+          <t>P6 乱撃+最終三蛮神</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -2356,12 +2338,10 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">アルテマウェポン本体フェーズの終盤。乱撃 (タンクLB3 ※顔面受け)、
-アルテマ詠唱、エーテル波動、紫玉(パープルレディアンス)、そして
-最終三蛮神ルーレット (ガルーダ/イフリート/タイタン のランダム順序処理) で締める。
-所要時間 約2分28秒。
-野良主流は「乱撃TLB (タンクLB3顔面受け)」+「紫玉 4 隅散開」。
-</t>
+          <t>アルテマウェポン本体フェーズの終盤。乱撃 (タンクLB3 ※顔面受け)、
+アルテマ詠唱、エーテル波動、紫玉、そして
+最終三蛮神ルーレット (ガルーダ/イフリート/タイタン のランダム順序処理) 。
+野良主流は「乱撃TLB (タンクLB3顔面受け)」+「紫玉 4 隅散開」。</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2373,10 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">開幕フェーズ。リビングリキッド (本体) と頭手 (Liquid Hand / Hand of Prayer/Parting) を相手取る。
-主要ギミック: プロティアンウェイブ、ハンドオブペイン、ジャグドール、ドレナージ、
-圧壊 (Pressurize/Embolus)、スプラッシュ、スルース、サイコロ (Throttle - 1/2/3/4 番号デバフ)。
+          <t>リビングリキッド (本体) とハンドを相手取る。
+主要ギミック: プロティアンウェイブ、ハンドオブペイン、サイコロ。
 野良主流は「ヤークト無視 (20秒バースト) + サイコロ 1211」。
-時間切れ 2分20秒だがヤークト無視では 1分9秒以内に本体だけ削り切る。
-</t>
+時間切れ 2分20秒だがヤークト無視では 1分9秒以内に本体だけ削り切る。</t>
         </is>
       </c>
     </row>
@@ -2425,18 +2403,16 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>ヒラ先 (Healer-priority Nisi渡し) + サイコロ番号配置</t>
+          <t>ヒラ先</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ジャスティス＋チェイサーの2体フェーズ。間に Limit Cut (アルファソード / スーパーブラスティチャージ /
-ホークブラスター) を挟む。
+          <t>ジャスティス＋チェイサーの2体フェーズ。
 主要ギミック: 初期散開チャクラム、雷・水圧縮 (1〜3回目)、ミサイル全弾発射、
-カウント・地雷処理、ナイサイ (Judgment Nisi)、最後の審判 (開廷/結審)、
-ロケットパンチ&amp;スーパージャンプ、Verdict (時間切れ)。
-野良主流は「ヒラ先 (Healer-priority Nisi渡し) + サイコロ番号配置」。
-</t>
+カウント・地雷処理、ナイサイ 、最後の審判 (開廷/結審)、
+ロケットパンチ&amp;スーパージャンプ。
+野良主流は「ヒラ先渡し」。</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2439,14 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>ぬけまる/ハムカツ式 34固定 + 時間停止 脳死法</t>
+          <t>ハムカツ式 34固定 + 時間停止 脳死法</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">アレキサンダー・プライム単体の準ラスフェーズ。
-主要ギミック: チャステイニングヒート (Chastening Heat / TB)、ディヴァインスピア、
-メガホーリー、時間停止 (Temporal Stasis)、時空潜航のマーチ (Inception)、
-次元断絶のマーチ (Wormhole)、サモン・アレキサンダー (Summon Alexander)。
-野良主流は「ぬけまる/ハムカツ式 34固定 + 時間停止 脳死法」。
-</t>
+          <t>アレキサンダー・プライム単体の準ラスフェーズ。
+主要ギミック: 時間停止、時空潜航のマーチ 、次元断絶のマーチ。
+野良主流は「ハムカツ式 34固定 + 時間停止 脳死法」。</t>
         </is>
       </c>
     </row>
@@ -2498,20 +2471,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 + 未来観測 北/南頭割り</t>
-        </is>
-      </c>
+      <c r="E16" s="8" t="inlineStr"/>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最終フェーズ。3体融合したパーフェクト・アレキサンダー。
-主要ギミック: 確定判決 (The Final Word)、運命の輪 (Ordained Motion / Stillness)、
-光学式波動砲 (Optical Sight)、聖なる大審判 (Almighty Judgment)、
-未来観測 α/β (Fate Calibration α/β)、時空干渉 (Temporal Prison)、
-抑圧の懲罰 (Ordained Capital Punishment)、強制的引力 (Irresistible Grace)。
-野良主流は「ぬけまる式 + 未来観測 北/南頭割り」。
-</t>
+          <t>最終フェーズ。3体融合したパーフェクト・アレキサンダー。
+主要ギミック: 確定判決 、未来観測 α/β</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2503,7 @@
       <c r="E17" s="8" t="inlineStr"/>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ボス完結型。鎖と監獄の魔王によるギミック。
+          <t>1 ボス完結型。鎖と監獄の魔王によるギミック。
 主要ギミック:
   - 氷火の侵食 (Shining Cells)         属性ヒット数管理、調整役 MT/D3
   - 結呪の魔鎖 (Aetherchain)           ペア結呪。MTD4 / H2D2 / STD1 / H1D3 が標準
@@ -2547,8 +2511,7 @@
   - 時限の魔鎖 (Heavy Hand)            対象者デバフ → 光/火振分け
   - 罪のフレイル (Pitiless Flail)      鎖の振り回し AoE
   - シャックル・オブ・タイム            時間停止デバフ
-野良主流: ペア調整 / 氷火 MT・D3 交代式 (Game8 採用)。
-</t>
+野良主流: ペア調整 / 氷火 MT・D3 交代式 (Game8 採用)。</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2539,7 @@
       <c r="E18" s="8" t="inlineStr"/>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ボス完結型。水の創造生物ヒッポカムポスによる頭割り＋ノックバック特化フェーズ。
+          <t>1 ボス完結型。水の創造生物ヒッポカムポスによる頭割り＋ノックバック特化フェーズ。
 主要ギミック:
   - ショックウェーブ (頭割り、ボス下 vs 通路に分散)
   - チャネリングフロウ (十字形 KB)         TH/DPS 交差配置
@@ -2585,8 +2548,7 @@
   - ダブルインパクト (タンクペア頭割り)
   - ブレス＆カタラクティス (頭/胴分離)
   - マーキーディープ (全体)
-野良主流: Game8 ペア基本散開 + ボス下/通路分散頭割り。
-</t>
+野良主流: Game8 ペア基本散開 + ボス下/通路分散頭割り。</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2576,7 @@
       <c r="E19" s="8" t="inlineStr"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">フェニックス前半フェーズ。鳥雑魚 + 闇の炎 + 突進 + 線取り。
+          <t>フェニックス前半フェーズ。鳥雑魚 + 闇の炎 + 突進 + 線取り。
 主要技:
   - 4:4 分け (雑魚 / 霊泉)            MT 組 = MTH1D1D3, ST 組 = STH2D2D4
   - 闇の炎設置ペア (X 字)            サイコロ数字マーカー、時計回り処理
@@ -2622,8 +2584,7 @@
   - 突進 (中央散開 / 左右散開)       ボスから T → H → D の順
   - 雑魚誘導                          MT 組: 北→西 / ST 組: 東→南
   - 雑魚突進 (線 2 本 / 線 1 本)
-野良主流: Game8 採用「基本犬丸＋闇の炎X字 (しのしょー)＋霊泉ハピおじ」式。
-</t>
+野良主流: Game8 採用「基本犬丸＋闇の炎X字 (しのしょー)＋霊泉ハピおじ」式。</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2612,7 @@
       <c r="E20" s="8" t="inlineStr"/>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">後半フェーズ。魔力錬成 (闇)、霊泉フェーズ、辺獄シリーズ。
+          <t>後半フェーズ。魔力錬成 (闇)、霊泉フェーズ、辺獄シリーズ。
 主要技:
   - 魔力錬成・闇 (辺獄の炎嵐以外)     近接組北 / 遠隔組南
   - 霊泉フェーズ (ハピおじ式)         塔踏み AoE 時計回り
@@ -2660,8 +2621,7 @@
   - 黒玉散開 (赤小玉→黒小玉 / 赤大玉→黒小玉)
   - 辺獄中ピザカット避け              3 番目待機 → 1 番目退避
   - 辺獄中ノックバック後散開
-野良主流: 同上 Game8 採用 融合版。
-</t>
+野良主流: 同上 Game8 採用 融合版。</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2649,7 @@
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 1 (前半)。ピナクス・毒線・緑玉ギミック中心。
+          <t>Part 1 (前半)。ピナクス・毒線・緑玉ギミック中心。
 主要技:
   - 基本散開                          標準 8 人散開
   - 毒線 (YPP 式)                     TH 北 / DPS 南、塔線時計回り (線ぐるぐる)
@@ -2698,8 +2658,7 @@
   - 緑玉脳死 (十字配置)               MTH2 / STH1 → D3D4 / D1D3 → MT / D2D4 → H1
                                       上記の玉を取って時計回りで処理
 野良主流: YPP 式 (毒線 YPP 緑玉脳死) - Game8 採用。
-DPS チェック前層比厳しめのため、装備 / 食事 / 薬使用 (最大 2 回) 必須。
-</t>
+DPS チェック前層比厳しめのため、装備 / 食事 / 薬使用 (最大 2 回) 必須。</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2686,7 @@
       <c r="E22" s="8" t="inlineStr"/>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 2 (後半)。序幕 → 第二幕 → 第三幕 → 第四幕 → 終幕 → カーテンコールの
+          <t>Part 2 (後半)。序幕 → 第二幕 → 第三幕 → 第四幕 → 終幕 → カーテンコールの
 「劇」演出形式で進行。最終ギミック「カーテンコール」が時間切れ判定。
 主要技:
   - 序幕                              標準散開
@@ -2736,8 +2695,7 @@
   - 第四幕                            ウォタガ + ダージャ 塔処理、南西集合 → 時計回り
   - 終幕                              ボス基準散開 + 塔配置
   - カーテンコール                    TH 6 秒 / D 11 秒で切り (13/23/33/43)
-野良主流: 犬丸式 (および、ぬけまる式も Game8 で並列掲載)。
-</t>
+野良主流: 犬丸式 (および、ぬけまる式も Game8 で並列掲載)。</t>
         </is>
       </c>
     </row>
@@ -2769,11 +2727,10 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">開幕フェーズ。蒼天騎士団3名（聖騎士アデルフェル / グリノー / シャリベル）と戦う。
+          <t>開幕フェーズ。蒼天騎士団3名（聖騎士アデルフェル / グリノー / シャリベル）と戦う。
 ハイパーディメンション、プレステ散開（◯×△□マーカー）、光翼閃、
 ホーリーブレードダンス（線処理）、ホリエストブレッシング（沈黙）など。
-野良主流は「MTアデル / STグリノー / 線ST無敵 / 沈黙 MT→レンジ→MT」。
-</t>
+野良主流は「MTアデル / STグリノー / 線ST無敵 / 沈黙 MT→レンジ→MT」。</t>
         </is>
       </c>
     </row>
@@ -2805,11 +2762,10 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷槍、聖杖、隕石（ホーリーコメット）など。
+          <t>雷槍、聖杖、隕石（ホーリーコメット）など。
 野良主流は「ゼフィラン基準散開 / 隕石ハムカツ式」。
 雷槍はスパイラルスラスト＋百雷、聖杖はゼフィラン基準でペア調整（MTST/H1H2/D1D2/D3D4）。
-隕石GGパターンは多くの固定で「詰みパターンとして諦める」とされる。
-</t>
+隕石GGパターンは多くの固定で「詰みパターンとして諦める」とされる。</t>
         </is>
       </c>
     </row>
@@ -2841,10 +2797,9 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイコロ（堕天のドラゴンダイブ）、4塔（ジオーガとゲイルスコグル）、
+          <t>サイコロ（堕天のドラゴンダイブ）、4塔（ジオーガとゲイルスコグル）、
 ソウルテザー、アイ・オブ・タイラント、牙尾/尾牙の連旋などのギミック。
-野良主流は「①②③ イル↓D・スパ↑B 固定 / 4塔近接調整」。
-</t>
+野良主流は「①②③ イル↓D・スパ↑B 固定 / 4塔近接調整」。</t>
         </is>
       </c>
     </row>
@@ -2876,12 +2831,11 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">邪竜の目（左眼 / 右眼）を破壊する短いフェーズ。
+          <t>邪竜の目（左眼 / 右眼）を破壊する短いフェーズ。
 赤線/青線の交換による眼への攻撃、ミラージュダイブ（複数回の円形範囲）など。
 野良主流は「近接青眼寄せ / ミラージュダイブ交代固定」。
 ※ARUTORA 等の 8 段階構成では P5「教皇庁②（タンクLB / 光翼閃②）」を独立フェーズとして
-扱うが、本ファイルは P1〜P7 構成のため、教皇庁② を P4 の後半（P4-2）として含む。
-</t>
+扱うが、本ファイルは P1〜P7 構成のため、教皇庁② を P4 の後半（P4-2）として含む。</t>
         </is>
       </c>
     </row>
@@ -2913,11 +2867,10 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">偽典トールダン戦。「至天の陣:風槍」と「至天の陣:死刻」の 2 大ギミック。
+          <t>偽典トールダン戦。「至天の陣:風槍」と「至天の陣:死刻」の 2 大ギミック。
 死刻は絶竜詩最大の山場とも言われる複雑なギミックで、
 死の宣告デバフ + ツイスター + ヘヴィインパクトを直線移動で処理する。
-野良主流は「こまぞう式改」（イディル式 + こまぞう式のハイブリッド）。
-</t>
+野良主流は「こまぞう式改」（イディル式 + こまぞう式のハイブリッド）。</t>
         </is>
       </c>
     </row>
@@ -2949,11 +2902,10 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ニーズヘッグ（D側）とフレースヴェルグ（B側）の 2 体戦。
+          <t>ニーズヘッグ（D側）とフレースヴェルグ（B側）の 2 体戦。
 聖竜/邪竜の息吹（線処理）、滅殺の誓い（DPS リレー）、
 アク・アファー（ヒラ起点頭割り）、邪念の炎、カータライズなどのギミック。
-野良主流は「おこめ式息吹1 / 脳死息吹2 / 南三角」。
-</t>
+野良主流は「おこめ式息吹1 / 脳死息吹2 / 南三角」。</t>
         </is>
       </c>
     </row>
@@ -2985,11 +2937,10 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最終フェーズ。騎竜剣エクサフレア、トリニティ（オートアタック）、
+          <t>最終フェーズ。騎竜剣エクサフレア、トリニティ（オートアタック）、
 騎竜剣アク・モーン、騎竜剣ギガフレア、騎竜剣モーン・アファー（時間切れ攻撃）の連続。
 「エクサ→アクモーン→ギガフレア」のサイクルを 3 週繰り返して時間切れに到達する設計。
-野良主流は「アクモーン2回目 TLB3」処理。
-</t>
+野良主流は「アクモーン2回目 TLB3」処理。</t>
         </is>
       </c>
     </row>
@@ -3017,7 +2968,7 @@
       <c r="E30" s="8" t="inlineStr"/>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ライオン型「創造の継承者」プロトカーバンクル戦。1ボス完結型。
+          <t>ライオン型「創造の継承者」プロトカーバンクル戦。1ボス完結型。
 主要ギミック:
   - ソニックハウル (全体攻撃 + ノックバック)
   - ベノムマス / ベノムクランチ (タンク強攻撃、スワップ運用)
@@ -3030,8 +2981,7 @@
   - 捕食 (Starving Stampede / 8青マーカーの順次飛び、スタン→捕食)
   - 十字毒沼 (十字配置の毒沼、塔踏み)
   - ベノムスプラッシュ (4部屋の3個部屋から対角逃げ)
-野良主流: ぬけまる式 (Game8 採用)。
-</t>
+野良主流: ぬけまる式 (Game8 採用)。</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3009,7 @@
       <c r="E31" s="8" t="inlineStr"/>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">白蛇人型「半神の継承者」ヘーゲモネ戦。1ボス完結型。
+          <t>白蛇人型「半神の継承者」ヘーゲモネ戦。1ボス完結型。
 主要ギミック:
   - ヘーミテオス・ダージャ (Hemitheos's Dark IV、開幕全体)
   - ケリックシナジー (Chelic Synergy、タンク強攻撃)
@@ -3071,8 +3021,7 @@
   - ダークホーリー / ダークドーム / ダークアッシュ (各種闇属性技)
   - エクソークリーバー (Exocleaver)
   - カヘキシー (Cachexia、全2回、複合ギミック)
-野良主流: ぬけまる式 (Game8 採用)、流派分岐少なめ。
-</t>
+野良主流: ぬけまる式 (Game8 採用)、流派分岐少なめ。</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3049,7 @@
       <c r="E32" s="8" t="inlineStr"/>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">巨大樹「半神の継承者」アグディスティス戦。1ボス完結型、アド管理が肝。
+          <t>巨大樹「半神の継承者」アグディスティス戦。1ボス完結型、アド管理が肝。
 主要ギミック:
   - アッティスの刃葉 (エクサフレア、外周連続AoE)
   - ホーリガ + 鳥突進 (ノックバック + 鳥誘導)
@@ -3114,8 +3063,7 @@
   - 多重操炎 / 多重操心 (寄生・呪詛系デバフ)
   - 不可侵の絆 / 不可侵の浄罪 (Inviolate Bonds/Purgation、ペア/散開)
   - 神鳥/牛/イオ召喚 (Forbidden Fruit のサブパターン)
-野良主流: ぬけまる式 (Game8 採用、獄8人 凶無敵 乱犬丸)。
-</t>
+野良主流: ぬけまる式 (Game8 採用、獄8人 凶無敵 乱犬丸)。</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3091,7 @@
       <c r="E33" s="8" t="inlineStr"/>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 1 (前半)。ヘファイストス第1形態。創獣 (ケンタウロス/蛇) ギミックがメイン。
+          <t>Part 1 (前半)。ヘファイストス第1形態。創獣 (ケンタウロス/蛇) ギミックがメイン。
 主要技:
   - 創獣炎舞 / 炎蛇砲 (ケンタウロス炎攻撃 / 蛇形態のビーム)
   - 熾炎創火 (Genesis of Flame、全体大ダメージ)
@@ -3155,8 +3103,7 @@
   - 多重操炎 / 四重炎嵐 (Quadrupedal Crush、4連 AoE)
   - ブレイジングフィート (Blazing Footfalls、形態変身演出)
   - テトラ/ディフレア (Tetraflare/Difflare、複数頭割り)
-野良主流: ぬけまる式 (Game8 採用、FFO式)。
-</t>
+野良主流: ぬけまる式 (Game8 採用、FFO式)。</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3131,7 @@
       <c r="E34" s="8" t="inlineStr"/>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 2 (後半)。第2形態ヘファイストス。概念ギミック (High Concept) がメイン。
+          <t>Part 2 (後半)。第2形態ヘファイストス。概念ギミック (High Concept) がメイン。
 最終的に「万象灰燼」(Ego Death) を生存するため、概念デバフ合成 (Immortal Conception)
 が必要。煉獄編最大の山場。
 主要技:
@@ -3197,8 +3144,7 @@
   - 自概念崩壊 (Self-Concept Collapse、デバフ分解)
   - エイオンアゴニア (Aionagonia、全体大ダメージ)
   - 暴君の一撃 / 支配者の一撃 (Tyrant's Grasp、タンク無敵級)
-野良主流: ぬけまる式 (Game8 採用、はいじあ式 / ビジョン式)。
-</t>
+野良主流: ぬけまる式 (Game8 採用、はいじあ式 / ビジョン式)。</t>
         </is>
       </c>
     </row>
@@ -3225,17 +3171,16 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">南集合・北11.5時から時計回り (H1MTSTD1D2D3D4H2) </t>
+          <t>南集合・北11.5時から時計回り (H1MTSTD1D2D3D4H2)</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">開幕フェーズ。ビートル形態のオメガ。
+          <t>開幕フェーズ。ビートル形態のオメガ。
 主要ギミック: サークルプログラム (塔踏み・線とり・線捨て)、
 パントクラトル (ミサイル/頭割り)、波動砲 (T無敵 / 7方向散開)、
 Atomic Ray (時間切れ)。
-野良主流は「南集合・北11.5時から時計回り (H1MTSTD1D2D3D4H2) 」。
-</t>
+野良主流は「南集合・北11.5時から時計回り (H1MTSTD1D2D3D4H2) 」。</t>
         </is>
       </c>
     </row>
@@ -3267,12 +3212,11 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">男女形態フェーズ。
+          <t>男女形態フェーズ。
 主要ギミック: ファイアウォール、連携プログラム (PT / LB)、
 プレイステーション (ミドル/ファー)、4:4吹き飛ばし、
 シールドバッシュ&amp;フレア、Laser Shower (時間切れ)。
-野良主流は「下から調整・男三人基準で左右組振り分け」。
-</t>
+野良主流は「下から調整・男三人基準で左右組振り分け」。</t>
         </is>
       </c>
     </row>
@@ -3299,16 +3243,15 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">優先TDH (検知式波動砲) / ファー→ニアー線渡し (ハロワ) </t>
+          <t>優先TDH (検知式波動砲) / ファー→ニアー線渡し (ハロワ)</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化版オメガ単体フェーズ。
+          <t>強化版オメガ単体フェーズ。
 主要ギミック: コロッサスブロー、ハローワールド (Hello, World)、
 検知式波動砲 (Oversampled Wave Cannon)、Ion Efflux (時間切れ)。
-野良主流は「優先TDH (検知式波動砲) / ファー→ニアー線渡し (ハロワ) 」。
-</t>
+野良主流は「優先TDH (検知式波動砲) / ファー→ニアー線渡し (ハロワ) 」。</t>
         </is>
       </c>
     </row>
@@ -3340,11 +3283,10 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ダメージを受けた状態のオメガ。
+          <t>ダメージを受けた状態のオメガ。
 主要ギミック: 波動砲 (3 iterations)、Wave Repeater、
 ブルースクリーン (DPSチェック付き時間切れ)。
-野良主流は「下調整・D1D2人数調整」のシンプル散開。
-</t>
+野良主流は「下調整・D1D2人数調整」のシンプル散開。</t>
         </is>
       </c>
     </row>
@@ -3376,13 +3318,12 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">オメガM/オメガFの2体ディナミスフェーズ。
+          <t>オメガM/オメガFの2体ディナミスフェーズ。
 コード「＊＊＊ミ＊」の3パターン (デルタ / シグマ / オメガ) を順次処理。
 ロケパン、アーム&amp;バッシュ誘導、ハロワ散開、塔踏み、
 Solar Ray (タンクバスター)、Quickening Dynamis スタック蓄積、
 Blind Faith (時間切れ) を含む。
-野良主流は「デルタ：ハムカツ式 / シグマ：りょんめ式 (塔Wingwan) / オメガ：ぬけまる式」。
-</t>
+野良主流は「デルタ：ハムカツ式 / シグマ：りょんめ式 (塔Wingwan) / オメガ：ぬけまる式」。</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3351,11 @@
       <c r="E40" s="8" t="inlineStr"/>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最終フェーズ。Quickening Dynamis スタック3個必須。
+          <t>最終フェーズ。Quickening Dynamis スタック3個必須。
 主要ギミック: コスモメモリー (タンクLB3)、フラッシュゲイル、
 コスモアロー、コスモダイブ、Unlimited Wave Cannon (リミッターカット)、
 波動砲、コスモメテオ (DPS LB必要)、マジックナンバー (タンク&amp;ヒーラーLB)。
-時間切れ Run: ◆◆◆◆mi◆。
-</t>
+時間切れ Run: ◆◆◆◆mi◆。</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3383,7 @@
       <c r="E41" s="8" t="inlineStr"/>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">パンデモニウム戦。1ボス完結型。クモ・ウェブ系のギミックがメイン。
+          <t>パンデモニウム戦。1ボス完結型。クモ・ウェブ系のギミックがメイン。
 主要技:
   - ディバイドウィング + ヘビーウェブ (1回目)
   - 尖脚 + グランドウェブ + パンデモニックピラー
@@ -3453,8 +3393,7 @@
   - パンデモニックレイ
   - ディバイドプルーム
   - 魔殿の震撃 (タッチダウン時は西島集合)
-野良主流: 犬丸改FFO式 (Game8 採用)、補足としてぬけまる様の震撃ボンドマクロ併用。
-</t>
+野良主流: 犬丸改FFO式 (Game8 採用)、補足としてぬけまる様の震撃ボンドマクロ併用。</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3421,7 @@
       <c r="E42" s="8" t="inlineStr"/>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">テミス戦。1ボス完結型。光と闇の対比、魔法陣・戒律など秩序系ギミックがメイン。
+          <t>テミス戦。1ボス完結型。光と闇の対比、魔法陣・戒律など秩序系ギミックがメイン。
 主要技:
   - ジューリー・オーバールール (光/闇属性判定)
   - アップヘルド・オーバールール (十字 or X字)
@@ -3494,8 +3433,7 @@
   - ダークストリーム
   - 理法の幻想 (闇線中央 / 光線その場)
   - ステュクス (5〜8連、フィニッシュ)
-野良主流: ハムカツ様準拠 + 光と闇の調停はジジー式 (Game8 採用)。
-</t>
+野良主流: ハムカツ様準拠 + 光と闇の調停はジジー式 (Game8 採用)。</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3461,7 @@
       <c r="E43" s="8" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 1 (前半)。「アテナ」戦。パラデイグマ系のギミックが軸。
+          <t>Part 1 (前半)。「アテナ」戦。パラデイグマ系のギミックが軸。
 主要技:
   - パラデイグマ 1回目 (タンク無敵処理)
   - パラデイグマ 2回目 (十字、線対面伸ばし、塔TH反時計/塔DPS時計)
@@ -3534,8 +3472,7 @@
   - パラデイグマ 3回目 (イディル: 北十字 / 南X字)
   - サイコロフェーズ (ネバーランド)
   - オン・ザ・ソウル
-野良主流: ぬけまる式 (「パラ1無敵パラ2十字パラ3イディルサイコロネバラン」)。
-</t>
+野良主流: ぬけまる式 (「パラ1無敵パラ2十字パラ3イディルサイコロネバラン」)。</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3500,7 @@
       <c r="E44" s="8" t="inlineStr"/>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 2 (後半)。「パラス・アテナ」戦。神格融合形態。
+          <t>Part 2 (後半)。「パラス・アテナ」戦。神格融合形態。
 Idol of Darkness 系・カロリック系・パンゲネシスが軸。
 主要技:
   - パラスの手 (T:西 / 他:東)
@@ -3577,8 +3514,7 @@
   - カロリック2回目 (反時計/最後中央行かずに2回移動)
   - サモンダークネス + デミ 2回目 (MTD1 が奥まで走る)
   - 最終線処理 (MT/D1, ST/D2, H1/D3, H2/D4 ペア)
-野良主流: ぬけまる動画ベース (Game8 採用、X処理メイン)。
-</t>
+野良主流: ぬけまる動画ベース (Game8 採用、X処理メイン)。</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3542,7 @@
       <c r="E45" s="8" t="inlineStr"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">コキュートス戦。1ボス完結型 (フェーズ分けはしないが、内部的に「メイジ」「マーシャリスト」
+          <t>コキュートス戦。1ボス完結型 (フェーズ分けはしないが、内部的に「メイジ」「マーシャリスト」
 「キメラ」「ビースト」の魂を取り込んで姿を変える展開)。
 主要ギミック:
   - グラトニーズアーガー (全体)
@@ -3619,8 +3555,7 @@
   - ビーストフェーズ (毒・扇誘導)
   - キメリックコンボ (サイコロ2回目)
   - 憑魔双撃 (フィニッシュ系)
-野良主流: 無職マラソン式 (Game8 採用、ぬけまる動画ベース)。
-</t>
+野良主流: 無職マラソン式 (Game8 採用、ぬけまる動画ベース)。</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3583,7 @@
       <c r="E46" s="8" t="inlineStr"/>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディスコ/ダンスモチーフの「パーティー野郎」ダンシング・グリーン戦。1ボス完結型。
+          <t>ディスコ/ダンスモチーフの「パーティー野郎」ダンシング・グリーン戦。1ボス完結型。
 主要ギミック:
   - ディープカット (タンク強攻撃)
   - ジングル予約 A/B (固定流派では予約位置に固定)
@@ -3661,8 +3596,7 @@
   - カモン！フロッグダンサー (MT組:北西 / ST組:南東)
   - ダンシングフィールド (扇誘導 TH→DPS)
 野良主流: ぬけまる式 (Game8 採用)。
-※ PERFECT GROOVE×2 で LB ゲージ獲得が想定されている火力設計。
-</t>
+※ PERFECT GROOVE×2 で LB ゲージ獲得が想定されている火力設計。</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3624,7 @@
       <c r="E47" s="8" t="inlineStr"/>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">シュガーライオット 前半。スプレーガンで描いたアートを具現化させる戦闘。
+          <t>シュガーライオット 前半。スプレーガンで描いたアートを具現化させる戦闘。
 主要技:
   - カラーライオット
   - ウイングマーク
@@ -3699,8 +3633,7 @@
   - ランドスケープ
   - カラークラッシュ (2:2:2:2 配置)
   - 砂漠フェーズ: サボテン避け、サボテン+流砂、爆弾捨て (流砂北基準)
-野良主流: Game8 採用版 (新FFO式 Ver.3.1)。
-</t>
+野良主流: Game8 採用版 (新FFO式 Ver.3.1)。</t>
         </is>
       </c>
     </row>
@@ -3728,15 +3661,14 @@
       <c r="E48" s="8" t="inlineStr"/>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">雑魚フェーズ後の後半。山川 (山と川のフィールド) ギミック。
+          <t>雑魚フェーズ後の後半。山川 (山と川のフィールド) ギミック。
 主要技:
   - 山川 (火・雷)
   - 雷雲 (TH←左 / 他DPS→右)
   - 雷 (基本散会)
   - マグマ (北 H1H2 / 南 D3D4 → MT/ST/D1/D2)
   - 塔処理 2回目: 4・2・2 or 南8塔 (構成によって配置変動)
-野良主流: Game8 後半マクロ (Lucrezia 様動画準拠)。
-</t>
+野良主流: Game8 後半マクロ (Lucrezia 様動画準拠)。</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3696,7 @@
       <c r="E49" s="8" t="inlineStr"/>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ブルートアボミネーター前半フェーズ。
+          <t>ブルートアボミネーター前半フェーズ。
 主要技:
   - スキャッターシード 1回目 (種捨て + エラプ)
     * 近接: 南内側開始→上→中央→下
@@ -3773,8 +3705,7 @@
   - ソーンスマッシュ (北固定散開)
   - ブルートグラワー (中央集合からの十字配置)
   - ソーンデスマッチ・ビルディング (いしあ式・さり式・ぽにこね式が存在、Game8 はさり式)
-野良主流: さり式 (Game8 採用) または ぽにこね式。
-</t>
+野良主流: さり式 (Game8 採用) または ぽにこね式。</t>
         </is>
       </c>
     </row>
@@ -3802,15 +3733,14 @@
       <c r="E50" s="8" t="inlineStr"/>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">後半フェーズ。石化視線ギミックと2体ボス処理。
+          <t>後半フェーズ。石化視線ギミックと2体ボス処理。
 主要技:
   - ゾーンデスマッチ・ウォール (石化視線: 北西/南東避け、雑魚石化後処理)
   - スキャッターシード 2回目 (近接北西集合)
     * 近接 AoE: 北西から時計回り→南西安置 (遠隔: シード十字捨て、南側外周避け)
     * 遠隔 AoE: 最外周捨て→中央安置 (近接: シード十字内側捨て、外から2マス、中央避け)
   - ウェポンツイン + ブロウシード (1回目北向き / 2回目ボス北基準)
-  - ストーンウェポン: ツイン (P3 最大の山場、移動シビア)
-</t>
+  - ストーンウェポン: ツイン (P3 最大の山場、移動シビア)</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3768,7 @@
       <c r="E51" s="8" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 1 (前半)。土と風のフェンリルを操る戦闘。
+          <t>Part 1 (前半)。土と風のフェンリルを操る戦闘。
 主要技:
   - 空間斬り (タンク強攻撃)
   - 土の魔技 (MTD4/D3/H1/D1ST/H2/D2 の配置)
@@ -3849,8 +3779,7 @@
   - 光狼招来 (分身ギミック)
   - 大地の怒り (風化散開 + 安置時計回り or ズレ時計回り)
   - 幻狼招来 (MT/D3 / ST/D4 / H1/D1 ST/D2 配置)
-野良主流: ぬけまる様マクロ (イディル土修正 / 風化IQ6000 / 狐狼Alice / 81128 構成)。
-</t>
+野良主流: ぬけまる様マクロ (イディル土修正 / 風化IQ6000 / 狐狼Alice / 81128 構成)。</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3807,7 @@
       <c r="E52" s="8" t="inlineStr"/>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 2 (後半)。土と風のフェンリルの力を全て取り込み巨大化したハウリングブレード戦。
+          <t>Part 2 (後半)。土と風のフェンリルの力を全て取り込み巨大化したハウリングブレード戦。
 主要技:
   - クエイガ / 1-3 魔光 (青マカ上から北島→その場→南島)
   - 双牙撃 (西島:MT / 東島:ST)
@@ -3886,8 +3815,7 @@
   - 風狼陣 / 双牙暴風撃 (D1D3 / D2D4 配置、線・誘導処理)
   - 孤狼の呪い (Alice式: Tニア北東 / Tファー西 / H不動 / Dニア線南北判定 / Dファー線南北判定)
   - 八連光弾 (時間切れ前: 2=MT無敵 / 3=ST無敵 / 4=T二人フルバフ)
-野良主流: ぬけまる様 魔印正規 / 狐狼Alice / 81128 構成 (Game8 採用)。
-</t>
+野良主流: ぬけまる様 魔印正規 / 狐狼Alice / 81128 構成 (Game8 採用)。</t>
         </is>
       </c>
     </row>
@@ -3915,15 +3843,14 @@
       <c r="E53" s="8" t="inlineStr"/>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">レッドホット (赤、火属性) 単独フェーズ。
+          <t>レッドホット (赤、火属性) 単独フェーズ。
 主要技:
   - ホットインパクト (全体)
   - フレイムフローター (1回目はボス見て右上/左上交互、逆Z字)
   - フレイムアリウープ (火アリウープ)
   - ハイジャンプカットバック
   - バイロローテーション
-野良主流: Game8 / 家無しララ様 / 犬丸様の融合版。
-</t>
+野良主流: Game8 / 家無しララ様 / 犬丸様の融合版。</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3878,7 @@
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディープブルー (青、水属性) 単独フェーズ。
+          <t>ディープブルー (青、水属性) 単独フェーズ。
 主要技:
   - シック・スウェル
   - シック・テイクオフ
@@ -3959,8 +3886,7 @@
   - ディープインパクト
   - ハイドロスネーキング (蛇ライン、1回目は MT組青ボス下/ST組赤ボス下)
   - ハイドロバリエル (赤デバフ→赤沼有り半面、青デバフ→赤沼無し半面)
-  - 水牢 (H1H2 塔入り)
-</t>
+  - 水牢 (H1H2 塔入り)</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3914,7 @@
       <c r="E55" s="8" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">赤青2体同時相手にする合流フェーズ。
+          <t>赤青2体同時相手にする合流フェーズ。
 主要技:
   - エクストリーム・スペクタクル
   - インセインエアー (扇誘導 - 青MT組/赤ST組)
@@ -3996,8 +3922,7 @@
   - エクストリームウェイブ
   - スネーキング2回目 (交代散開: 1回目近接、2回目遠隔)
   - 青+赤アリウープ (マップ基準、基本散開方向の外周で時計回り)
-  - ファイティングスピリット (時間切れ)
-</t>
+  - ファイティングスピリット (時間切れ)</t>
         </is>
       </c>
     </row>
@@ -4025,7 +3950,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">開幕〜中盤フェーズ。
+          <t>開幕〜中盤フェーズ。
 主要技:
   - キング・オブ・アルカディア (全体)
   - ウェポンジェネレート・バスター (タンク強)
@@ -4037,8 +3962,7 @@
   - ワン・アンド・オンリーフェーズ
   - ファイアストリーム
   - メテオレイン (3回連続、隕石処理)
-野良主流: ぬけまる様式 (Game8 採用)。
-</t>
+野良主流: ぬけまる様式 (Game8 採用)。</t>
         </is>
       </c>
     </row>
@@ -4066,15 +3990,14 @@
       <c r="E57" s="8" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">後半フェーズ。チャンピオンズ・メテオから始まり、メテオスタンピード、
+          <t>後半フェーズ。チャンピオンズ・メテオから始まり、メテオスタンピード、
 最終的にハートブレイクキック (時間切れ) で終了。
 主要技:
   - チャンピオンズ・メテオ (塔踏み2セット、ジジ式位置固定)
   - メテオスタンピード (DXA 式: 沼捨て+範囲捨て+塔)
   - フォーウェイ (X字ペア / 内側誘導)
   - ツーウェイ (東西4:4)
-  - ハートブレイクキック (時間切れ)
-</t>
+  - ハートブレイクキック (時間切れ)</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4025,7 @@
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 1 (前半)。細胞付着ギミックがメイン。
+          <t>Part 1 (前半)。細胞付着ギミックがメイン。
 主要技:
   - リーサルスカージ (玉誘導、D側:MT組 / B側:ST組)
   - 細胞付着・前期 (左前タゲサ端で散開、頭割り:角扇外周)
@@ -4110,8 +4033,7 @@
   - 細胞付着・後期 (細胞中央向け、X字/十字判断)
   - 細胞付着・終期 (AoE 左上から外周沿い捨て)
   - スローターシェッド (頭割り＆散開＆半面攻撃判定)
-野良主流: ぬけまる様式 (ほぼイディル式) - Game8 採用。
-</t>
+野良主流: ぬけまる様式 (ほぼイディル式) - Game8 採用。</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4061,7 @@
       <c r="E59" s="8" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 2 (後半)。リンドブルム・メテオから始まり、フィールドが浮島×2に変化。
+          <t>Part 2 (後半)。リンドブルム・メテオから始まり、フィールドが浮島×2に変化。
 4 色の塔 (赤/黄/紫/緑) ギミック → アルカディアンドリーム (3 分以上の大ギミック)
 が後半の山場。最終的にアルカディアンドリームを処理しきれば実質クリア。
 主要技:
@@ -4150,8 +4072,7 @@
   - 模倣細胞 (牛子式)
   - 変異細胞 + マナスフィア (αβデバフ管理)
   - アルカディアンドリーム (3 分以上、予告遅延型大ギミック、ワンエース式)
-野良主流: Game8 推奨は レプリ:位置固定式 / 模倣:牛子式 / ドリーム:ワンエース式。
-</t>
+野良主流: Game8 推奨は レプリ:位置固定式 / 模倣:牛子式 / ドリーム:ワンエース式。</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4100,7 @@
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">コウモリモチーフの「魔性の処刑人」ヴァンプ・ファタール戦。1ボス完結型。
+          <t>コウモリモチーフの「魔性の処刑人」ヴァンプ・ファタール戦。1ボス完結型。
 主要ギミック:
   - ヴァンプストンプ (近接タゲサ上、コウモリ1の背後)
   - エーテルレッティング (扇範囲散開・最外周捨て・中央集合)
@@ -4188,8 +4109,7 @@
   - バット・デスマッチ (コウモリ追従、MT組北西 / ST組南東)
   - その他: フィナーレ・ファターレ / ハーフムーン / ブルータルレイン (頭割り) /
     サングインスクラッチ / インセーシャブル・サースト / ハードコア (タンク強)
-野良主流: ぬけまる式 (Game8 マクロが採用)。
-</t>
+野良主流: ぬけまる式 (Game8 マクロが採用)。</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4137,7 @@
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">黒猫モチーフの「爪研ぐ猫魂」ブラックキャット戦。1ボス完結型。
+          <t>黒猫モチーフの「爪研ぐ猫魂」ブラックキャット戦。1ボス完結型。
 主要ギミック:
   - クアドラプルネイル (十字固定処理、先:TH/後:DPS、ペア割は扇誘導位置から反時計)
   - ナインライヴス (近接 8 連撃、タンク強)
@@ -4230,8 +4150,7 @@
   - ネイルチッパー
   - レイニングキャッツ (タンク無敵、本ボスのソフト時間切れ)
   - コピーキャット (分身)
-野良主流: 犬丸式 (Game8 採用、十字固定 + タンク無敵)。
-</t>
+野良主流: 犬丸式 (Game8 採用、十字固定 + タンク無敵)。</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4178,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">「劇毒の愛」ハニーB・ラブリー戦。1ボス完結型。
+          <t>「劇毒の愛」ハニーB・ラブリー戦。1ボス完結型。
 主要ギミック:
   - ハニーツイスター / ハニーブラスト (全体ダメージ)
   - ハニー・B・ライヴ (1st / 2nd / 3rd の 3 回構成)
@@ -4272,8 +4191,7 @@
   - ブラックハート (8 方向散開 → HP 回復後早いペア順に中央集合)
   - キラースラッシュ / キラースティング (タンク強)
   - 毒捨て: TH 北西 / DPS 南東
-野良主流: ぬけまる版 (Game8 採用)。
-</t>
+野良主流: ぬけまる版 (Game8 採用)。</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4219,7 @@
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">「爆ぜる悪意」ブルートボンバー戦。1ボス完結型 (途中分身追加あり)。
+          <t>「爆ぜる悪意」ブルートボンバー戦。1ボス完結型 (途中分身追加あり)。
 主要ギミック:
   - 4 or 8 ウェイ・ダブルラリアット (4/8 方向 AOE 連撃、近接全員のラリアット 1 発受け必須)
   - 4 or 8 ショック・パワーダイブ (4/8 ショック散開)
@@ -4311,8 +4229,7 @@
   - ボンバリアンスペシャル (8 ショック/基本散開、4 ショック/ペア X 受け)
   - 極盛り式スピニングファイヤー (アタッチ)
   - チェーンデスマッチ (チェーンで繋がれた相手のラリアットを受ける)
-野良主流: ぬけまる版 Ver.2.0 (Game8 採用)。
-</t>
+野良主流: ぬけまる版 Ver.2.0 (Game8 採用)。</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4257,7 @@
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 1 (前半)。雷魔女モチーフのウィケッドサンダー前半フェーズ。
+          <t>Part 1 (前半)。雷魔女モチーフのウィケッドサンダー前半フェーズ。
 主要技:
   - フライングウィッチ (北と西からの直線範囲攻撃)
   - ライトニング・ウィッチハント (床予兆 + 東側エレクトロープ対応)
@@ -4350,8 +4267,7 @@
   - シャインスパーク (被撃回数管理)
   - エレクトロンストリーム (デバフ色逆ビーム受け、紫/誘電/青の 5 ライン)
   - エレクトロープ移植 (8 方向扇範囲回避、時計→反時計往復)
-野良主流: ぬけまる版 + DN 式 (Game8 採用)。
-</t>
+野良主流: ぬけまる版 + DN 式 (Game8 採用)。</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4295,7 @@
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 2 (後半)。クロステイル・スペシャル (タンク LB3 推奨) からスタートし、
+          <t>Part 2 (後半)。クロステイル・スペシャル (タンク LB3 推奨) からスタートし、
 ブラックサバト 3 連 (日没・夜半・日出) を経て剣の舞 (時間切れ) で終了。
 主要技:
   - クロステイル・スペシャル (9 連魔法攻撃、タンク LB3 推奨)
@@ -4394,8 +4310,7 @@
       * 誘導: TH 11 時から反時計、DPS 12 時から時計
   - 剣の雨 (MT ST / D1 D2 / H1 H2 / D3 D4 の 4:4 ペア)
   - 剣の舞 (時間切れ、MT/D1 + ST/D2 + H1/D3 + H2/D4 のペア構成、2:2:2:2 配置)
-野良主流: ぬけまる版 (Game8 採用)。
-</t>
+野良主流: ぬけまる版 (Game8 採用)。</t>
         </is>
       </c>
     </row>
@@ -4587,9 +4502,8 @@
       <c r="E71" s="8" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ケフカ第1形態。詳細は未公開 (リリース 2026-06-02 予定)。
-# Source: 要追加調査
-</t>
+          <t>ケフカ第1形態。詳細は未公開 (リリース 2026-06-02 予定)。
+# Source: 要追加調査</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4900,12 +4814,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>FF14 みんとのギミック解説 絶アルテマウェポン ガルーダ編(メソハイMTキャス)</t>
+          <t>P1 ガルーダ解説 【みんとっと】</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zZ6qhddIO3I</t>
+          <t>https://youtu.be/Sb6NfNCUWtM?si=wga2blrKf35-52Dr</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -4922,17 +4836,17 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>FF14 みんとのギミック解説 絶アルテマ破壊作戦 ガルーダ編 MT視点 (メソハイキャスMT)</t>
+          <t>P2 イフリート解説 【みんとっと】</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iWQmHY19zt0</t>
+          <t>https://youtu.be/qoI6B2QZxb8?si=BEVMlR6Kls-QhK0H</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -4949,17 +4863,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>FF14 みんとのギミック解説 絶アルテマウェポン破壊作戦 イフリート編(楔逆Z)</t>
+          <t>P3 タイタン＆LBフェーズ解説 【みんとっと】</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=LCjYKOImeuM</t>
+          <t>https://youtu.be/-hAfONuZEcE?si=ELfei57MX6PSBTQR</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -4976,17 +4890,17 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>FF14 みんとのギミック解説 絶アルテマ破壊作戦 タイタン編</t>
+          <t>P4 アルテマフェーズ序 解説 【みんとっと】</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cJaNpDkBwu4</t>
+          <t>https://youtu.be/iSZOcsMIKhQ?si=KAqiSXCwORaBJTRD</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -5003,17 +4917,17 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>FF14 みんとのギミック解説 絶アルテマウェポン タイタン＆LB編</t>
+          <t>P5 アルテマフェーズ 中 解説【みんとっと】</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2safeyumQ9o</t>
+          <t>https://youtu.be/fjDJattJTi4?si=LX_sM3Wr5bH9WtnQ</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -5030,17 +4944,17 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>FF14 みんとのギミック解説 絶アルテマウェポン 追撃の究極幻想</t>
+          <t>P6アルテマフェーズ 終 解説【みんとっと】</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ENn9O274DMw</t>
+          <t>https://youtu.be/gQK6JOK7nZw?si=VIhwqVzIKTH3WKHi</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -5052,75 +4966,83 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>FF14 ⑤絶アルテマ きりたんたちと学ぶ アルテマフェーズ(中)</t>
+          <t>P1 リビングリキッド（ヤークト無視）解説【ふうcだよ】</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fjDJattJTi4</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=mxy_ZYEYwlE&amp;t=3s</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>ふうｃだよ</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>FF14 みんとのギミック解説 絶アルテマ破壊作戦 完結編(3111 乱撃インビン)</t>
+          <t>P1 リビングリキッド（サイコロフェーズ）解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QpuleeUOHh0</t>
+          <t>https://youtu.be/AMdtMyvbPNs?si=1bpCn66GIcS1Wqlw&amp;t=1037</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>みんとっと</t>
+          <t>ぬけまるG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>uwu</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>D4特化型 絶アルテマウェポン超絶シンプル破壊大作戦解説</t>
+          <t>P2 2体フェーズ解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=74_JclZrORA</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr"/>
+          <t>https://youtu.be/yuLjtpm2ti8?si=s06vqJPX5VB10aPR</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -5130,17 +5052,17 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>【FF14/濃厚解説】絶アレキ討滅戦 リキッドセパレ式 サイコロ44と1211【ぬけまる】Re</t>
+          <t>P3 プライムフェーズ解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AMdtMyvbPNs</t>
+          <t>https://youtu.be/3wtfeXognIY?si=905JsYF7OMv-5_qh</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -5157,25 +5079,29 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>FF14 みんとのギミック解説 絶アレキサンダー討滅戦 リキッド&amp;サイコロ編 (だいたいセパレ 4:4)</t>
+          <t>P4 パーフェクトアレキサンダー解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a_D-UFcMiYU</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr"/>
+          <t>https://youtu.be/9YgDXyUWbiQ?si=g63xrfP-nJre3pxS</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p1s</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -5185,12 +5111,12 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>FF14 絶アレキ サイコロフェーズ 1211式 イメトレ用 ポイント解説付き</t>
+          <t>ゆっくりと振り返るパンデモニウム辺獄編零式1層</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BSTvYXvM1ls</t>
+          <t>https://www.youtube.com/watch?v=eGJ5eRvRzK8</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr"/>
@@ -5198,7 +5124,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p2s</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -5208,12 +5134,12 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>【絶アレキサンダー】リキッドフェーズ【解説動画】</t>
+          <t>ゆっくりと振り返るパンデモニウム辺獄編零式1層</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j8taILNR6-g</t>
+          <t>https://www.youtube.com/watch?v=eGJ5eRvRzK8</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
@@ -5221,7 +5147,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p3s</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5231,12 +5157,12 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>【絶アレキサンダー討滅戦】饅頭でも分かるリビングリキッド徹底解説【ゆっくり実況プレイ/FF14】</t>
+          <t>ゆっくりと振り返るパンデモニウム辺獄編零式1層</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=o4PCuw7FS70</t>
+          <t>https://www.youtube.com/watch?v=eGJ5eRvRzK8</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr"/>
@@ -5244,34 +5170,30 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p4s</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>【FF14/濃厚解説】絶アレキ討滅戦 2体フェーズ 5ジョブ視点有【ぬけまる】</t>
+          <t>ゆっくりと振り返るパンデモニウム辺獄編零式4層(前半)</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yuLjtpm2ti8</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=AH0mRxuJx7c</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>p4s</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -5281,12 +5203,12 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>【FF14】2体フェーズ ギミック解説【絶アレキサンダー討滅戦】</t>
+          <t>ゆっくりと振り返るパンデモニウム辺獄編零式4層(後半)</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xl7jU2EmmaE</t>
+          <t>https://www.youtube.com/watch?v=GYCDnITC_jc</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
@@ -5294,49 +5216,45 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>【FF14/濃厚解説】絶アレキ討滅戦 プライムフェーズ ハムカツさん34固定方式 各視点有【ぬけまる】</t>
+          <t>【絶竜詩戦争】文字を読みたくない人のための教皇庁① (P1解説)</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3wtfeXognIY</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=Xd9DQojqmWA</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>【FF14/濃厚解説】絶アレキ討滅戦 最終パレキフェーズ【ぬけまる】</t>
+          <t>【FF14/絶】絶竜詩戦争 攻略配信 Day 1【ぬけまる】</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9YgDXyUWbiQ</t>
+          <t>https://www.youtube.com/watch?v=knE5LqufEW8</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -5348,22 +5266,22 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>【絶アレキ】パーフェクトアレキサンダーフェーズ【解説】</t>
+          <t>【絶竜詩戦争】文字を読みたくない人のためのトールダンフェーズ</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dXZBMPY9gjE</t>
+          <t>https://www.youtube.com/watch?v=mxeQNCgHI7Y</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
@@ -5371,45 +5289,49 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>【FF14/解説】誰でもわかる 最終フェーズ 図解 ゆっくり音声付 絶アレキサンダー討滅戦【再掲載】</t>
+          <t>【FF14/絶解説】絶竜詩戦争 ニーズフェーズ図解解説 ジャンプ全パターン視点あり【ぬけまる】</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XR9IFP647oI</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=mxeQNCgHI7Y</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>p1s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>ゆっくりと振り返るパンデモニウム辺獄編零式1層</t>
+          <t>【絶竜詩戦争】文字を読みたくない人のためのニーズヘッグフェーズ前半【解説】</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eGJ5eRvRzK8</t>
+          <t>https://www.youtube.com/watch?v=Xd9DQojqmWA</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr"/>
@@ -5417,94 +5339,110 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>p2s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>ゆっくりと振り返るパンデモニウム辺獄編零式1層</t>
+          <t>【絶竜詩戦争】邪眼フェーズ解説（要調査）</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eGJ5eRvRzK8</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/@nukemarugames/videos</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>p3s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>ゆっくりと振り返るパンデモニウム辺獄編零式1層</t>
+          <t>【FF14/絶解説】こまぞう式改 死刻 絶竜詩 アニメーション解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eGJ5eRvRzK8</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=NIroKcIHpnI</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>ゆっくりと振り返るパンデモニウム辺獄編零式4層(前半)</t>
+          <t>【FF14/絶解説】絶竜詩戦争 いいところ取り死刻+α アニメーション解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AH0mRxuJx7c</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=TBt_AgoHn80</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>p4s</t>
+          <t>dsr</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>ゆっくりと振り返るパンデモニウム辺獄編零式4層(後半)</t>
+          <t>【FF14/絶解説】絶竜詩戦争 2天竜フェーズ 図解解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GYCDnITC_jc</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=3yJpWHmKjpg</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -5514,20 +5452,24 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>【絶竜詩戦争】文字を読みたくない人のための教皇庁① (P1解説)</t>
+          <t>【FF14/絶解説】絶竜詩戦争 最終フェーズ 図解解説 軽減例付き 忍暗白視点【ぬけまる】</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Xd9DQojqmWA</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=1fsbzkZsWUE</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -5537,144 +5479,148 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶】絶竜詩戦争 攻略配信 Day 1【ぬけまる】</t>
+          <t>【絶竜詩戦争】文字を読みたくない人のための騎竜神トールダン【解説】</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=knE5LqufEW8</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=pRkdxw9YOLo</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p5s</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>【絶竜詩戦争】文字を読みたくない人のためのトールダンフェーズ</t>
+          <t>【 FF14 / 煉獄零式解説 】煉獄編 零式 1層 さらっと解説 概要欄にマクロあります【ぬけまる】</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mxeQNCgHI7Y</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=GRrZvJT1fXM</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p5s</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶竜詩戦争 ニーズフェーズ図解解説 ジャンプ全パターン視点あり【ぬけまる】</t>
+          <t>【 FF14 】速報版 パンデモニウム 煉獄編 零式1層 解説動画 【 犬丸のぞみ 】</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mxeQNCgHI7Y</t>
+          <t>https://www.youtube.com/watch?v=W7nJ5q8cU7w</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>ぬけまるG</t>
+          <t>犬丸のぞみ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p6s</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>【絶竜詩戦争】文字を読みたくない人のためのニーズヘッグフェーズ前半【解説】</t>
+          <t>【 FF14 / 煉獄零式解説 】煉獄編 零式 2層 さらっと解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Xd9DQojqmWA</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=pibChZ8AjZ8</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p6s</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>【絶竜詩戦争】邪眼フェーズ解説（要調査）</t>
+          <t>【 FF14 】速報版 パンデモニウム 煉獄編 零式2層 解説動画 【 犬丸のぞみ 】</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
+          <t>https://www.youtube.com/watch?v=0DOhkqfDELw</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>ぬけまるG</t>
+          <t>犬丸のぞみ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p7s</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】こまぞう式改 死刻 絶竜詩 アニメーション解説【ぬけまる】</t>
+          <t>【 FF14 / 煉獄零式解説 】煉獄編 零式 ３層 獄八凶無敵乱犬丸 主流図解解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NIroKcIHpnI</t>
+          <t>https://www.youtube.com/watch?v=iaxDpAfkTIA</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -5686,22 +5632,22 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p7s</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶竜詩戦争 いいところ取り死刻+α アニメーション解説【ぬけまる】</t>
+          <t>主流まとめ解説 ハピおじ ほララ 辺獄無敵 零式3層をアニメーションで理解する動画【 ぬけまる 】最新版</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TBt_AgoHn80</t>
+          <t>https://www.youtube.com/watch?v=31_2BeHgSwQ</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -5713,49 +5659,45 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p7s</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶竜詩戦争 2天竜フェーズ 図解解説【ぬけまる】</t>
+          <t>生命の繁茂【凶】 無敵式 解説動画!! 【煉獄編零式3層】【賢者視点】【FF14】</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3yJpWHmKjpg</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=ltw49krh4JI</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶竜詩戦争 最終フェーズ 図解解説 軽減例付き 忍暗白視点【ぬけまる】</t>
+          <t>【 FF14 / 煉獄零式解説 】概要欄に最新版のアニメーション版があります。煉獄編 零式 4層 前半 さらっと解説Re:【ぬけまる】</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1fsbzkZsWUE</t>
+          <t>https://www.youtube.com/watch?v=tY6c1yXCe18</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -5767,22 +5709,22 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>【絶竜詩戦争】文字を読みたくない人のための騎竜神トールダン【解説】</t>
+          <t>ゆっくりと振り返るパンデモニウム煉獄編零式4層前半</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pRkdxw9YOLo</t>
+          <t>https://www.youtube.com/watch?v=MNKL9NqluRI</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr"/>
@@ -5790,7 +5732,7 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -5800,66 +5742,62 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 / 煉獄零式解説 】煉獄編 零式 1層 さらっと解説 概要欄にマクロあります【ぬけまる】</t>
+          <t>煉獄編零式4層前半ヘファイストス 賢者視点解説動画 【FF14】</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GRrZvJT1fXM</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=CdOhzb7EUqs</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>p5s</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 】速報版 パンデモニウム 煉獄編 零式1層 解説動画 【 犬丸のぞみ 】</t>
+          <t>【 FF14 / 煉獄零式解説 】最新版が概要欄にあります。煉獄編 零式 4層 後半 軽減例付き アニメーション解説【ぬけまる】:Re</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W7nJ5q8cU7w</t>
+          <t>https://www.youtube.com/watch?v=RaLfkv-B2Zg</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>犬丸のぞみ</t>
+          <t>ぬけまるG</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 / 煉獄零式解説 】煉獄編 零式 2層 さらっと解説【ぬけまる】</t>
+          <t>【 FF14 / 補足解説 】はいじあ式 煉獄編 4層後半 万象灰燼 解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pibChZ8AjZ8</t>
+          <t>https://www.youtube.com/watch?v=8kdGUhXYBJI</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -5871,61 +5809,61 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>p6s</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 】速報版 パンデモニウム 煉獄編 零式2層 解説動画 【 犬丸のぞみ 】</t>
+          <t>煉獄編 零式 4層後半 初回クリア動画 学者視点【ぬけまる】</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0DOhkqfDELw</t>
+          <t>https://www.youtube.com/watch?v=ttwdLF9di10</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>犬丸のぞみ</t>
+          <t>ぬけまるG</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>p8s</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 / 煉獄零式解説 】煉獄編 零式 ３層 獄八凶無敵乱犬丸 主流図解解説【ぬけまる】</t>
+          <t>【 FF14 】※概要欄に補足動画あり パンデモニウム 煉獄零式 4層後半 解説動画 【 犬丸のぞみ / inumaru 】</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iaxDpAfkTIA</t>
+          <t>https://www.youtube.com/watch?v=Umwojv_T5yc</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>ぬけまるG</t>
+          <t>犬丸のぞみ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -5935,12 +5873,12 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>主流まとめ解説 ハピおじ ほララ 辺獄無敵 零式3層をアニメーションで理解する動画【 ぬけまる 】最新版</t>
+          <t>【FF14/絶解説】絶オメガフェーズ1 さらっとアニメーション解説【ぬけまる】修正</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=31_2BeHgSwQ</t>
+          <t>https://www.youtube.com/watch?v=vcQizvMjSio</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -5952,7 +5890,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>p7s</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -5962,12 +5900,12 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>生命の繁茂【凶】 無敵式 解説動画!! 【煉獄編零式3層】【賢者視点】【FF14】</t>
+          <t>【FF14】パントクラトル 完全解説【絶オメガ検証戦 フェーズ１】</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ltw49krh4JI</t>
+          <t>https://www.youtube.com/watch?v=3Xa4Sdc76KA</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr"/>
@@ -5975,7 +5913,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -5985,12 +5923,12 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 / 煉獄零式解説 】概要欄に最新版のアニメーション版があります。煉獄編 零式 4層 前半 さらっと解説Re:【ぬけまる】</t>
+          <t>【FF14/イメトレ用】絶オメガ パンクライメトレまとめ</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=tY6c1yXCe18</t>
+          <t>https://www.youtube.com/watch?v=5okMJ8LzxlE</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -6002,7 +5940,7 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
@@ -6012,20 +5950,24 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>ゆっくりと振り返るパンデモニウム煉獄編零式4層前半</t>
+          <t>【FF14/イメトレ用】絶オメガ サークルプログラムイメトレまとめ</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=MNKL9NqluRI</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=J0uBb7Xe9oQ</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -6035,12 +5977,12 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>煉獄編零式4層前半ヘファイストス 賢者視点解説動画 【FF14】</t>
+          <t>【絶オメガ】文字を読みたくない人のための絶オメガＰ１【解説】</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CdOhzb7EUqs</t>
+          <t>https://www.youtube.com/watch?v=GABEtFVcn58</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr"/>
@@ -6048,7 +5990,7 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
@@ -6058,12 +6000,12 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 / 煉獄零式解説 】最新版が概要欄にあります。煉獄編 零式 4層 後半 軽減例付き アニメーション解説【ぬけまる】:Re</t>
+          <t>【FF14/絶解説】絶オメガフェーズ P2さらっと図解解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RaLfkv-B2Zg</t>
+          <t>https://www.youtube.com/watch?v=bDXXSksWPQo</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -6075,22 +6017,22 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 / 補足解説 】はいじあ式 煉獄編 4層後半 万象灰燼 解説【ぬけまる】</t>
+          <t>【FF14/絶解説】絶オメガP3 ハロワ検知 アニメーション解説 The Omega Protocol P3【ぬけまる】</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8kdGUhXYBJI</t>
+          <t>https://www.youtube.com/watch?v=mj1a2G2TBgk</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -6102,22 +6044,22 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>煉獄編 零式 4層後半 初回クリア動画 学者視点【ぬけまる】</t>
+          <t>【絶オメガ/イメトレ】P3 検知式波動砲 十字式イメトレ【ぬけまる】</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ttwdLF9di10</t>
+          <t>https://www.youtube.com/watch?v=eUPGkeg6qCU</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -6129,29 +6071,25 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>p8s</t>
+          <t>top</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 】※概要欄に補足動画あり パンデモニウム 煉獄零式 4層後半 解説動画 【 犬丸のぞみ / inumaru 】</t>
+          <t>【絶オメガ】文字を読みたくない人のための絶オメガＰ３【解説】</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Umwojv_T5yc</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>犬丸のぞみ</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=9dyL-nSOJuA</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -6161,17 +6099,17 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶オメガフェーズ1 さらっとアニメーション解説【ぬけまる】修正</t>
+          <t>【FF14/絶解説】絶オメガP4 ブルースクリーン解説 The Omega Protocol P4【ぬけまる】</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vcQizvMjSio</t>
+          <t>https://www.youtube.com/watch?v=ayGtjf0__0k</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -6188,20 +6126,24 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>【FF14】パントクラトル 完全解説【絶オメガ検証戦 フェーズ１】</t>
+          <t>【絶オメガ】ブルースクリーンをひたすら見る動画【P4】</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3Xa4Sdc76KA</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=rPa6ei-fgJs</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -6211,17 +6153,17 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>【FF14/イメトレ用】絶オメガ パンクライメトレまとめ</t>
+          <t>【FF14/絶解説】絶オメガP5 コード:＊＊＊ミ＊【デルタ】 アニメーション解説 The Omega Protocol P5【ぬけまる】</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5okMJ8LzxlE</t>
+          <t>https://www.youtube.com/watch?v=vg_AEbdn2zM</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -6238,17 +6180,17 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>【FF14/イメトレ用】絶オメガ サークルプログラムイメトレまとめ</t>
+          <t>【FF14/絶解説】絶オメガP5 コード:＊＊＊ミ＊【シグマ】注意点追加版 アニメーション解説 The Omega Protocol P5【ぬけまる】</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=J0uBb7Xe9oQ</t>
+          <t>https://www.youtube.com/watch?v=3x-_d8RZJXE</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -6265,20 +6207,24 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>【絶オメガ】文字を読みたくない人のための絶オメガＰ１【解説】</t>
+          <t>【FF14/絶解説】絶オメガP5 コード:＊＊＊ミ＊【オメガ】 アニメーション解説 The Omega Protocol P5-3【ぬけまる】修正版</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GABEtFVcn58</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=6LIXoAk7wrI</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -6288,24 +6234,20 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶オメガフェーズ P2さらっと図解解説【ぬけまる】</t>
+          <t>【FF14】絶オメガ検証戦 ランデュナミス解説 フェーズ5 (さらちゃんのつぶやき)</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bDXXSksWPQo</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://sarachantubuyaki.jp/finalfantasyxiv/run-dynamis/</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -6315,24 +6257,20 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶オメガP3 ハロワ検知 アニメーション解説 The Omega Protocol P3【ぬけまる】</t>
+          <t>【絶オメガ】文字を読みたくない人のためのP5オメガ【解説】</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mj1a2G2TBgk</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=316MZKSBXdc</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -6342,17 +6280,17 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p6</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>【絶オメガ/イメトレ】P3 検知式波動砲 十字式イメトレ【ぬけまる】</t>
+          <t>【FF14/絶解説】絶オメガ最終P6 アルファオメガ 軽減付アニメーション解説 The Omega Protocol P6【ぬけまる】最新</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eUPGkeg6qCU</t>
+          <t>https://www.youtube.com/watch?v=2u_I9zYh2j4</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -6364,45 +6302,49 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>p10s</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>【絶オメガ】文字を読みたくない人のための絶オメガＰ３【解説】</t>
+          <t>【FF14】解説 天獄編零式2層 犬丸改FFO式</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9dyL-nSOJuA</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=B0cH0HmcPk4</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>犬丸</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>p11s</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶オメガP4 ブルースクリーン解説 The Omega Protocol P4【ぬけまる】</t>
+          <t>【FF14】解説 天獄編零式3層 アニメーション解説 Zizie式マクロ有り【ぬけまる】</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ayGtjf0__0k</t>
+          <t>https://www.youtube.com/watch?v=AsS4R1qYbGM</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -6414,49 +6356,45 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>p11s</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>【絶オメガ】ブルースクリーンをひたすら見る動画【P4】</t>
+          <t>【FF14】パンデモニウム天獄編零式3層【解説】修正版</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rPa6ei-fgJs</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=-EM-XR6qocU</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶オメガP5 コード:＊＊＊ミ＊【デルタ】 アニメーション解説 The Omega Protocol P5【ぬけまる】</t>
+          <t>【FF14】解説 天獄編零式4層前半 ぬけまる式</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vg_AEbdn2zM</t>
+          <t>https://www.youtube.com/watch?v=rgqmXnsPsAc</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -6468,49 +6406,45 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>p12s</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶オメガP5 コード:＊＊＊ミ＊【シグマ】注意点追加版 アニメーション解説 The Omega Protocol P5【ぬけまる】</t>
+          <t>【FF14】解説 天獄編零式4層後半 ぬけまる式 (パラスレイX処理)</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3x-_d8RZJXE</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=9jE9zWeWkAg</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>p9s</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶オメガP5 コード:＊＊＊ミ＊【オメガ】 アニメーション解説 The Omega Protocol P5-3【ぬけまる】修正版</t>
+          <t>【FF14】解説 天獄編零式1層 無職マラソン式【ぬけまる】</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6LIXoAk7wrI</t>
+          <t>https://www.youtube.com/watch?v=rnKHQtYCuAk</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -6522,45 +6456,49 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m5s</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>【FF14】絶オメガ検証戦 ランデュナミス解説 フェーズ5 (さらちゃんのつぶやき)</t>
+          <t>【FF14】クルーザー級零式1層 攻略解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>https://sarachantubuyaki.jp/finalfantasyxiv/run-dynamis/</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=s5CACs9ey9o</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m6s</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1-front</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>【絶オメガ】文字を読みたくない人のためのP5オメガ【解説】</t>
+          <t>世界一わかりやすいアルカディア零式クルーザー級2層解説【game8準拠】【FF14黄金】</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=316MZKSBXdc</t>
+          <t>https://www.youtube.com/watch?v=RWt1GQzv-fU</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr"/>
@@ -6568,22 +6506,22 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>top</t>
+          <t>m7s</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>【FF14/絶解説】絶オメガ最終P6 アルファオメガ 軽減付アニメーション解説 The Omega Protocol P6【ぬけまる】最新</t>
+          <t>【FF14/解説】さり式 クルーザー級零式 3層解説 GAME8準拠【ぬけまる】(M7S)</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2u_I9zYh2j4</t>
+          <t>https://www.youtube.com/watch?v=EvPn0UHMevk</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -6595,7 +6533,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>p10s</t>
+          <t>m8s</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -6605,39 +6543,39 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>【FF14】解説 天獄編零式2層 犬丸改FFO式</t>
+          <t>【FF14/解説】GAME8準拠 クルーザー級 4層 前半 解説 マクロ有【ぬけまる】(M8S-1)</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B0cH0HmcPk4</t>
+          <t>https://www.youtube.com/watch?v=Pqxs9VBKn74</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>犬丸</t>
+          <t>ぬけまるG</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m8s</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>【FF14】解説 天獄編零式3層 アニメーション解説 Zizie式マクロ有り【ぬけまる】</t>
+          <t>【FF14】クルーザー級零式 4層後半 攻略解説【ぬけまる】(M8S Part 2)</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AsS4R1qYbGM</t>
+          <t>https://www.youtube.com/@nukemarugames/videos</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -6649,80 +6587,88 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>p11s</t>
+          <t>m10s</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p1-fire</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>【FF14】パンデモニウム天獄編零式3層【解説】修正版</t>
+          <t>【FF14】ヘビー級零式2層 攻略解説 (家無しララ様)</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-EM-XR6qocU</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=PvWR-ARutLU</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>家無しララ</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m10s</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p1-fire</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>【FF14】解説 天獄編零式4層前半 ぬけまる式</t>
+          <t>【FF14】ヘビー級零式2層 攻略解説 (犬丸様)</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rgqmXnsPsAc</t>
+          <t>https://www.youtube.com/watch?v=B0cH0HmcPk4</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>ぬけまるG</t>
+          <t>犬丸</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>p12s</t>
+          <t>m11s</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>【FF14】解説 天獄編零式4層後半 ぬけまる式 (パラスレイX処理)</t>
+          <t>【FF14】ヘビー級零式3層 攻略解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9jE9zWeWkAg</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=9fMy4yJRNTM</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>p9s</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
@@ -6732,12 +6678,12 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>【FF14】解説 天獄編零式1層 無職マラソン式【ぬけまる】</t>
+          <t>【FF14】ほぼイディル式 アルカディア：ヘビー級 零式 4層前半 攻略解説 M12S Part1 Guide【ぬけまる】</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rnKHQtYCuAk</t>
+          <t>https://www.youtube.com/watch?v=Tmfv_bbDqQ8</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -6749,22 +6695,22 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>m5s</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>【FF14】クルーザー級零式1層 攻略解説【ぬけまる】</t>
+          <t>【FF14】最新修正版 アルカディア：ヘビー級 零式 4層後半 攻略解説 M12S Part 2 Guide【ぬけまる】</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s5CACs9ey9o</t>
+          <t>https://www.youtube.com/watch?v=YXxp8nrRw3o</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -6776,45 +6722,49 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>m6s</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>p1-front</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>世界一わかりやすいアルカディア零式クルーザー級2層解説【game8準拠】【FF14黄金】</t>
+          <t>【FF14/イメトレ用】アルカディアンドリームをいくつか見る動画 (ヘビー級 零式 4層後半) M12S part2 Image training【ぬけまる】</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RWt1GQzv-fU</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=lF8RJ97UWeo</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>m7s</t>
+          <t>m12s</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>【FF14/解説】さり式 クルーザー級零式 3層解説 GAME8準拠【ぬけまる】(M7S)</t>
+          <t>【FF14】アルカディア：ヘビー級 零式 4層後半 攻略解説 M12S Part2 Guide【ぬけまる】(初版)</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EvPn0UHMevk</t>
+          <t>https://www.youtube.com/watch?v=Fl1nPBxcPpM</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -6826,7 +6776,7 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>m8s</t>
+          <t>m9s</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
@@ -6836,12 +6786,12 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>【FF14/解説】GAME8準拠 クルーザー級 4層 前半 解説 マクロ有【ぬけまる】(M8S-1)</t>
+          <t>【FF14】ヘビー級零式1層 攻略解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Pqxs9VBKn74</t>
+          <t>https://www.youtube.com/watch?v=m4_8a0N8GcM</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -6853,88 +6803,84 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>m8s</t>
+          <t>m9s</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>【FF14】クルーザー級零式 4層後半 攻略解説【ぬけまる】(M8S Part 2)</t>
+          <t>【FF14】アルカディア零式ヘビー級１層 世界一わかりやすい解説【game8対応】</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@nukemarugames/videos</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=S_bhkYVN5Yk</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>m10s</t>
+          <t>m1s</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>p1-fire</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>【FF14】ヘビー級零式2層 攻略解説 (家無しララ様)</t>
+          <t>【FF14】アルカディア零式：ライトヘビー級1層 攻略解説【犬丸】</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PvWR-ARutLU</t>
+          <t>https://www.youtube.com/watch?v=S1SBXo9tLfo</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>家無しララ</t>
+          <t>犬丸</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>m10s</t>
+          <t>m1s</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>p1-fire</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>【FF14】ヘビー級零式2層 攻略解説 (犬丸様)</t>
+          <t>【FF14】アルカディア零式：ライトヘビー級1層 攻略解説【ゴールデンたけし】</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B0cH0HmcPk4</t>
+          <t>https://www.youtube.com/watch?v=9dCWOvx9Mqw</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>犬丸</t>
+          <t>ゴールデンたけし</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>m11s</t>
+          <t>m1s</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
@@ -6944,24 +6890,20 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>【FF14】ヘビー級零式3層 攻略解説【ぬけまる】</t>
+          <t>【FF14】アルカディア零式ライトヘビー級１層【解説】</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9fMy4yJRNTM</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=zNQCr7QBUEw</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>m12s</t>
+          <t>m1s</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
@@ -6971,12 +6913,12 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>【FF14】ほぼイディル式 アルカディア：ヘビー級 零式 4層前半 攻略解説 M12S Part1 Guide【ぬけまる】</t>
+          <t>【 FF14 / 解説 】アルカディア零式：ライトヘビー級零式1 マクロ</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Tmfv_bbDqQ8</t>
+          <t>https://nukemarugames.com/2024/07/31/%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A%E9%9B%B6-2/</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -6988,22 +6930,22 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>m12s</t>
+          <t>m2s</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>【FF14】最新修正版 アルカディア：ヘビー級 零式 4層後半 攻略解説 M12S Part 2 Guide【ぬけまる】</t>
+          <t>【FF14】アルカディア零式：ライトヘビー級2層 攻略解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YXxp8nrRw3o</t>
+          <t>https://www.youtube.com/watch?v=p9tE-x0XEC4</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -7015,22 +6957,22 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>m12s</t>
+          <t>m2s</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>【FF14/イメトレ用】アルカディアンドリームをいくつか見る動画 (ヘビー級 零式 4層後半) M12S part2 Image training【ぬけまる】</t>
+          <t>【 FF14 / 解説 】アルカディア零式：ライトヘビー級零式2 マクロ</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lF8RJ97UWeo</t>
+          <t>https://nukemarugames.com/2024/07/31/%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A%E9%9B%B6/</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -7042,22 +6984,22 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>m12s</t>
+          <t>m3s</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>【FF14】アルカディア：ヘビー級 零式 4層後半 攻略解説 M12S Part2 Guide【ぬけまる】(初版)</t>
+          <t>【FF14】アルカディア零式：ライトヘビー級3層 攻略解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Fl1nPBxcPpM</t>
+          <t>https://www.youtube.com/watch?v=zZDu5NY7DIo</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -7069,7 +7011,7 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>m9s</t>
+          <t>m3s</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
@@ -7079,12 +7021,12 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>【FF14】ヘビー級零式1層 攻略解説【ぬけまる】</t>
+          <t>【 FF14 / 解説 】アルカディア零式：ライトヘビー級零式3 マクロ</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m4_8a0N8GcM</t>
+          <t>https://nukemarugames.com/2024/08/01/%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A%E9%9B%B6-3/</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -7096,7 +7038,7 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>m9s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
@@ -7106,20 +7048,24 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>【FF14】アルカディア零式ヘビー級１層 世界一わかりやすい解説【game8対応】</t>
+          <t>【 FF14 /Game8準拠解説】DN式円輪,輪円+くうや アルカディア零式：ライトヘビー級4前半解説 マクロ有【ぬけまる】最終改定 M4S</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=S_bhkYVN5Yk</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=gl4BNKLr3rk</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>ぬけまるG</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>m1s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
@@ -7129,74 +7075,74 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>【FF14】アルカディア零式：ライトヘビー級1層 攻略解説【犬丸】</t>
+          <t>【FF14】アルカディア零式ライトヘビー級４層前半【解説】</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=S1SBXo9tLfo</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>犬丸</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=zEvghGfSkVM</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>m1s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>【FF14】アルカディア零式：ライトヘビー級1層 攻略解説【ゴールデンたけし】</t>
+          <t>【FF14】アルカディア零式ライトヘビー級4層後半 攻略解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9dCWOvx9Mqw</t>
+          <t>https://www.youtube.com/watch?v=YXxp8nrRw3o</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>ゴールデンたけし</t>
+          <t>ぬけまるG</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>m1s</t>
+          <t>m4s</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>【FF14】アルカディア零式ライトヘビー級１層【解説】</t>
+          <t>【FF14】後世のためにライトヘビー級4層零式の”正解”を書き記す【LH4層零式】</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNQCr7QBUEw</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr"/>
+          <t>https://note.com/mokatamk/n/n92368fe90e97</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Mokatamk</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>m1s</t>
+          <t>fru</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
@@ -7206,66 +7152,66 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 / 解説 】アルカディア零式：ライトヘビー級零式1 マクロ</t>
+          <t>P1 フェイトブレイカー解説【Lucrezia】</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>https://nukemarugames.com/2024/07/31/%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A%E9%9B%B6-2/</t>
+          <t>https://youtu.be/m1dMWTvdPiI?si=6sABigdyc8BatT0A</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>ぬけまるG</t>
+          <t>Lucrezia</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>m2s</t>
+          <t>fru</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>【FF14】アルカディア零式：ライトヘビー級2層 攻略解説【ぬけまる】</t>
+          <t>P2～2.5 シヴァ･ミトロン～光の氾濫解説【しのしょー】</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=p9tE-x0XEC4</t>
+          <t>https://youtu.be/u7yy2BMyaIU?si=Qe7CLMrmnnktrXNC</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>ぬけまるG</t>
+          <t>しのしょー</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>m2s</t>
+          <t>fru</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 / 解説 】アルカディア零式：ライトヘビー級零式2 マクロ</t>
+          <t>P3-1 時間圧縮・絶 解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>https://nukemarugames.com/2024/07/31/%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A%E9%9B%B6/</t>
+          <t>https://youtu.be/oKSHteslL2w?si=IEF3cPBdEPmxD1q0</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -7277,22 +7223,22 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>m3s</t>
+          <t>fru</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>【FF14】アルカディア零式：ライトヘビー級3層 攻略解説【ぬけまる】</t>
+          <t>P3-2 アポカリ解説 安置基準&amp;アポカリ基準【ぬけまる】</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zZDu5NY7DIo</t>
+          <t>https://youtu.be/4gWtS7GWiFQ?si=KQ39y1ZDNZixEut-</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -7304,22 +7250,22 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>m3s</t>
+          <t>fru</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 / 解説 】アルカディア零式：ライトヘビー級零式3 マクロ</t>
+          <t>P4 2体フェーズ解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>https://nukemarugames.com/2024/08/01/%E3%80%90-ff14-%E8%A7%A3%E8%AA%AC-%E3%80%91%E3%82%A2%E3%83%AB%E3%82%AB%E3%83%87%E3%82%A3%E3%82%A2%E9%9B%B6%E5%BC%8F%EF%BC%9A%E3%83%A9%E3%82%A4%E3%83%88%E3%83%98%E3%83%93%E3%83%BC%E7%B4%9A%E9%9B%B6-3/</t>
+          <t>https://youtu.be/nX2kfaMnCiU?si=jF80rhVAJCnm_0ZV</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -7331,264 +7277,25 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>m4s</t>
+          <t>fru</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>【 FF14 /Game8準拠解説】DN式円輪,輪円+くうや アルカディア零式：ライトヘビー級4前半解説 マクロ有【ぬけまる】最終改定 M4S</t>
+          <t>P5 パンドラ・ミトロン ギミック解説【ぬけまる】</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gl4BNKLr3rk</t>
+          <t>https://youtu.be/nzpOdfOyUNo?si=PNFVTdyQv87FH4Zk</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>【FF14】アルカディア零式ライトヘビー級４層前半【解説】</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zEvghGfSkVM</t>
-        </is>
-      </c>
-      <c r="E108" s="8" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>【FF14】アルカディア零式ライトヘビー級4層後半 攻略解説【ぬけまる】</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=YXxp8nrRw3o</t>
-        </is>
-      </c>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>【FF14】後世のためにライトヘビー級4層零式の”正解”を書き記す【LH4層零式】</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t>https://note.com/mokatamk/n/n92368fe90e97</t>
-        </is>
-      </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>Mokatamk</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>P1 フェイトブレイカー解説【Lucrezia】</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t>https://youtu.be/m1dMWTvdPiI?si=6sABigdyc8BatT0A</t>
-        </is>
-      </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t>Lucrezia</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>P2～2.5 シヴァ･ミトロン～光の氾濫解説【しのしょー】</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>https://youtu.be/u7yy2BMyaIU?si=Qe7CLMrmnnktrXNC</t>
-        </is>
-      </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>しのしょー</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>P3-1 時間圧縮・絶 解説【ぬけまる】</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t>https://youtu.be/oKSHteslL2w?si=IEF3cPBdEPmxD1q0</t>
-        </is>
-      </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t>P3-2 アポカリ解説 安置基準&amp;アポカリ基準【ぬけまる】</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t>https://youtu.be/4gWtS7GWiFQ?si=KQ39y1ZDNZixEut-</t>
-        </is>
-      </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>P4 2体フェーズ解説【ぬけまる】</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>https://youtu.be/nX2kfaMnCiU?si=jF80rhVAJCnm_0ZV</t>
-        </is>
-      </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまるG</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>P5 パンドラ・ミトロン ギミック解説【ぬけまる】</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t>https://youtu.be/nzpOdfOyUNo?si=PNFVTdyQv87FH4Zk</t>
-        </is>
-      </c>
-      <c r="E116" s="8" t="inlineStr">
         <is>
           <t>ぬけまるG</t>
         </is>
@@ -8414,7 +8121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8454,3302 +8161,6 @@
       <c r="F1" s="7" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>shin-mintotto-h3</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>新みんとっと / H3構成 / 拘束具逆▽ (野良主流)</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2024-09 にりりーどーる Lodestone マクロが「みんとっと → 新みんとっと」へ
-切替わったタイミングで野良主流が刷新された。
-H3 構成 (ヒーラー 3) + 拘束具を逆三角形 (▽) 配置で災厄ギミックの視認性を上げる流派。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>t3-mintotto</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>T3構成 みんとっと (代替・旧主流)</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実装初期からの「みんとっと」(タンク 3) 構成。
-現在も一部固定で採用される代替流派。
-# 出典: https://na.finalfantasyxiv.com/lodestone/character/18500174/blog/4804267/
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>kata-tlb</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>カータTLB (新みんとっと)</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">カータライズ (Cauterize / 直線ダイブ) のタイミングで タンク LB3 を発動し
-パーティ全体のダメージを軽減する野良主流処理。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>shingun-juuji</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>進軍十字 (Quickmarch Trio)</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">進軍の三重奏 (Quickmarch Trio) の野良主流処理。
-十字状の配置でアースシェイカー / メテオストリーム / Dive を捌く。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>rengeki-v</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>連撃V字 (Tenstrike Trio)</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">連撃の三重奏 (Tenstrike Trio) の野良主流処理。
-魔力錬成 (Generate) 対象 3 名を V 字に配置して拘束具誘導 + 散開を両立。
-# 出典: https://asellog.com/bahamut-p3tl3/
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>gunryu-tlb</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>群竜TLB (Grand Octet)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">群竜の八重奏 (Grand Octet) の最終ギミック。
-メガフレアダイブのタイミングでタンク LB3 を発動し、頭割りマーカーを無視できる
-「マラソン処理」の野良主流。プライムの東西南北位置で時計/反時計回りを分岐。
-# 出典: https://asellog.com/bahamut-p3tl3/
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>ucob</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>gold-bahamut-final</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>金バハ最終処理 (新みんとっと / ボス足元集合)</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">モーン・アファーはボス足元集合で全員均等に受ける。
-アク・モーンは MT/ST 無敵切替で対応。
-エクサフレアの安置 (8 方向ランダム) は床マーカーをパーティで分担コールする。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>dome-shori</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>ドーム処理 (低気圧)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">低気圧 (サーマルロウ/メソハイ) の被弾優先度を「ST &gt; ST/H1/H2/D3/D4 &gt; D1 &gt; D2」で
-回す野良主流処理法。初動 ST 受けで誘導距離を最小化する。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>mesohigh-mt-cast</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>メソハイ MT キャス担当</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">メソハイ線取りを D 側に D4、B 側に MT (キャスター MT 想定) で取る流派。
-みんとっと動画準拠で野良主流。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>kusabi-gyaku-z</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>楔:逆Z (野良主流)</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">炎獄の楔を逆 Z 字配置で①〜④の順に破壊する流派。
-①D1 / ②D2 / ③D3 / ④D4 が担当。
-D3D4 はエラプ誘導から楔へ。みんとっと動画準拠。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>jail-jimetsu</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>ジェイル自滅式 (4連スキップ)</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">重み 2 回目で ST/D1/D2/D3 が自滅して人数を減らし、
-3 連ジェイル + 4 連ジェイルを処理する野良主流。
-蘇生先は H1-&gt;ST / H2-&gt;D1 / D4-&gt;D2,D3。
-みん学 (4連スキップ) ジェイル自滅 TLB 法プレイリスト参照。
-Source: https://www.youtube.com/playlist?list=PL2Hitw4uipFQQ8svogk788A9eWSPtz33M
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>juuji-mushi</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>十字無視法 (安置判定)</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">十字範囲攻撃を安置判定で無視して位置取りを最適化する流派。
-フェザーレイン回避方向は ★ -&gt; A -&gt; D。
-ジェイル破壊はフェザーレイン回避時にターゲット可能。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>san-ichi-ichi-ichi</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>3111 (緑玉 3-1-1-1 配分)</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">緑玉(エメラルドレディアンス)を 3-1-1-1 で配分する野良主流。
-1 回目は MT/ST/D1 / 2-4 回目は MT が処理。
-爆撃 P メソハイは 1 回目 D3 / 2 回目 灼熱ヒラ。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>ranhageki-tlb</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>乱撃 TLB (タンクLB3 顔面受け)</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">乱撃を ST のタンク LB3 (顔面受け) で処理する野良主流。
-D マーカー誘導 -&gt; 外周避け + ST メソハイ -&gt; D 集合。
-MT がアルテマ詠唱 LB3、ST がエーテル波動 LB1 を担当。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>final-3-primals</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>最終三蛮神ルーレット (3パターン分岐)</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最終三蛮神はガルーダ/イフリート/タイタンのスタートがランダム。
-①ガルーダスタート (イフ→タコ)
-②イフリートスタート (ガル→タコ)
-③タイタンスタート (イフ→ガル)
-各パターンで移動ルートが異なる。スプリントをイフリート処理に合わせる。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>yarkt-mushi-20</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>ヤークト無視 (20秒バースト / 野良主流)</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">リキッドフェーズ 2分20秒の時間切れを 1分9秒以内に本体だけ全力で殴り切る手法。
-HP均等化を行わず、ペイン大ダメージを軽減とバリアで耐える。
-ふうcだよが図解＋解説動画でまとめている派生も含む。野良の現在主流。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>dice-1211</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>サイコロ 1211 (野良主流)</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイコロ (Throttle) 1番→2番→1番→1番 の順で爆発位置を踏み替えていく処理。
-東西スタートの場合は東側優先。1211式 = 最初の爆発中心を通る線を0本目として、
-1本先 / その2本先 / さらに1本先 / さらに1本先で処理する命名。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>dice-44-separate</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>サイコロ 4:4 セパレ式 (派生)</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ぬけまる「リキッドセパレ式」動画で解説される 4:4 分割の派生処理。
-1211 より遭遇率は低いが固定で採用するケースあり。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>nisi-hira-saki</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>ナイサイ ヒラ先渡し (野良主流)</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ナイサイ (Judgment Nisi) 受け渡しを「ヒラが先に渡してから DPS が処理」する流派。
-1回目DPS反時計受け渡し、3回目は一列 (A｝MT・D1・D3・D4・D2・ST｛C)、
-4回目はタンヒラが先に並ぶ (MT・H1・H2・ST｛氷)。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>super-jump-d3-yuudou</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>スーパージャンプ D3 誘導 (野良主流)</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">スーパージャンプ誘導を D3 が担当する標準処理。地雷は D3:5時 / ST:6時 配置。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>jikan-teishi-nooshi</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>時間停止 脳死法 (野良主流)</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">時間停止 (Temporal Stasis) を「無印→左側ロボ、緑線→右側ロボ、青線TH左/青線D右、
-雷→ジャスの側面」で機械的に処理する脳死法。
-ジャス左側/右側で散開図がミラー反転する。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>dansetsu-hamukatsu-34-kotei</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>断絶 ハムカツ式 34固定 (野良主流)</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">次元断絶のマーチを「ハムカツさん34固定方式」で処理する流派。
-ぬけまる「ハムカツさん34固定方式 各視点有」動画で詳細解説。
-懴悔順は 5,6 → 7,8 → 1,2。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>mirai-kansoku-alpha-beta</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>未来観測 α/β 北南頭割り (野良主流)</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未来観測 α/β を「黄親→北頭割り / 紫親→南頭割り」で処理する流派。
-α: ボス側安置=名誉罰 / 対面側安置=左集団罰+他, 右加重罰。
-β: 接触保護(黄親)→北寄り北西, 接触禁止(黄子)→2左上, 等の細かい配置あり。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>kakutei-hanketsu-kihon</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>確定判決 基本散開 (野良主流)</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">確定判決を「黄親→4 / 紫親→2 / 他6人→2左側」で処理。
-頭割り TH北/DPS南、散開は MT ST / H1 H2 / D3 D1 D2 D4 配置。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>p1s</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>pair-adjust-game8</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>ペア調整 / 氷火 MT・D3 交代式 (Game8 採用)</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が公式採用している野良主流処理法。
-- 結呪調整ペア: MTD4 / H2D2 / STD1 / H1D3 (マーカー色基準)
-- 紫色マーカー: 秒数の短い順に ABCD
-- 赤色マーカー: 秒数の短い順に 1234
-- 氷火の侵食: MT/D3 が調整役 (2 回目で属性を必ず変更し、3 回目で調整)
-- 時限の魔鎖: 対象者は光、他は火を取る
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>p2s</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>game8-standard</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Game8 採用版 (基本散開 / サイコロマーカー方式)</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が公式採用している野良主流処理法。
-- ショックウェーブ: MT 組 (MT/H1/D1/D2) ボス下 / ST 組 (ST/H2/D3/D4) 通路
-- チャネリングフロウ: 十字配置で TH/DPS 互い違い
-- 多重刻印 1 回目: T が左、頭割り中央、DPS が右
-- 多重刻印 2 回目: T 角に / DPS は内側
-- カンペオスハルマ: 青サイコロ 1・3 → ボス対角 / 2・4 → ボス下、紫は数字マーカー基準
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>p3s</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>inumaru-shinoshow-hapioji</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>基本犬丸 + 闇の炎 X 字 (しのしょー) + 霊泉ハピおじ式 (Game8 採用)</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 採用流派。複数の野良流派を融合した形。
-- 4:4 分け: MT 組 (MTH1D1D3) / ST 組 (STH2D2D4)
-- 闇の炎設置ペア (X字): D3/MT → ① / D4/ST → ② / D1/H1 → ③ / D2/H2 → ④
-  サイコロ数字マーカー、時計回りに炎を倒す
-- 十字走火: 大玉/小玉は基本北西へ走る、北東に出た場合は北東
-- 突進中央散開: ボスから MT/D3 → H1/D1 → H2/D2 → ST/D4
-- 突進左右散開: ←TH / DPS→ (縦の並びは中央散開)
-- 雑魚誘導: MT 組 北→西 / ST 組 東→南
-- 雑魚突進: 線 2 本 → 繋がってる鳥の対角の時計回り、線 1 本 → 繋がってるペアの対角
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>p4s</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>ypp-style-game8</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>YPP 式 (毒線 YPP 緑玉脳死) - Game8 採用版</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 採用流派。
-- 基本散開: 標準 8 人配置
-- 毒線 YPP 式: TH 北 / DPS 南、塔線時計回り (線ぐるぐる)
-- ピナクス炎 頭割り: MTH1 / STH2 / D1D3 / D2D4 ペア
-- ピナクス炎 シフト後: 敵正面 MTH1D1D3 / 敵背面 STH2D2D4
-- ピナクス毒 散開: MT 中央誘導、遠隔は外周
-- 緑玉脳死: 十字配置で MTH2→D3 / STH1→D4 / D1D3→MT / D2D4→H1
-  上記の玉を取った後、時計回りで処理
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>p4s</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>inumaru-style-game8</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>犬丸式 (Game8 採用版・第三幕)</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 採用流派。第三幕アースシェイカー誘導に「犬丸式」を採用。
-- 序幕: 標準散開 (D3/D4 北、MT/ST 中段、D1/D2 / H1/H2 南)
-- 第二幕: 1 番目に T ダージャ北西 / H ダージャ南東で切り、エアロガ北西、
-  D ファイガ南東、DPSファイガ移動は時計回り D1→D2→D3→D4 反時計回り
-- 第三幕 (犬丸式): アースシェイカー誘導は ST が左/D1 が中央/その他右
-- 第四幕: ウォタガは塔の対角の 1 つ時計回り側で切り、ダージャは自塔の時計回り側塔を踏む
-  → 南西集合し北のダージャから時計回り処理
-- 終幕: ボス基準散開 + 塔配置
-- カーテンコール: TH 6 秒切り / D 11 秒切り (メモ: 13/23/33/43)
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>p4s</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-style</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 並列掲載)</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 ページ上で犬丸式と並列掲載されている別流派。
-主に第三幕の処理が異なる。詳細はぬけまる動画参照。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>ririd-style-p1</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>リリド式 P1 (MTアデル/STグリノー/線ST無敵/沈黙 MT→レンジ→MT)</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">りりーどーる版野良主流。
-- MTアデルフェル / STグリノー固定
-- ホーリーブレードダンス線は ST 無敵で受ける
-- ホリエストブレッシング詠唱は沈黙でキャンセル: MT→レンジ→MT の順
-- プレステ散開: 北基準で◯×△□マーカーをロール固定で散開
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>ririd-style-p2</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>リリド式 P2 (ゼフィラン基準散開/隕石ハムカツ式)</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">りりーどーる版野良主流。
-- 雷槍: MT組 D-1 / ST組 B-3 で扇配置
-- 聖杖: ゼフィラン基準でペア (MTST/H1H2/D1D2/D3D4) を組み、剣1+MT組はゼフィラン対角、剣2+ST組はゼフィラン後ろ
-- 隕石（ホーリーコメット）: ハムカツ式（南北スタートで7回設置）
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>iru-d-spa-b</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>イル↓D・スパ↑B固定 (リリド式)</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイコロ番号と塔配置を固定する野良主流。
-- イルーシブジャンプ↓: D ライン担当
-- スパインダイブ↑: B ライン担当
-- サイコロ②③は北でアピール、①は中央配置
-- 4塔近接調整: 近接ジョブが移動調整、優先度は時計回り&gt;反時計回り&gt;対角
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-nidhogg</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (ニーズフェーズ図解版)</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ぬけまる動画準拠の処理法。サイコロ全パターンの視点動画あり。
-固定の流派として選ばれることもある。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>kinsetsu-aoi-yose</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>近接青眼寄せ (リリド式)</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">近接ジョブが青眼に寄って効率的にダメージを与える野良主流。
-- 黄玉: DPS / 青玉: TH 担当
-- 黄玉後: 邪眼南北で受け渡し
-- ミラージュダイブ: 青眼集合、交代順は ①②③④優先順位
-- 1回目: ①D1&gt;D2④ / 2回目: ①D3&gt;D4④ / 3回目: ①MT&gt;ST&gt;H2&gt;H1④
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>komazou-shiki-kai</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>こまぞう式改 (野良主流死刻処理)</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">現在もっとも採用されている主流処理法。
-イディル式とこまぞう式のハイブリッドで、基本動作はこまぞう式、
-散開座標はイディル式を採用。
-死の宣告解放点を固定し、ツイスターを意識する必要を最小化する。
-散開優先度: D4&gt;D3&gt;D2&gt;D1&gt;ST&gt;MT&gt;H1&gt;H2 (※固定により変動あり)
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>komazou-w3rd</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>こまぞう式 (W3rd / オリジナル)</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">オリジナル「こまぞう式」。W3rd クリアチームの流派。
-散開優先度は D4MTSTD1D2D3H1H2 系統。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>idyll-shiki</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>イディル式 (旧主流)</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旧主流処理法。現在は「こまぞう式改」に取って代わられているが
-固定によっては依然採用されることもある。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>okome-style-p6</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>おこめ式（息吹1回目） / 脳死（息吹2回目） / 南三角</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">野良主流の二天竜処理。
-- ニーズ担当: MT H1 D1 D3 / フレース担当: ST H2 D2 D4
-- 息吹1回目: おこめ式（調整: H2 D2 D3、初期配置で散開）
-- 息吹2回目: 脳死配置（A基準で北側にMT、フレース側に頭割り集合）
-- 南三角: 初期散開から「赤線と青線を1対ずつ3ペアに分けて処理」、
-  動くのは2名のみで効率的
-- 滅殺の誓い受け渡し順: DPS→MT→ST→近接(D1優先)→D3
-- 邪念の炎: ←MT ST D1 D2 D3 D4 H1 H2→ の優先順位で白+(無)/紫を配置
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>acmorn2-tlb3</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>アクモーン2回目 TLB3 (リリド式)</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">野良主流の最終フェーズ処理。
-- アクモーン2回目で タンク LB3 を発動
-- エクサ→アクモーン→ギガフレア の 3 周構成（3 周目はギガフレアなし）
-- トリニティ AA 受け順: エクサ後→H1/H2 / アクモーン後→D1/D2 / ギガ後→D3/D4
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>dsr</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>tate-yoke</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>エクサ縦避け（フィールド模様基準）</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARUTORA 推奨のエクサフレア処理法。
-ボスを北または南に向けた状態で、最初の爆発後に中心に移動、
-その後ひし形の床模様の頂点へ移動する縦避け方式。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>p5s</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が採用しているぬけまる氏解説に準拠した処理法 (マクロVer2)。
-- 基本散開: 北 D3/MT/D4、中央 H1/H2、南 D1/ST/D2
-- 十字毒塔: MTが無敵受け、H1D3 / H2D4 / D1D2 で塔処理 (STフリー)
-- 毒石ペア: MTST/H1D3 は 12時から反時計回り、D1D2/H2D4 は 1時から時計回り
-- ベノムサージ/スプラッシュ: 西/内壁に MT組 (MTH1D1D3)、東/外壁に ST組 (STH2D2D4)
-- 毒沼+ベノムスコール: マーカー1or4 に出た毒に MT組、2or3 は ST組
-- 4部屋ベノムスプラッシュ: 3個部屋の対角に逃げる
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>p6s</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が採用しているぬけまる氏解説に準拠した処理法 (マクロVer1)。
-- MT組: MTH1D1D3 / ST組: STH2D2D4
-- 基本散開: 北 MT/D3, ST/D4 / 南 H1/D1, H2/D2 / 中央 ★
-- 頭割り+扇範囲: 西 MT組 / 東 ST組 (時計回りで頭割り)
-- サイコロ: 西 奇数 / 東 偶数
-- カヘキシー1回目: 内周20→外周16→中央8の数字配置でAOE誘導
-- カヘキシー2回目: 西 紫デバフ / 東 緑デバフ、北南外周マス→AoE、内周マス→頭割り
-- チェンジバースト2回目: 西→T・H / 東→DPS (AOEも上記方向に捨てる)
-- 4:4頭割り: 西側→MT組、東側→ST組 (内周4マスを使用)
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>p7s</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 採用版 - 獄8人 凶無敵 乱犬丸)</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が採用しているぬけまる氏解説に準拠した処理法 (マクロVer1.5)。
-- MT組: MTH1D1D3 / ST組: STH2D2D4
-- 基本散開: 北 MT/D1, ST/D2 / 南 H1/D3, H2/D4 / 中央 ★
-- ノックバック + 鳥: 中央列に MT/ST、上下に D1-D4、両通路を H1/H2
-- 生命の果実 (頭割り): 北側 MT組 / 南側 ST組
-- 魔印創成 (散開): 基本散開準拠、頭割りと被ったら通路へ
-- エクサ + 頭割り: 西 MT組 / 東 ST組
-- 鳥誘導 + 塔: 基本散開準拠でズレたら時計回り
-- 魔印創成【獄】: 西島/東島で対称配置 (頭割り MT/D1 / ST/D2 / H2/D4 / H1/D3 / 通路)
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>p8s</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8-ffo</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 採用版 - FFO式)</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が採用しているぬけまる氏解説 + 野良標準「FFO式」処理法 (マクロVer1)。
-- 基本散開: 北 D3 MT D4 / 中 H1(H2) ST / 南 D1 H2 D2
-- テトラオクタ/誘導/蛇2: MT/D3 → ST/D4 / H1/D1 ← H2/D2 の4方向誘導
-- イントゥシャドウ(1回目): 蛇は北から時計回り MTD1 &gt; STD2 &gt; H1D3 &gt; H2D4
-- フェイタルストンプ: 1,3回目→1(北西), 2,4回目→中央, 待機→A(北)
-- 幻影創造: 竜竜×散開 or フェニ×散開 でパターン分岐
-- 四重炎嵐: 縦横/角 の2パターン、頭割りは近H位置 (MTD1/STD2/H1D3/H2D4)
-- イントゥシャドウ(2回目): 4:4頭割り、デバフ持ち 北西&gt;MT/D1&gt;...&gt;H2/D4&gt;南東、無職は北西TH/南東DPS
-- テトラ/ディフレア: テトラは(ボス)MT/D1&gt;ST/D2&gt;H1/D3&gt;H2/D4、ディフレアは(ボス)MTH1D1D2&gt;STH2D3D4
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>p8s</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8-haijia</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 採用版 - はいじあ式 / ビジョン式)</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が採用しているぬけまる氏解説 + ビジョン式「万象灰燼処理法」(マクロVer1)。
-- 術式1回目: 頭割りは西、紫 ST、★中央 / D1 MT D2 / H1 H2 / D3 ST D4
-- 術式炎氷: TH西 DPS東 / 炎は中央前詰め MT&gt;ST&gt;H1&gt;H2、氷誘導 西 D1&gt;ST / 東 MT&gt;D2
-- 術式2回目散開: STMT 紫 D3D1 / H1H2D4D2
-- 概念1回目①: 早α/早β/早γ + 複/遅α/重/遅βγ → 配置
-- 概念1回目②: 遅α/遅β/遅γ + 生物 → 配置
-- 4塔合成: 遅αβγ→北で合成、複/重/早余り→南で合成
-- 万象灰燼 (はいじあ/ビジョン式): MT/D1 ST/D2 H1/D3 H2/D4 の +位置
-  * 1,3番塔は前+で範囲捨て、2,4番塔は後+で範囲捨て
-- 概念2回目①: 無/早α + 単 + 早β/複/遅 + 早γ → 配置
-- 概念2回目②: 遅α + 生物 + イフ + 遅β + 遅γ → 配置
-- 4塔合成 (2回目): 遅αβ→北で合成、遅γ/早余り→南で合成
-- 支配者の一撃: MTH1 D3 D1 / ST H2 D4 D2 の配置
-- 塔優先度: 西&gt;MTSTH1H2D4D3D2D1&gt;東
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>south-shuhgo-clockwise</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>南集合・11.5時時計回り (リリド式 / 野良主流)</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サークルプログラムは南集合、北11.5時を基準に時計回りで
-H1MTSTD1D2D3D4H2 の順で塔踏み・線処理。
-パンクラは北(東)→南(西)へ H1MTSTD1D2D3D4H2 で並ぶ。
-ミサイル前方・頭割り後方が基本。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>shimokara-chosei</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>下から調整 / 男三人基準 (リリド式 / 野良主流)</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">連携プログラムPTは全て下から調整。
-4:4 吹き飛ばしは男三人を基準に西を左組、南or東を右組として
-右組が調整役を担当。
-プレステはファーを右組が調整。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>ast-shiki</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>アスト式 (検知式波動砲・優先TDH)</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3 検知式波動砲の野良主流処理。
-優先順位は ①❶＞MTSTD1234H12＞❸⑤ で組分け、AC縦列はボスモニター無い方へ。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>cross-shiki</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>十字式 (検知式波動砲)</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">十字状の配置で安置を作る代替流派。ぬけまる「P3 検知式波動砲 十字式イメトレ」動画で解説。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>hello-world-far-near</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>ハローワールド：ファー→ニアー線渡し (野良主流)</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">塔組外側・線組内側ルートで移動。
-塔は早い者勝ち、線受け渡しは貰いに行く、
-線処理はファー→ニアー、4回目のみニアー→ファー。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>shitachoukei-d1d2</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>下調整・D1D2人数調整 (野良主流)</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MT/ST 上、D3/D4 左右、H1/H2 中段、D1/D2 下段、
-頭割りは下調整、人数調整は D1D2 が担当。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>delta-hamukatsu</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>デルタ：ハムカツ式 (野良主流)</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P5 デルタの主流処理。ロケパンは内側調整、❶❷ニア / ①②ファー。
-線切りタイミング、アーム/バッシュ誘導、ハロワ散開も含む。
-りりーどーる更新履歴によると 2023/3/18 にハムカツ式へ統一。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>sigma-ryonme-tower-wingwan</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>シグマ：りょんめ式 (塔Wingwan / 野良主流)</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P5 シグマの塔踏み処理は「りょんめ式 (塔Wingwan)」が野良主流。
-# 出典: 要調査 (Hanabi note より名称のみ抽出 / 詳細マクロは要手動補完)
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>omega-nukemaru</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>オメガ：ぬけまる式 (ボス検知＆虫オメガ北基準)</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P5 オメガの野良主流処理。ボス検知＆虫オメガ北基準で配置。
-マーカー付与の優先順位：1回目 II+ディナミス2&gt;ディナミス2&gt;ディナミス1、
-2回目 ディナミス3&gt;ディナミス2。★ハロワファー、◆ハロワニア。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>hamukatsu-cosmo-arrow</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>ハムカツ式 (コスモアロー波動砲処理)</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P6 コスモアロー波動砲処理。
-Hanabi note (note.com/hana25o) で「安定する」と評される野良主流。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-p6</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (P6 全般)</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ぬけまる P6 解説動画準拠の処理。コスモダイブ・波動砲・コスモメテオ・
-マジックナンバーを含む最終フェーズ全般の流派。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>p10s</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>inumaru-ffo</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>犬丸改FFO式 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が採用している犬丸様の攻略動画ベースの処理法。
-- 尖脚: 左 MT / 右 ST
-- グランドウェブ: 左 H / 右 DPS
-- パンデモニックピラー: ST H1 MT // D1 H2 D2 // D3 D4 など細かい配置あり
-- スピットウェブ: MT/ST 北側、内側 D1/D2、H1 中央、外側 D3/D4、H2 南
-- ヘビーウェブ (1回目): 左 TH / 右 DPS、扇北向け、頭割り南で横並び、線クロスしない
-- ボンド (西島/片面/震撃): MT D1 / ST D2 / H1 D3 / H2 D4 縦並び
-  ダブル: MTD1 STD2 H1D3 H2D4
-  クアドラ: MTSTH1H2 / D1D2D3D4
-  タッチダウン時は西島に8人入って処理
-- タレット: 西 H1MT→D3MT→D1MT→MT / 東 H2ST→D4ST→D2ST→ST
-  3番レーザーは4番タレットに向けて角度調整
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>p10s</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-shingeki</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる様 魔殿の震撃ボンド (補足)</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">魔殿の震撃ボンドの処理法だけ別解として記載されているもの。
-- ダブル(22) MT組:ST組: D1 MT ST D2 / D3 H1 H2 D4
-- クアドラ(44) TH組:DPS組: MT ST D1 D2 / H1 H2 D3 D4
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>p11s</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>hamukatsu-zizie</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>ハムカツ様準拠 + ジジー式調停 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 採用流派。基本散開・配置はハムカツ様準拠。光と闇の調停はジジー式。
-- ボスを見る場合以外は北 (A) 基準で散開
-- MT組: MTH1D1D3、ST組: STH2D2D4
-- 基本散開: D3/MT/D4 // H1/★/H2 // D1/ST/D2
-- アップヘルド闇/ペア散開: MTD3, H1D1/H2D4, STD2 (十字形)
-  * 闇ジューリー → DPS時計回り
-  * 塔 X字 → 反時計回り
-- 魔法陣 &amp; 戒律:
-  * 初動 MT組:西待機 / ST組:東待機
-  * 魔法陣ディスミサル闇 / 戒律闇ディバイドはボスを見て
-    左: MTD3/STD2 / 右: H1D1/H2D4
-  * 戒律の闇線 → T線: A マーカー / 光: ボス中央
-- ライトストリーム後ディバイド: ボスを見て MT組:左 / ST組:右
-- 光と闇の調停 (ジジー式): 光→TH:西側/DPS:東側、闇→TH:東側/DPS:西側
-- 調停ディバイド: 近マーカー待機→位置確定後時計回り
-- ダークストリーム: MT組:北西 / ST組:南東、内:近接(T側) / 外:遠隔(H側)
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>p11s</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>shinosho-xshiki</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>しのしょー式 (X字処理 - アップヘルド闇)</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">アップヘルド闇の処理で十字 (ハムカツ式) ではなく X字を採用する流派。
-Game8 ページに「別解」として注記あり。詳細は動画予習推奨。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-zenhan</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 採用版 / 前半)</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 採用流派。「パラ1無敵 / パラ2十字 / パラ3イディル / サイコロネバラン」。
-- パラデイグマ 1回目: タンク無敵で処理
-- パラデイグマ 2回目 (十字):
-  * 線: 対面に伸ばす
-  * 塔TH: 北西から反時計回り
-  * 塔DPS: 北東から時計回り
-- スーパーチェイン I (8方向): D1/MT/D2 // ★ // H1/D3/D4/H2 // 円配置
-  ペア: MT/D1 // ST/D2 // H1/D3 // H2/D4
-  ペア半面 (ⅡA): MTD1 / STD2 / H1D3 / H2D4
-- スーパーチェイン II (ビーム誘導): 黒ビーム / 白ビーム、白デバフ/黒デバフ
-  4:4 + 塔/天火散開: MT/D1 ST/D2 // ★ 白/黒 // H1/D3 H2/D4
-- アポ・ペリ: アポ HD ボス下 / ペリ HD ボス背面サークル外
-- パラデイグマ 3回目 (イディル): 北:十字 / 南:X字
-  北 MT &gt; ST &gt; H1 &gt; H2 南
-  DPS 塔踏み: 中央 &gt; D1D2D3D4
-- サイコロネバラン: 2/4 は辺から頭割り、ビーム順: 5,7→6,8→1,3→2,4
-  サイコロ後は北に集合
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-kouhan-xshori</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 採用版 / 後半 X処理)</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 採用流派。パラスレイは X処理メイン (1回目は K処理することも多い)。
-- パラスの手: T:西 / 他:東
-- サモンダークネス: 北&gt;西:TH / 南&gt;東:DPS
-- デミハルペリオン: 3 セット連続、TH/DPS のスワップ配置
-- イデア: 西←〇×△□→東、α:赤▲ β:黄■
-- パラスレイ X処理:
-  ● ● ● ●
-  〇α ★ ×α (1回目) / △α ★ □α (2回目)
-  ● ● ● ●
-  〇β ★ ×β / △β ★ □β
-  2回目は〇×△□が反転、誘導後→★ に入る
-- カロリック1 (もちべ式): 炎マーカー頭割り 西TH/東DPS
-  風炎は MTSTH1H2D1D2D3D4 の順で A から時計
-- エクピロシス: MT/ST 上 // D1 MT // D2 ST // H1 H2 上 // D3 D4 // 等
-- パンゲネシス: MT:西無敵、他:南(東側)
-  極性なし: 西←MTSTH1H2D1D2D3D4→東
-  無職:スライム → 西:1マーカー、東:2マーカー
-- カロリック2: マーカーは MT と交代、反時計/最後中央行かずに2回移動
-- サモンダークネス + デミ 2 回目: MTD1 が奥まで走る、安置の逆側に
-  MT/D1 ST/D2 H1/D3 H2/D4 ペア
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>p12s</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-kshori</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>パラスレイ K処理 (1回目バリアント)</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">パラスレイの 1回目を K処理で行うバリアント。Game8 マクロは X処理だが
-「1回目は K処理することも多い」と注記あり。PT 募集時に必ず流派確認すること。
-詳細処理は ぬけまる別解動画 / Lodestone 等で要確認。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>p9s</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>musyoku-marathon</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>無職マラソン式 (Game8 採用版 / ぬけまる動画ベース)</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が採用しているぬけまる動画ベースの処理法。「無職マラソン式」
-(jobless marathon) と呼ばれる。
-- 基本散開: D3/MT/D4 // H1/★/H2 // D1/ST/D2
-- ペア十字 (X字反時計回り): MT/D3, ST/D2, H1/D1, H2/D4
-- 古式破砕拳: 4:4 頭割り、西 MTH1D1D3 / 東 STH2D2D4
-- ジャンブルコンボ (サイコロ1回目):
-  * 無職 (デバフ無し) は 1壁 (西) から進行方向に走り、青AoE が
-    ついたら止まる (= マラソン式の語源)
-  * 塔は 6→8→2→4 の順で処理
-  * 炎は 2→4→6→8 (塔から進行方向に45度ずれる)
-- ビーストフェーズ: 毒は 12時から時計回り、優先順 DPS &gt; TH
-  扇誘導は TH→D の順
-- キメリックコンボ (サイコロ2回目): 1→東 / 2→西 / 3,4→北 / 無職→南
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>m5s</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説に準拠した処理法。
-- ジングル予約 A/B: ジングルがランダムに A or B を詠唱するが、固定流派では
-  散開を一貫させるため位置固定で処理。
-- ディスコインファーナル 1回目: 西=MT組 / 東=ST組 / 内周=近接 / 外周=遠隔。
-- 音響爆弾: 北から秒数短い順にペア整列。
-- フロッグダンサー 1回目: MT組=北西 / ST組=南東。
-- ペア頭割り: 横隣り。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>m6s</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>p1-front</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>shin-ffo</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>新FFO式 (Game8 採用版 Ver.3.1)</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yuna'' Kanon' (FFO) 氏が公開した新FFO式マクロを Game8 が採用。
-- 基本散開: ねばねば北基準、Tボス下。
-- カラークラッシュ: 2:2:2:2 配置 (H1D3 / MTD1 / STD2 / H2D4)。4:4 はMT組ST組 (左/右)。
-- 砂漠フェーズのサボテン: 北で避ける。流砂は北基準。
-- 爆弾捨て: H1/D3 → MT/D1 → ST/D2 → H2/D4 順。
-- 雑魚処理順: ジャバ ＞ キャット ＞ フェザー ＞ ムー ＞ ヤーン (リキャバースト)。
-- Wave1: MT がムー、ST+近接がヤーン、遠隔がキャット。
-- Wave2: D側フェザーD3、B側フェザーH2 (北から捨て)。
-- Wave3: ジャバ+ムー行進、スタンは MT→D1→D2、STヤーン北東、バインドヒラ南東。
-- Wave4: MTムーC、STヤーンA (スタン: ST→D1→D2)、D側フェザーD3、B側フェザーD4 (南から捨て)。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>sari-shiki</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>さり式 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">さり氏 (Asche Okumura, note.com/srm_br) が考案、Game8 採用流派。
-- いしあ式よりも後出しGCDを多く回せる処理法 (火力寄り)。
-- 移動がシビアで P3 ストーンウェポンでスプリント必須。
-- ソーンデスマッチ・ビルディング (奇数 3回目安置 / 13捨て位置 など) の位置を固定。
-- ペア頭割り: MTD1=①, STD2=②, H1D3=③, H2D4=⑤。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>m7s</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>ponikone-shiki</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>ぽにこね式 (代替流派)</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が代替として掲載しているもうひとつの処理法。
-ソーンデスマッチ・ビルディングを別アプローチで処理する。詳細は Game8 ページ参照。
-# Source: https://game8.jp/ff14/681274
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-idyll-mod</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる様マクロ (Game8 採用 / イディル土修正 / 風化IQ6000)</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ぬけまる様 + イディルシャイア居住区様の土修正版を融合した流派。
-- 土の魔技: MTD4 / D3 / H1 / D1ST / H2 / D2 の配置。
-- 風の魔技 / 千年の風化 (IQ6000式):
-  MT/D3 H2/D4 / H1/D1 ST/D2、塔ズレ時計、回転中に前=近接 / 南北=遠隔 / 後=無職。
-- 群狼剣 (薙/廻): 北 MT/ST → 中央 H1組/H2組 へ移行。
-- 大地の怒り:
-  ① 風化散開 → 安置時計回り、頭割り中央。
-  ② 風化散開 → ズレ時計回り、頭割り北。
-- 幻狼招来: MT/D3 (頭割り) / H2/D4 / H1/D1 ST/D2。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>m8s</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-maxin-alice</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる様マクロ (Game8 採用 / 魔印正規 / 狐狼Alice / 81128)</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 採用流派。
-- 風震の魔印: 正規処理 (頭割りは風撃タンク隣島)。
-- 双牙撃: 西島=MT / 東島=ST。
-- 孤狼の呪い: Alice式 (T/H/D の位置とライン誘導を分岐固定)。
-  * Tニア: 北東 / Tファー: 西 / H: 不動
-  * Dニア: 線が北伸び→北東 / 南伸び→南
-  * Dファー: 線が北伸び→不動 / 南伸び→北東
-- 八連光弾: 2=MT無敵 / 3=ST無敵 / 4=T二人フルバフ。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>m10s</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>p1-fire</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>inumaru-suirou-hira-ac</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>基本犬丸水牢ヒラ/炎AC (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">犬丸様の攻略をベースに、家無しララ様の野良準拠解法を融合した処理法。
-- 水牢: ヒーラー入り
-- 炎: AC (近接) 担当
-- 詳細はマクロ参照
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>m11s</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる様式 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 採用流派。
-- 基本: ルクレ (基本散開)
-- ドミネーション: 安置を北基準に処理
-- オービタル: 北固定
-- メテオレイン: H 遠近 (H1: 南西遠、H2: 北東タゲサ上 など、3回ローテーション)
-- チャンピオンズ・メテオ: ジジ式位置固定
-- メテオスタンピード: DXA 式
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-idyll-style</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる様式 (ほぼイディル式) - Game8 採用版</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ぬけまる様 + イディル様の解説をベースにした処理法。
-- リーサルスカージ: D側 MT組 / B側 ST組
-- 細胞付着 前期: 左前タゲサ端で散開、頭割り角扇外周
-- 細胞付着 中期: 線取り 1234 / 塔踏み 3412
-- 細胞付着 後期: X字/十字判断で散開位置変更
-  X字: DPS右上 TH左下
-  十字 東西: DPS右上 TH左下 / 南北: DPS左上 TH右下
-- タン強: 無敵前捨て D側MT/B側ST
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-wanace-game8</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>Game8 採用版 (レプリ位置固定 / 模倣牛子式 / ドリームワンエース式)</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が採用しているハイブリッド流派。
-- レプリケーション: 位置固定式
-- 模倣細胞: 牛子式
-- アルカディアンドリーム: ワンエース式
-- マクロは Game8 では直接掲載されておらず、ぬけまる動画リンク先からコピーする必要あり。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>m12s</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-improved-srodin</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる改良版 (Sr Odin 改) - レプリ近接内+レプリ固定法</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sr Odin 氏が公開した「ヘビー級零式4層後半 アルカディアンドリーム用 ぬけまる改良版」。
-ぬけまる動画 (修正版) で追加された
-- レプリ近接内 + レプリ固定法
-- アルカディアンドリーム理屈説明
-- マナバ図修正
-を反映した /e (emote) コール用マクロ。
-確認したい場合は Lodestone を参照。
-# Source: https://na.finalfantasyxiv.com/lodestone/character/39631700/blog/5649775/
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>m9s</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説に準拠した処理法。
-- ヴァンプストンプ: 近接 (D1/D2) はコウモリ1の背後に寄り、TH+遠は前散開。
-- エーテルレッティング: 最外周扇範囲を捨てて中央集合。
-- 茨塔 (ラディスティック・スクリーチ): 北から時計回り、優先順 T&gt;近&gt;遠&gt;H。
-- ヘル・イン・ア・セル: 4セット連続塔踏み。
-- バット・デスマッチ: MT組 北西 / ST組 南東。
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>m1s</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>inumaru-game8</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>犬丸式 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が公式採用している犬丸氏解説に準拠した処理法。
-- クアドラプルネイル: 十字固定 (先 TH / 後 DPS)
-- レイニングキャッツ: タンク無敵で 2 連処理
-- 4:4 頭割り: 北/西 MTH1D1D3 / 南/東 STH2D2D4
-- フィールドマーカー: ABCD で東西南北、1234 で分身移動先を指定
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>m2s</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる版 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説に準拠した処理法。
-- 基本散開: D3 MT D4 / H1 ☆ H2 / D1 ST D2
-- 1st ライヴ: 近接 ♡2 / 遠隔 ♡3
-- 2nd ライヴ ♡0: 中央→北→TH 西、DPS 東で頭割り
-- 2nd ライヴ ♡1: 南待機 → AOE 対象者は捨てる、塔は TH 北/西 DPS 南/東
-- 毒捨て: TH 北西 / DPS 南東
-- ブラックハート: 8 方向散開 → HP 戻り次第早いペア順に中央集合
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>m3s</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる版 Ver.2.0 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説の改訂版 (Ver.2.0)。
-- 基本散開: D3 MT D4 / H1 ★ H2 / D1 ST D2
-- 4ウェイ: MT/D3 北西 + H2/D4 北東 + H1/D1 南西 + ST/D2 南東
-- 8ショック: MT ★ ST 上、D1 D2 中段、D3 H1 H2 D4 下段
-- 4ショック: 内側 MT/D1 + D2/ST、外側 D3/H1 + H2/D4
-- ボンバリアンボム: 1 塔目 北西:近接 + 南東:遠隔、2 塔目 ボスを見て左:MT 組 + 右:ST 組
-- 零式フューズボム: 単体の長ボムを北に見る、1 回目短/2 回目長 で配置切替
-- フューズフィールド: A から時計回り、短→長で MT→ST→H1→H2 / D1→D2→D3→D4
-- ボンバリアンスペシャル: 8 ショック → 基本散開、4 ショック → ペア X 受け
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-dn-game8</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる版 + DN 式 (Game8 採用版, Ver.2.1)</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が公式採用しているぬけまる氏動画 (最終改定版) + DN 式円輪/輪円処理法。
-- 縦散開: D3 D4 / MT ST / D1 D2 / H1 H2
-- 円輪・輪円 (DN 式): D3 MT D4 / D1 ☆ D2 / H1 ST H2
-- エレクトロープ 1 回目: MT D2 D4 / D1 ST H2 / D3 H1 角
-- エレクトロープ 2 回目: 基本散開 + 多/少振り分け
-  * 22 秒: 3 回 or 2 回
-  * 42 秒: 2 回 or 1 回
-  * TH 多: B,D / DPS 多: 中央
-  * TH 少: A / DPS 少: C
-- ストリーム: 紫/誘電/青/青/誘電/紫 の 6 ライン、TH 外側 / DPS 内側
-- エレクトロープ移植: 時計→反時計で往復
-- 8 月 8 日に散開位置をアップデート (Game8 表記)
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>m4s</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-game8</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる版 (Game8 採用版)</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Game8 が公式採用しているぬけまる氏解説に準拠した処理法。
-- クロステイル・スペシャル: タンク LB3 で凌ぐ
-- ウィケッドブレイズ: 西 MT 組 / 東 ST 組
-- マスタードボム: デバフ受取優先順位 MT←D1D3H1 / H2D4D2→ST
-- ブラックサバト【夜半】: MT/D2 上 / D1/ST 上 / H1/D4 下 / D3/H2 下
-- ブラックサバト【日出】:
-  * 塔: TH 南/西、DPS 北/東
-  * 誘導: TH 11 時から反時計、DPS 12 時から時計
-- 剣の雨: MT/ST、D1/D2、H1/H2、D3/D4 の 4 ペア
-- 剣の舞: MT/D1、ST/D2、H1/D3、H2/D4 のペアで 2:2:2:2 配置
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>priority-htd-std4</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>優先HTD/STD4入替/塔キャス固定</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>野良主流。STとD4が入替、塔をキャスター固定で処理する流派。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>idyll-basic</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>基本イディル (リリド式)</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>りりーどーるの「基本イディル」処理法。
-DD（ダイアモンドダスト）は基本散開から時計回り調整、
-扇誘導は D3 MT D4 ライン上に1,3枚目（スプリント）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>atobe-kingdom-kai</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>跡部王国改 (時間圧縮・絶)</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>ポネコニさんが派生させた跡部王国改版。
-P3野良主流の時間圧縮処理。X投稿 (PoneKoni) に詳細図あり。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>anchi-kijun</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>アポカリ：最初の安置基準</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>TH 赤紫マーカー / DPS 黄青マーカーで、最初の安置を基準にアポカリ処理。
-固定での採用が主流。遠隔組の移動距離が少ない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t>apoka-kijun</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>アポカリ：アポカリ基準</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>アポカリの出現位置を見て安置を決定する流派。
-ぬけまる動画 (P3-2) で詳細解説。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-style</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (扇前調整/アクモーン1:7/赤爆走アムレンY字)</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>P4-P5 野良主流。
-- 扇前調整: ウォタガ扇前調整
-- アクモーン: 1:7（1人と7人の分割）
-- 赤爆走: アムレンY字配置
-- attack me マクロ使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>fru</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>nukemaru-style-p5</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>ぬけまる式 (アクモーン ボス基準/MT組左/ST組右)</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>P5 野良主流。光塵の剣、アクモーン、パラダイスリゲインド、星霊の剣をぬけまる解説動画準拠で処理。</t>
         </is>
       </c>
     </row>
@@ -11832,7 +8243,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"># マクロ全文は著作権上の理由で抜粋のみ。完全版は Lodestone 原文を参照。
+          <t># マクロ全文は著作権上の理由で抜粋のみ。完全版は Lodestone 原文を参照。
 # 出典: https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5248067/
 # 短縮URL: https://ffxiv.link/096666
 #
@@ -11850,8 +8261,7 @@
 #  カータTLB     = P2 カータライズで タンク LB3
 #  進軍十字      = P3 進軍の三重奏で十字配置
 #  連撃V字       = P3 連撃の三重奏で V 字配置
-#  群竜TLB       = P3 群竜の八重奏 (Grand Octet) で タンク LB3
-</t>
+#  群竜TLB       = P3 群竜の八重奏 (Grand Octet) で タンク LB3</t>
         </is>
       </c>
     </row>
@@ -11921,7 +8331,11 @@
           <t>uwu</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
@@ -11935,82 +8349,76 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【覚醒バフ】BH＞D4＞D1
+          <t>/p 【覚醒バフ】BH＞D4＞D1
 /p 【低気圧処理】ST＞STヒラD3D4＞D1＞D2
 /p 【ミストラルソング】MT：B&gt;A&gt;C ST：D&gt;C&gt;A
-/p 【メソハイ】【D】…D4　 【B】…MT
-/p 【インシネレート】1回目：ST/2回目：MT
+/p 【メソハイ】【D】…D4　 【B】…MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>uwu</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>りりーどーる (P1-P3 共通 - 新みんとっと / 楔逆Z / ジェイル自滅)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>https://jp.finalfantasyxiv.com/lodestone/character/34120564/blog/5248065/</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>/p 【インシネレート】1回目：ST/2回目：MT
 /p 【楔：逆Ｚ】楔①：D1/楔②：D2/楔③：D3/楔④：D4
 /p 　　 　 　　　③　 ④
 /p 　　↑ 　　　　　　　　　　↑
-/p 　　D3　①　　　　　　②　D4
-/p 【タイタン自殺ポイント】 重み２回目（ST/メレー/レンジ）
+/p 　　D3　①　　　　　　②　D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>uwu</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>りりーどーる (P1-P3 共通 - 新みんとっと / 楔逆Z / ジェイル自滅)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>https://jp.finalfantasyxiv.com/lodestone/character/34120564/blog/5248065/</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>/p 【タイタン自殺ポイント】 重み２回目（ST/メレー/レンジ）
 /p 【ジェイル位置】　　　　　 |【蘇生】
 /p 　ボスD4 H1 H2　　　　 | H1⇒ST　H2⇒D1　D４⇒D2/D3
 /p 　ランスラ斜めに誘導　　　 |
-/p 【マウンテンバスター】1回目：MT/2回目：ST(orかばう)/3回目：MT
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>りりーどーる (P4-P6 - 新みんとっと / 十字無視 / 3111 / 乱撃TLB)</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>https://jp.finalfantasyxiv.com/lodestone/character/34120564/blog/5248065/</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/p ＝＝＝＝＝アルテマフェーズ＝＝＝＝＝
-/p 【緑玉】1回目：MTSTD1/2~4回目：MT
-/p 【爆撃Ｐメソハイ】1回目：D3/2回目：灼熱ヒラ
-/p 【乱撃タンクLB3法】
-/p 　　　　A
-/p 　　 ST
-/p 　D　 ★　 B　　※★はヒラ・DPS
-/p 　　　　　MT
-/p 　　　　C
-/p 【フェザーレイン回避方向】★→A→D
-/p 【ジェイル破壊】フェザーレイン回避時にターゲット可能。殴る。
-/p 【エーテル波動】ST：LB1
-/p 【紫玉】MT：AB間→AD間　ST：BC間　その他：CD間
-/p 【三蛮神】
-/p 　・ガル(A北→A→2)→イフ(2→3)→タコ(3→2.3間→3)
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>uwu</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>あせろぐ (asellog) - 絶アルテマウェポン 攻略準備&amp;マーカー配置 (3分割マクロ)</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>https://asellog.com/uwu/</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr"/>
+/p 【マウンテンバスター】1回目：MT/2回目：ST(orかばう)/3回目：MT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -12018,19 +8426,50 @@
           <t>uwu</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr"/>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
       <c r="C9" s="8" t="inlineStr"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>もず (note) - 絶アルテマまとめ (みん学/楔逆Z/ジェイル自殺式/十字無視/3111/乱撃TLB)</t>
+          <t>りりーどーる (P4-P6 - 新みんとっと / 十字無視 / 3111 / 乱撃TLB)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://note.com/mozuzuzu/n/nd4fb5fff75ab</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr"/>
+          <t>https://jp.finalfantasyxiv.com/lodestone/character/34120564/blog/5248065/</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>/p ＝＝＝＝＝アルテマフェーズ＝＝＝＝＝
+/p 【緑玉】1回目：MTSTD1/2~4回目：MT
+/p 【爆撃Ｐメソハイ】1回目：D3/2回目：灼熱ヒラ
+/p 【乱撃タンクLB3法】
+/p 　　　　A　　　　
+/p 　　 ST　　
+/p  　D　   ★　    B　　※★はヒラ・DPS
+/p 　　　　　MT
+/p 　　　　C
+/p ・MT:タンクLB3(1回目→エラプ1回目出現、2回目→1回目LBバフ残り2秒）
+/p ・ST:全体軽減バフ
+/p ・ヒラ:堅実魔、全体回復バリア連打
+/p ・レンジ:全体軽減バフ
+/p 【フェザーレイン回避方向】★→A→D ※タンクはフェザーレイン被弾でも生存可能
+/p 【ジェイル破壊】フェザーレイン回避時にターゲット可能。殴る。
+/p ・ジェイル破壊後、Dでランスラ誘導と頭割処理
+/p ・ST：メソハイ処理、タンクLB3　　MT：アルテマ詠唱リプ
+/p 【エーテル波動】ST：LB1
+/p 【紫玉】MT：AB間→AD間　ST：BC間　その他：CD間
+/p 【三蛮神】
+/p 　・ガル(A北→A→2)→イフ(2→3)→タコ(3→2.3間→3)
+/p 　・イフ(２→3)→ガル(A北→A→2)→タコ(２→2.３間→2)
+/p 　・タコ(２→2.3間→2)→イフ(2→3)→ガル(A北→A→2)
+/p 　※イフの時スプリント使用</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -12043,10 +8482,14 @@
           <t>p1</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>yarkt-mushi-20</t>
+        </is>
+      </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>りりーどーる (P1 - ヤークト無視 / サイコロ1211)</t>
+          <t>りりーどーる (P1 - ヤークト無視)</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -12056,17 +8499,14 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ヤークト無視法（水沼の頂点を北、無い方角を南）
+          <t>/p ヤークト無視法（水沼の頂点を北、無い方角を南）
 /p 　 D3〇北　　　　　　｜D3：可視扇を誘導後、南で合流（ヤークトの円範囲に注意）
 /p 　　　　　　　　　　　｜
 /p 〇　　手　　〇　　　　｜
 /p D4　 ST　　H1 　　　 ｜ST：手を中央へ誘導、パーにする
 /p 　　　　　　　　　　　｜D4：不可視扇後、南で合流
 /p 　　　人　　　　　　　｜
-/p 　　MT・H2・D1・D2 ｜MT：人型を南へ誘導、手がパーになったら挑発して南へ誘導
-/p ■サイコロ１２１１
-/p 　東西スタートの場合、東側優先
-</t>
+/p 　　MT・H2・D1・D2 ｜MT：人型を南へ誘導、手がパーになったら挑発して南へ誘導</t>
         </is>
       </c>
     </row>
@@ -12078,23 +8518,100 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>dice-1211</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>りりーどーる (P1 - サイコロ1211)</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5274750/</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>/p ■サイコロ１２１１
+/p 　東西スタートの場合、東側優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>dice-44-separate</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>りりーどーる (P1 - サイコロ 4:4 セパレ式 )</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>https://jp.finalfantasyxiv.com/lodestone/character/2460105/blog/4282117/</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>/p ーーー２体フェーズーーー
+/p ■照準
+/p 　　　○　　
+/p 　　○　○　　①②⑤⑥：○側（北側）
+/p 　●　　　○　
+/p 　　●　●　　③④⑦⑧：●側（南側）
+/p 　　　●
+/p ■処理法
+/p 　扇着弾後に入る⑤⑥→ ／
+/p 　　ーーーーーー　　／↓
+/p 　　後ろに飛ばす②◎①扇は進行方向に向ける
+/p 　　ーーーーーー　　＼　
+/p 　　　　　　　　　　　 ＼</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>p2</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>りりーどーる (P2 - 基本散開 / ナイサイ ヒラ先渡し / 水雷処理)</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5274750/</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/p ■基本散開　　　■カウント（調整DPS・ヒラは縦に並ぶ）
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>/p ■基本散開　　　■カウント（調整DPS・ヒラは縦に並ぶ）
 /p 　　　 MT　　　　西H1　西D3D4D2D1東
 /p 　　D3　D1　　　　H2
 /p 　H1　　　H2　■地雷
@@ -12108,36 +8625,35 @@
 /p ■水雷処理
 /p 　1回目　水[4]：対象H・雷以外のDPS3人　 雷[北]：対象DPS・MT
 /p 　2回目　水[2]：DPS４人　　　　　　　　 雷[北]：MT・H1
-/p 　3回目　水[B]：水低下以外のDPS３人・ST　雷[D]：ヒラ2人
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+/p 　3回目　水[B]：水低下以外のDPS３人・ST　雷[D]：ヒラ2人</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>tea</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>p3</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>りりーどーる (P3 - 時間停止 脳死法 / 時空潜航のマーチ / 次元断絶のマーチ)</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5274750/</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/p ■時間停止(脳死法)
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>/p ■時間停止(脳死法)
 /p 　無印→左側ロボ(TH上/DPS下)
 /p 　緑線→右側ロボ(TH上/DPS下)
 /p 　青線TH→左側　青線D→右側(チェイサー側は近づく)
@@ -12163,36 +8679,35 @@
 /p 　⑤⑦　　　　⑥⑧　　 （ついてないDPSは抜ける）
 /p 　　　③　　④
 /p 　　　 プライム
-/p 懴悔の順番：５６→７８→１２
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+/p 懴悔の順番：５６→７８→１２</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>tea</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>p4</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>りりーどーる (P4 - 確定判決 / 未来観測 α/β)</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5274750/</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/p ■確定判決
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>/p ■確定判決
 /p 黄親→4/紫親→2/他６人→2左側
 /p ・頭割り：TH北/DPS南
 /p ・散開：MT ST
@@ -12208,50 +8723,9 @@
 /p 逃亡禁止（紫子/緑線）：2左上
 /p 逃亡禁止（紫子/無職）：2左横
 /p 逃亡禁止（紫子/青線）：2左下
-/p ・頭割り：黄北/紫南
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr"/>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>ふうcだよ FF14情報サイト - 絶アレキサンダー討滅戦 カンペ集 (野良主流処理法)</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>https://fuucdayo.com/battle/4046/</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr"/>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>ふうcだよ FF14情報サイト - 絶アレキサンダー ヤークト完全無視処理法</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>https://fuucdayo.com/battle/3685/</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr"/>
+/p ・頭割り：黄北/紫南</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -12273,7 +8747,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【基本散開/氷火の侵食】
+          <t>/p 【基本散開/氷火の侵食】
 /p 　　D3　 MT　 D4
 /p 　　H1 　 ■ 　 H2
 /p 　　D1 　 ST 　D2
@@ -12287,8 +8761,7 @@
 /p 結呪調整ペア MTD4 / H2D2 / STD1 / H1D3 マーカー色基準
 /p ※紫色：秒数短い順にABCDマーカー
 /p ※赤色：秒数短い順に1234マーカー
-/p 【時限の魔鎖】対象者は光、他は火
-</t>
+/p 【時限の魔鎖】対象者は光、他は火</t>
         </is>
       </c>
     </row>
@@ -12312,7 +8785,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【ショックウェーブ・頭割り】
+          <t>/p 【ショックウェーブ・頭割り】
 /p MT H1 D1 D2 (ボス下）
 /p ST H2 D3 D4（通路）
 /p 【チャネリングフロウ・十字】
@@ -12326,8 +8799,7 @@
 /p T：角　DPS：内側
 /p 【カンペオスハルマ】
 /p 青サイコロ：1・3→ボス対角　2・4→ボス下
-/p 紫サイコロ：数字マーカー基準
-</t>
+/p 紫サイコロ：数字マーカー基準</t>
         </is>
       </c>
     </row>
@@ -12351,7 +8823,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【4:4分け（雑魚/霊泉）】
+          <t>/p 【4:4分け（雑魚/霊泉）】
 /p MT組：MTH1D1D3　ST組：STH2D2D4
 /p 【闇の炎設置ペア：X字】
 /p 　D3/MT ① D4/ST
@@ -12364,8 +8836,7 @@
 /p 【雑魚誘導】MT組：北→西 　ST組：東→南
 /p 【雑魚突進】
 /p 線2本：繋がってる鳥の対角の時計回り
-/p 線1本：繋がってるペアの対角
-</t>
+/p 線1本：繋がってるペアの対角</t>
         </is>
       </c>
     </row>
@@ -12389,7 +8860,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【魔力錬成：闇（辺獄の炎嵐以外）】
+          <t>/p 【魔力錬成：闇（辺獄の炎嵐以外）】
 /p 近接組(MTSTD1D2)：北安置　遠隔組(H1H2D3D4)：南安置
 /p 【霊泉フェーズ：ハピおじ】
 /p 塔踏みAOEスタート場所：MT組→北/西　ST組→南/東
@@ -12402,8 +8873,7 @@
 /p 〇 　D1 D4 D2　〇
 /p 【辺獄黒竜巻ノックバック】
 /p 　　 　黒竜巻
-/p ←近接 　　　 遠隔→
-</t>
+/p ←近接 　　　 遠隔→</t>
         </is>
       </c>
     </row>
@@ -12427,7 +8897,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【赤小玉→黒小玉】　【赤大玉→黒小玉】
+          <t>/p 【赤小玉→黒小玉】　【赤大玉→黒小玉】
 /p 　 　MT　ST　　　　 D1　MT　D2　ST
 /p 　　　 ★　 　　 　　 　　　 ★
 /p 　 　D1　 D2
@@ -12441,8 +8911,7 @@
 /p 　　　　　〇
 /p ST　D2 　★　 H2　D4
 /p 　〇 　D1　 H1　〇
-/p 　　MT　　　　D3
-</t>
+/p 　　MT　　　　D3</t>
         </is>
       </c>
     </row>
@@ -12466,7 +8935,7 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【基本散開】　　　　　【毒線YPP式】
+          <t>/p 【基本散開】　　　　　【毒線YPP式】
 /p 　D3MTD4　　　　　TH：北　DPS：南
 /p 　H1 ◯ H2
 /p 　D1 ST D2　※塔線時計回り/線ぐるぐる
@@ -12480,8 +8949,7 @@
 /p 【緑玉脳死・十字】
 /p 　STMTH2　※MTH2→D3　STH1→D4
 /p 　H1 ● D4　　 D1D3→MT　D2D4→H1
-/p 　D1D3D2　　上記の玉を取って時計回り
-</t>
+/p 　D1D3D2　　上記の玉を取って時計回り</t>
         </is>
       </c>
     </row>
@@ -12505,7 +8973,7 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ―《序幕》――――――――――――――――――
+          <t>/p ―《序幕》――――――――――――――――――
 /p 　D3　　　　　D4
 /p 　　MT　　　ST
 /p 　　　　ボス
@@ -12519,8 +8987,7 @@
 /p 　　D3　　　D3　 　　アースシェイカー誘導
 /p 　H1　　●　　H1　→ 　ST　　　　ST
 /p 　H2　　　　　H2　　D1 ● その他　● D1
-/p 　　D4　　　D4　　　　 D2　　　　D2
-</t>
+/p 　　D4　　　D4　　　　 D2　　　　D2</t>
         </is>
       </c>
     </row>
@@ -12544,7 +9011,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ―《第四幕》――――――――――――――――
+          <t>/p ―《第四幕》――――――――――――――――
 /p ①ウォタガは塔の対角の１つ時計回り側で切る
 /p 　ダージャは自分の塔の時計回り側の塔を踏む
 /p ②南西集合し北のダージャから【時計回り】処理
@@ -12556,8 +9023,7 @@
 /p ―《カーテンコール》――――――――――――
 /p 　THは6秒で切りに行く
 /p 　Dは11秒で切りに行く
-/p 　（メモ：13/23/33/43）
-</t>
+/p 　（メモ：13/23/33/43）</t>
         </is>
       </c>
     </row>
@@ -12585,7 +9051,7 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【教皇庁①】
+          <t>/p 【教皇庁①】
 /p ｜■MTアデル／STグリノー
 /p ｜開幕アデルへバースト　線ST無敵
 /p ｜■ハイパーディメンション：北捨て→南捨て
@@ -12599,8 +9065,7 @@
 /p ｜ル　　 (MT組) シャリベル (ST組)
 /p ｜シ　　 　捨　　　安置　　　捨
 /p ｜ュ (H1H2)(D34) 　 (MTST)(D12)
-/p ｜ファン　※安置横にペア捨て（重ねる）
-</t>
+/p ｜ファン　※安置横にペア捨て（重ねる）</t>
         </is>
       </c>
     </row>
@@ -12628,7 +9093,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【トールダン】
+          <t>/p 【トールダン】
 /p ｜■雷槍
 /p ｜　MT組 D-1　　　ST組 B-3
 /p ｜　　／ H1 ＼　　　／ H2 ＼
@@ -12641,8 +9106,7 @@
 /p ｜■聖杖（前半）ゼフィラン基準
 /p ｜　※ペア調整 (MTST/H1H2/D1D2/D3D4)
 /p ｜　剣1+MT組→ゼフィランの対角
-/p ｜　剣2+ST組→ゼフィランの後ろ
-</t>
+/p ｜　剣2+ST組→ゼフィランの後ろ</t>
         </is>
       </c>
     </row>
@@ -12670,7 +9134,7 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【ニーズヘッグ】
+          <t>/p 【ニーズヘッグ】
 /p ｜■サイコロ
 /p ｜　　　　 A　　　※①②③イル↓D・スパ↑B固定
 /p ｜　　　 ②　②　　※②③は北でアピール
@@ -12682,8 +9146,7 @@
 /p ｜　D3/MT　　ST/D4　※遠隔位置固定＆ゲイル誘導
 /p ｜　　　　 ボス　　　　※調整優先度：時計回り＞反時計＞対角
 /p ｜　H1/D1　　D2/H2 ※タンク強攻撃：ボス下MT/分身下ST
-/p ｜　　　　　　　　　　 ※タンク強着弾後バースト（AA【南】向き）
-</t>
+/p ｜　　　　　　　　　　 ※タンク強着弾後バースト（AA【南】向き）</t>
         </is>
       </c>
     </row>
@@ -12711,7 +9174,7 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【竜の邪眼】※近接青眼寄せ
+          <t>/p 【竜の邪眼】※近接青眼寄せ
 /p ｜■玉取り
 /p ｜　　　 MT　　　 　ST　　　 赤⇒D1D2D3D4
 /p ｜ (青眼) D1　調整　 D3 (赤眼)　青⇒MTSTH1H2
@@ -12725,8 +9188,7 @@
 /p ｜ 交代順(①②③④優先順位)
 /p ｜ 1回目：①D1＞D2④
 /p ｜ 2回目：①D3＞D4④
-/p ｜ 3回目⇒1回目対象者①MT&gt;ST&gt;H2&gt;H1④
-</t>
+/p ｜ 3回目⇒1回目対象者①MT&gt;ST&gt;H2&gt;H1④</t>
         </is>
       </c>
     </row>
@@ -12754,7 +9216,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【教皇庁❷】TLB以外①と同じ
+          <t>/p 【教皇庁❷】TLB以外①と同じ
 /p ｜※シャリベルHP29%で火力温存
 /p ｜タンクLB3
 /p ｜■光翼閃（H→D12→D34→T）
@@ -12762,8 +9224,7 @@
 /p ｜ル　　 (MT組) シャリベル (ST組)
 /p ｜シ　　 　捨　　　安置　　　捨
 /p ｜ュ (H1H2)(D34) 　 (MTST)(D12)
-/p ｜ファン　※安置横にペア捨て（重ねる）
-</t>
+/p ｜ファン　※安置横にペア捨て（重ねる）</t>
         </is>
       </c>
     </row>
@@ -12791,15 +9252,14 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【儀典トールダン】
+          <t>/p 【儀典トールダン】
 /p ｜■風槍
 /p ｜　　騎　竜　騎
 /p ｜（以下マクロ全文は著作権上の理由で抜粋のみ）
 /p ｜■死刻 こまぞう式改 (アニメ解説: ぬけまる YouTube)
 /p ｜　D4&gt;D3&gt;D2&gt;D1&gt;ST&gt;MT&gt;H1&gt;H2 の散開優先度
 /p ｜　北西→南東に斜め8人並び、ゲリック出現位置を北として認識
-/p ｜　死の宣告解放点を固定、ツイスター直線移動処理
-</t>
+/p ｜　死の宣告解放点を固定、ツイスター直線移動処理</t>
         </is>
       </c>
     </row>
@@ -12827,7 +9287,7 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【二天竜】
+          <t>/p 【二天竜】
 /p ｜ニーズ：MTH1D1D3／フレース：STH2D2D4
 /p ｜■息吹１回目（おこめ式）
 /p ｜　　　　　 T
@@ -12855,8 +9315,7 @@
 /p ｜　　　　　C
 /p ｜■カータライズ
 /p ｜　MT　ST　→タッチダウンA集合
-/p ｜　 その他 　　 滅殺持ち近接とD3はAに残る
-</t>
+/p ｜　 その他 　　 滅殺持ち近接とD3はAに残る</t>
         </is>
       </c>
     </row>
@@ -12884,7 +9343,7 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【最終フェーズ】※アクモーン2回目TLB3
+          <t>/p 【最終フェーズ】※アクモーン2回目TLB3
 /p ｜■エクサフレア
 /p ｜（以下マクロ全文は著作権上の理由で抜粋のみ）
 /p ｜■トリニティ AA 受け順
@@ -12892,8 +9351,7 @@
 /p ｜■アクモーン
 /p ｜　1回目: 受け / 2回目: TLB3
 /p ｜■ギガフレア
-/p ｜　1発目予兆→対角移動→着弾後直線スプリント
-</t>
+/p ｜　1発目予兆→対角移動→着弾後直線スプリント</t>
         </is>
       </c>
     </row>
@@ -12937,7 +9395,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【基本散開】　　　【十字毒塔】STフリー
+          <t>/p 【基本散開】　　　【十字毒塔】STフリー
 /p D3 MT D4　　　　　　MT(無敵)
 /p H1　　H2　　　H1D3　　 H2D4
 /p D1 ST D2　　　　　　 D1D2
@@ -12955,8 +9413,7 @@
 /p MT組：マーカー1or4に出た毒に合わせて移動
 /p ST組：マーカー2or3に出た毒に合わせて移動
 /p AOEは外周に捨ててMT/STの位置で頭割り
-/p 【4部屋ベノムスプラッシュ：3個部屋の対角】
-</t>
+/p 【4部屋ベノムスプラッシュ：3個部屋の対角】</t>
         </is>
       </c>
     </row>
@@ -12980,7 +9437,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ※MT組：MTH1D1D3 ST組：STH2D2D4
+          <t>/p ※MT組：MTH1D1D3 ST組：STH2D2D4
 /p 　【基本散開】　　【カヘキシー1回目】
 /p MT/D3　ST/D4 　 　 8　　 　 　8
 /p 　　 　 ★　　 　 　12　20 ★ 20　12
@@ -12993,8 +9450,7 @@
 /p 東：偶数　　　　　｜※AOEも上記方向に捨てる
 /p 【カヘキシー2回目】
 /p 西：紫デバフ　東：緑デバフ
-/p 北・南外周マス→AoE　内周マス→頭割り
-</t>
+/p 北・南外周マス→AoE　内周マス→頭割り</t>
         </is>
       </c>
     </row>
@@ -13018,7 +9474,7 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p MT組：MTH1D1D3　ST組：STH2D2D4
+          <t>/p MT組：MTH1D1D3　ST組：STH2D2D4
 /p 　【基本散開】　　　　　【ノックバック+鳥】
 /p MT/D1　ST/D2　　　　 D1　　 　 　 D2
 /p 　　 　 ★　　　　　　D3　 MT　 　ST　 D4
@@ -13032,8 +9488,7 @@
 /p 　 ▼西島▼　　　　　　　 　 ▼東島▼
 /p 頭割り　MT/D1 　 　 　 MT/D1　頭割り
 /p ST/D2　H2/D4　通路　H2/D4　ST/D2
-/p 　　　　H1/D3　 　　　H1/D3
-</t>
+/p 　　　　H1/D3　 　　　H1/D3</t>
         </is>
       </c>
     </row>
@@ -13057,7 +9512,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■テトラオクタ/誘導/蛇2　 ■基本散開
+          <t>/p ■テトラオクタ/誘導/蛇2　 ■基本散開
 /p 　MT/D3　→　ST/D4　　　D3 MT D4
 /p 　　↑　　 ☆　　↓　 　　　H1(H2) ST
 /p 　H1/D1　←　H2/D2 　　D1 H2 D2
@@ -13081,8 +9536,7 @@
 /p 　無職：北西TH/南東DPS
 /p ■テトラ/ディフレア
 /p 　テトラ：(ボス)MT/D1&gt;ST/D2&gt;H1/D3&gt;H2/D4
-/p 　ディフレア：(ボス)MTH1D1D2&gt;STH2D3D4
-</t>
+/p 　ディフレア：(ボス)MTH1D1D2&gt;STH2D3D4</t>
         </is>
       </c>
     </row>
@@ -13106,7 +9560,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【術式1回目(頭割は西)】【術式炎氷(TH西 DPS東) 】
+          <t>/p 【術式1回目(頭割は西)】【術式炎氷(TH西 DPS東) 】
 /p 　 　★　　　紫 　 ST│ ▼炎:中央前詰め　▼氷誘導
 /p D1 MT D2　　 MT　│ MT&gt;ST &gt;H1&gt;H2 西 D1&gt;ST
 /p H1　　H2　H1　D2│ D1&gt;D2&gt;D3&gt;D4 東MT&gt;D2
@@ -13120,8 +9574,7 @@
 /p 重/遅βγ　　　　　 │
 /p 　　　　早γ　　 　 │　　　遅γ
 /p ※4塔：遅αβγ→北で合成
-/p 　 　 　 複/重/早余り→南で合成
-</t>
+/p 　 　 　 複/重/早余り→南で合成</t>
         </is>
       </c>
     </row>
@@ -13145,7 +9598,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【万象灰燼：はいじあ/ビジョン式】
+          <t>/p 【万象灰燼：はいじあ/ビジョン式】
 /p 　　MT　　D1
 /p ST　 +　　　+　D2　※1,3番塔は前+で範囲捨て
 /p H1　+　　　+　D3　※2,4番塔は後+で範囲捨て
@@ -13159,8 +9612,7 @@
 /p ※4塔：遅αβ→北で合成　遅γ/早余り→南で合成
 /p 【支配者の一撃】　　　　　【塔優先度】
 /p 　MTH1 D3 D1　西&gt;MTSTH1H2D4D3D2D1&gt;東
-/p 　ST H2 D4 D2
-</t>
+/p 　ST H2 D4 D2</t>
         </is>
       </c>
     </row>
@@ -13188,7 +9640,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【サークルプログラム】(南集合)
+          <t>/p 【サークルプログラム】(南集合)
 /p 塔ふみ/線とり/線捨て
 /p 北(11.5時)から時計＞H1MTSTD1D2D3D4H2
 /p 【パンクラ】
@@ -13199,8 +9651,7 @@
 /p 【波動砲T無敵】※7方向散開
 /p 　　　　　　MTST
 /p 　D3　　　　　　　　　　D4
-/p 　　　D1　H1　H2　D2
-</t>
+/p 　　　D1　H1　H2　D2</t>
         </is>
       </c>
     </row>
@@ -13228,7 +9679,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【連携プログラムPT】
+          <t>/p 【連携プログラムPT】
 /p ※調整優先度：全て下から調整
 /p 左組　　　右組
 /p H1　　 　 H2
@@ -13251,8 +9702,7 @@
 /p 　　　　　 盾
 /p 　　　MT　　ST
 /p 　　　　　 他(中央集合)
-/p 頭割り：中央で盾誘導以外7人
-</t>
+/p 頭割り：中央で盾誘導以外7人</t>
         </is>
       </c>
     </row>
@@ -13280,7 +9730,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【コロッサスブロー】
+          <t>/p 【コロッサスブロー】
 /p ❶①&gt;H1MTSTD1D2D3D4H2&gt;②❹
 /p 　　①　　②　 　白＋無職：①②
 /p 　❶　 ★ 　❹ 　紫：❶❷❸❹
@@ -13303,8 +9753,7 @@
 /p
 /p 　　　　　⑤Ｃ
 /p ※ボス検知逆の場合左右反転
-/p ※AC縦列(①④⑤)はボスモニターの無い方へ
-</t>
+/p ※AC縦列(①④⑤)はボスモニターの無い方へ</t>
         </is>
       </c>
     </row>
@@ -13332,14 +9781,13 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【P4 波動砲】
+          <t>/p 【P4 波動砲】
 /p 　 MT ST
 /p 　(D)D3 ★ D4(B)
 /p 　 H1 H2
 /p 　 (3)D1 D2(2)
 /p 　　　 頭(C)頭
-/p ※頭割り：下調整　人数調整：D1D2
-</t>
+/p ※頭割り：下調整　人数調整：D1D2</t>
         </is>
       </c>
     </row>
@@ -13367,7 +9815,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ◆コード： ＊＊＊ミ＊【デルタ】
+          <t>/p ◆コード： ＊＊＊ミ＊【デルタ】
 /p 【ロケパン】場所は早い者勝ち
 /p ❶❷：ニア/①②：ファー
 /p (目)
@@ -13391,8 +9839,7 @@
 /p 　　Ｙ　　　　　元ﾌｧｰ　　　　　　　　　Ｙ
 /p 　　　　　　　　 〇　元ﾌｧｰ　　　❶❶
 /p 　　　　　　　　　　　〇　　　元ﾆｱ(外)
-/p 　　　　　　　　　　　Ｙ
-</t>
+/p 　　　　　　　　　　　Ｙ</t>
         </is>
       </c>
     </row>
@@ -13420,12 +9867,11 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ◆コード： ＊＊＊ミ＊【シグマ】
+          <t>/p ◆コード： ＊＊＊ミ＊【シグマ】
 /p # 要手動補完: 塔Wingwan のマーカー配置 (A B C D / 1 2 3 4)、
 /p # シールドバッシュ&amp;シールドプロジェクション処理、
 /p # シノニム/不可侵領域処理、ハロワ散開を Lodestone 原文から補記すること。
-/p # 出典: https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5178791/
-</t>
+/p # 出典: https://na.finalfantasyxiv.com/lodestone/character/34120564/blog/5178791/</t>
         </is>
       </c>
     </row>
@@ -13453,7 +9899,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ◆コード： ＊＊＊ミ＊【オメガ】
+          <t>/p ◆コード： ＊＊＊ミ＊【オメガ】
 /p [オメガM] ｜　②無　❶左　　①無
 /p 　〇　〇　｜
 /p 　×　×　｜　❷左　　　　　❷右
@@ -13480,8 +9926,7 @@
 /p ③　　　　　★　④　l2回目：ﾃﾞｭﾅﾐｽ3＞ﾃﾞｭﾅﾐｽ2
 /p 　　　　　　　　　　l★ハロワファー
 /p 　　　　◆　　　　　l◆ハロワニア
-/p 　　　無　無　　　　l
-</t>
+/p 　　　無　無　　　　l</t>
         </is>
       </c>
     </row>
@@ -13509,7 +9954,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【コスモメモリー】LB3：ST
+          <t>/p 【コスモメモリー】LB3：ST
 /p 【AA】MT北内　ST東外　他南西内
 /p 【コスモダイブ1回目】
 /p MT北内　ST東内　他南西外
@@ -13533,8 +9978,7 @@
 /p Ｈ１　　Ｈ２
 /p Ｄ１ＳＴＤ２
 /p 【マジックナンバー】
-/p LB3：MT→H1→ST→H2
-</t>
+/p LB3：MT→H1→ST→H2</t>
         </is>
       </c>
     </row>
@@ -13598,7 +10042,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■尖脚 左MT 右ST
+          <t>/p ■尖脚 左MT 右ST
 /p ■グランドウェブ 左H 右DPS
 /p ■パンデモニックピラー-----------------------
 /p ST H1 MT 　　　　　　｜D1 MT ST D2
@@ -13609,8 +10053,7 @@
 /p 　　D1 　　 D2 　　　｜ 扇北向け
 /p 　　　　H1 　　　　　｜ 頭割り南で横並び
 /p 　　D3 　　 D4 　　　｜ 線クロスしない
-/p 　　　　H2 　　　　　｜
-</t>
+/p 　　　　H2 　　　　　｜</t>
         </is>
       </c>
     </row>
@@ -13634,7 +10077,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■ボンド
+          <t>/p ■ボンド
 /p -西島/片面/震撃---------------ﾀﾚｯﾄ------------
 /p MT D1 　　　　　　　｜ D1 / MT ST / D2
 /p ST D2 　　　　　　　｜
@@ -13646,8 +10089,7 @@
 /p ■タレット
 /p 西 H1MT → D3MT → D1MT → MT
 /p 東 H2ST → D4ST → D2ST → ST
-/p 3番レーザーは4番タレットに向けて角度調整
-</t>
+/p 3番レーザーは4番タレットに向けて角度調整</t>
         </is>
       </c>
     </row>
@@ -13671,14 +10113,13 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■魔殿の震撃ボンド
+          <t>/p ■魔殿の震撃ボンド
 /p ダブル(22)MT組:ST組
 /p D1　MT　ST　D2
 /p D3　H1　 H2　D4
 /p クアドラ(44)TH組:DPS組
 /p MT　ST　D1　D2
-/p H1　H2　D3　D4
-</t>
+/p H1　H2　D3　D4</t>
         </is>
       </c>
     </row>
@@ -13702,7 +10143,7 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ※ボスを見て以外は北(A)基準
+          <t>/p ※ボスを見て以外は北(A)基準
 /p MT組：MTH1D1D3　ST組：STH2D2D4
 /p 【基本散開】　　　【アップヘルド闇/ペア散開】
 /p D3 MT D4　　　 　　　　　　　MTD3
@@ -13715,8 +10156,7 @@
 /p ボスを見て　左:MTD3/STD2 右:H1D1/H2D4
 /p 戒律の闇線⇒T線：Aマーカー　光：ボス中央
 /p 【ライトストリーム後ディバイド】
-/p ボスを見て MT組：左　ST組：右
-</t>
+/p ボスを見て MT組：左　ST組：右</t>
         </is>
       </c>
     </row>
@@ -13740,7 +10180,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【光と闇の調停：ジジー式】
+          <t>/p 【光と闇の調停：ジジー式】
 /p 光⇒TH：西側　DPS：東側
 /p 闇⇒TH：東側　DPS：西側
 /p 【調停ディバイド】
@@ -13752,8 +10192,7 @@
 /p 【理法の幻想】
 /p 闇線中央捨て　光線その場
 /p 塔処理　北(A)基準で塔ペア散開
-/p 闇ディスミサル　ボスを見て　左:MTD3/STD2 右:H1D1/H2D4
-</t>
+/p 闇ディスミサル　ボスを見て　左:MTD3/STD2 右:H1D1/H2D4</t>
         </is>
       </c>
     </row>
@@ -13797,7 +10236,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■パラ1回目 タンク無敵
+          <t>/p ■パラ1回目 タンク無敵
 /p ーーーーーーーーーーーーーーーーーーーーーーーー
 /p ■パラ2回目 十字
 /p 線：対面に伸ばす
@@ -13810,8 +10249,7 @@
 /p 　　 　 ★　　　　　　　　　★　　　 　　 　 H1D3
 /p 　H1　　 　 H2 　 　H1/D3　H2/D4　 　　H2D4
 /p 　 　D3　D4
-/p ーーーーーーーーーーーーーーーーーーーーーーーー
-</t>
+/p ーーーーーーーーーーーーーーーーーーーーーーーー</t>
         </is>
       </c>
     </row>
@@ -13835,7 +10273,7 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 《ビーム誘導/4:4》　　　《塔/天火散開》
+          <t>/p 《ビーム誘導/4:4》　　　《塔/天火散開》
 /p 　　　　★ 　 　 　　 　 MT/D1 　 ST/D2
 /p 黒ビーム　 白ビーム 　 　　 　 　 ★
 /p 白デバフ　 黒デバフ　　　　　白　　黒
@@ -13847,8 +10285,7 @@
 /p 　北：十字 南：X字
 /p 　北　MT＞ST＞H1＞H2　南
 /p 　DPS塔踏み:中央＞D1D2D3D4
-/p ーーーーーーーーーーーーーーーーーーーーーーーー
-</t>
+/p ーーーーーーーーーーーーーーーーーーーーーーーー</t>
         </is>
       </c>
     </row>
@@ -13872,14 +10309,13 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■サイコロ　ネバラン
+          <t>/p ■サイコロ　ネバラン
 /p 　　 ★
 /p 　　　2/4（2,4は辺から頭割り）
 /p 5/7　 　 6/8
 /p 　　1/3
 /p ※ビーム:5,7→6,8→1,3→2,4
-/p ※サイコロ後北に集合
-</t>
+/p ※サイコロ後北に集合</t>
         </is>
       </c>
     </row>
@@ -13903,7 +10339,7 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【パラスの手】 T:西　他:東
+          <t>/p 【パラスの手】 T:西　他:東
 /p 【サモンダークネス】北＞西:TH　南＞東:DPS
 /p 【デミハルペリオン】
 /p 　 　 MT 　 　ST 　 　 　 MT 　 　 ST
@@ -13917,8 +10353,7 @@
 /p 〇α ★ ×α 　△α ★ □α　 2回目は〇×△□反転
 /p ●　　●　　●　　●　　 ※誘導後→★に入る
 /p 〇β ★ ×β　 △β ★ □β
-/p ●　　●　　●　　●
-</t>
+/p ●　　●　　●　　●</t>
         </is>
       </c>
     </row>
@@ -13942,7 +10377,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【カロリック1】※もちべ式
+          <t>/p 【カロリック1】※もちべ式
 /p 炎マーカー頭割り・・・西:TH　東:DPS
 /p 風炎:MTSTH1H2D1D2D3D4の順でAから時計
 /p 【エクピロシス】
@@ -13952,8 +10387,7 @@
 /p D3 D4
 /p 【パンゲネシス】MT:西無敵、他:南(東側)
 /p 極性なし:西←MTSTH1H2D1D2D3D4→東
-/p 無職:スライム 西：1マーカー、東：2マーカー
-</t>
+/p 無職:スライム 西：1マーカー、東：2マーカー</t>
         </is>
       </c>
     </row>
@@ -13977,7 +10411,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【カロリック2回目】
+          <t>/p 【カロリック2回目】
 /p 　　H2　　　　 マーカー:MTと交代
 /p D1　　　D4　 ※反時計/最後中央行かずに２回移動
 /p 　　MT
@@ -13987,8 +10421,7 @@
 /p 【サモンダークネス+デミ2】（MTD1が奥まで走る）
 /p 安置の逆側＞MT/D1　ST/D2　H1/D3　H2/D4＜安置
 /p 【サモンダークネス(線)】
-/p 　MT/D1　ST/D2　H1/D3　H2/D4ペアで処理
-</t>
+/p 　MT/D1　ST/D2　H1/D3　H2/D4ペアで処理</t>
         </is>
       </c>
     </row>
@@ -14012,7 +10445,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■基本散開　　　　■ペア十字(X字反時計回り)
+          <t>/p ■基本散開　　　　■ペア十字(X字反時計回り)
 /p D3 MT D4　　 　　　　 　MT/D3
 /p H1 ★ H2 　　 　 　H1/D1　★　H2/D4
 /p D1 ST D2　 　　　　 　　 ST/D2
@@ -14025,8 +10458,7 @@
 /p ■ビーストフェーズ
 /p 毒:12時から時計回り DPS＞TH　扇誘導:TH→D
 /p ■キメリック(サイコロ２回目)
-/p 1→東　2→西　3,4→北　無職→南
-</t>
+/p 1→東　2→西　3,4→北　無職→南</t>
         </is>
       </c>
     </row>
@@ -14050,7 +10482,7 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【ジングル固定】|【ナイトフィーバー】|【ウェーブオンウェーブ】
+          <t>/p 【ジングル固定】|【ナイトフィーバー】|【ウェーブオンウェーブ】
 /p 　　H1　　　　 |　　MT　 ST　　　　|　　MT　 ST
 /p MT　　遠D　　 | 　H1　　　　 H2　　 |　　D1　 D2
 /p ST　　 近D　　 | 　D3　 　　　D4　　|　　 H1 　H2
@@ -14062,8 +10494,7 @@
 /p 　ペア頭割り:横隣り　　　|
 /p 　　　　 ★　　　　　　　|　MTD3　　H2D4
 /p 　MT/ST　 D1/D2　　　|　　　　★
-/p 　H1/H2　 D3/D4　　　|　　H1D1　　 STD2
-</t>
+/p 　H1/H2　 D3/D4　　　|　　H1D1　　 STD2</t>
         </is>
       </c>
     </row>
@@ -14087,7 +10518,7 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■基本散開:ねばねば(北基準、Tボス下)■カラークラッシュ（2:2:2:2）
+          <t>/p ■基本散開:ねばねば(北基準、Tボス下)■カラークラッシュ（2:2:2:2）
 /p 　 D3 D4　 　 | 　 　 　　 ボス
 /p H1　☆　H2　| 　H1D3　MTD1　　STD2
 /p 　 D1 D2 　 　|　　　　　 H2D4　4:4は←MT組ST組→
@@ -14101,8 +10532,7 @@
 /p wave1：MTムー　ST＋近接ヤーン（リキャバーストで処理）　遠隔キャット　ヤーンの場所に遠隔ヒラ集合
 /p wave2：D側フェザーD3　B側フェザーH2　北から捨てる　MTムーを東→西フェザーへ誘導　他全員で範囲焼き
 /p wave3：ジャバ＋ムー行進(スタン：MT→D1→D2)　STヤーン北東待機　バインドヒラ南東
-/p wave4：MTムーC　STヤーンA(スタン：ST→D1→D2)　D側フェザーD3　B側フェザーD4　南から捨てる
-</t>
+/p wave4：MTムーC　STヤーンA(スタン：ST→D1→D2)　D側フェザーD3　B側フェザーD4　南から捨てる</t>
         </is>
       </c>
     </row>
@@ -14126,15 +10556,14 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【山川】火：内側MTH1D1D2　【雷雲】雷雲見て
+          <t>/p 【山川】火：内側MTH1D1D2　【雷雲】雷雲見て
 /p 　　　　　　 外側STH2D3D4　　TH←左　他　右→DPS
 /p 雷：基本散会
 /p 【マグマ】ーーーーーー【塔2回目】ーーーーーー
 /p D3D4　北　H1H2　 ◎4・2・2の場合：近接4人基準時計or反時計
 /p ※※※※※※※※※※ 　中央見て左←【D1MTSTD2】【H1H2】【D3D4】→右
 /p 　　 MT　　ST　　　　◎南８塔の場合：H1　H2　D3　D4
-/p 　　 D1　 　D2　　　　　　　　　　　 D1　 MT　 ST 　D2
-</t>
+/p 　　 D1　 　D2　　　　　　　　　　　 D1　 MT　 ST 　D2</t>
         </is>
       </c>
     </row>
@@ -14158,7 +10587,7 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【スキャッターシード一回目】
+          <t>/p 【スキャッターシード一回目】
 /p (種捨て)　　　　　　(エラプ)
 /p 　D3/MT　　 ST/D4 　近接:南内側開始→上→中央→下
 /p 　　　 　★　　　　 遠隔:D北H南開始→東西→最後中央寄せ
@@ -14172,8 +10601,7 @@
 /p (奇数)3回目安置 (13捨て位置)近D:④ TH:② 遠D:⑥
 /p ①　 　MT　　②　 　H1　　③　(ペア頭割り)
 /p 　 D1　 ST 　H2　　D3　　 MTD1:①　STD2:②
-/p ④　　 D2　　⑤　　 D4　　⑥　 H1D3:③　H2D4:⑤
-</t>
+/p ④　　 D2　　⑤　　 D4　　⑥　 H1D3:③　H2D4:⑤</t>
         </is>
       </c>
     </row>
@@ -14197,7 +10625,7 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【ゾーンデスマッチ・ウォール】
+          <t>/p 【ゾーンデスマッチ・ウォール】
 /p 　　　 MT/D3　　　　※石化視線：北西/南東避け
 /p 　　　　　　　　　　　 雑魚石化後処理
 /p H1/D1 ★　 H2/D2
@@ -14210,8 +10638,7 @@
 /p (一回目)　　　　　　 ｜ (二回目) ★
 /p MT/D3　 　 ST/D4 ｜　MT/D1　　 ST/D2
 /p 　　　 ★　　　　 ｜
-/p H1/D1　　 H2/D2 ｜ H1/D3　　 H2/D4
-</t>
+/p H1/D1　　 H2/D2 ｜ H1/D3　　 H2/D4</t>
         </is>
       </c>
     </row>
@@ -14255,7 +10682,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【土の魔技】　 |【風の魔技/千年の風化 IQ6000式】
+          <t>/p 【土の魔技】　 |【風の魔技/千年の風化 IQ6000式】
 /p 　 　MTD4　　| MT/D3　　H2/D4
 /p 　D3　　　H2 | 　　　　★　　　　 ※塔ズレ時計
 /p 　H1　　　D2 | H1/D1　 　ST /D2
@@ -14269,8 +10696,7 @@
 /p ②風化散開 ⇒ ズレ時計回り (頭割り)北
 /p 【幻狼招来】
 /p MT/D3　 (頭割り) 　H2/D4
-/p 　　　H1/D1　ST/D2
-</t>
+/p 　　　H1/D1　ST/D2</t>
         </is>
       </c>
     </row>
@@ -14294,7 +10720,7 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【クエイガ/1-3魔光】青マカ上から北島⇒その場⇒南島
+          <t>/p 【クエイガ/1-3魔光】青マカ上から北島⇒その場⇒南島
 /p MT　　　 　★　　　　ST
 /p D3　　　　　　　　　D4 【双牙撃】西島:MT 東島:ST
 /p 　D1　　　　　 　　D2　【風震の魔印(正規処理)】
@@ -14308,8 +10734,7 @@
 /p 　 T　島　　　 　Tニア　 :北東　Tファー:西　H:不動
 /p 　島　★　D　　 Dニア　:線が北伸び⇒北東 南伸び⇒南
 /p 　　　H　　　　 Dファー :線が北伸び⇒不動 南伸び⇒北東
-/p 【八連光弾】2:MT無敵 3:ST無敵 4:T二人フルバフ
-</t>
+/p 【八連光弾】2:MT無敵 3:ST無敵 4:T二人フルバフ</t>
         </is>
       </c>
     </row>
@@ -14333,7 +10758,7 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【基本散開】 【波乗り散開/4人割】
+          <t>/p 【基本散開】 【波乗り散開/4人割】
 /p 　D3MTD4 │　　 　　★
 /p 　H1 ★ H2 │　D3MT　 STD4
 /p 　D1 ST D2 │　H1D1　 D2H2
@@ -14362,8 +10787,7 @@
 /p 　　　　頭割り：H　T強：T
 /p 【青+赤アリウープ】
 /p マップ基準、基本散開方向の外周で時計回り
-/p 強攻撃：青タゲ持ちが離れる　頭割り：青直下から中央へ
-</t>
+/p 強攻撃：青タゲ持ちが離れる　頭割り：青直下から中央へ</t>
         </is>
       </c>
     </row>
@@ -14387,7 +10811,7 @@
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■基本散開　　■ミールストーム誘導
+          <t>/p ■基本散開　　■ミールストーム誘導
 /p 　D3 MT D4 　　 　D3MT
 /p 　H1 ☆ H2 　　　H1　　D4
 /p 　D1 ST D2　　　D1　　H2
@@ -14400,8 +10824,7 @@
 /p 1回目　H1:南西遠　　　　H2:北東タゲサ上
 /p 2回目　D3:南西中間　　　D4:南東タゲサ上
 /p 3回目　D1:南西タゲサ上　 D2:北東タゲサ上
-/p タンク線取り(隕石基準)　　MT:23マカ、ST:4マカ
-</t>
+/p タンク線取り(隕石基準)　　MT:23マカ、ST:4マカ</t>
         </is>
       </c>
     </row>
@@ -14425,7 +10848,7 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■チャンピオンズメテオ（ジジー式位置固定）
+          <t>/p ■チャンピオンズメテオ（ジジー式位置固定）
 /p ◯塔踏み1回目 ※範囲捨てボス下から割れ目沿い南北
 /p 　MTD3　H2D4
 /p 　H1D1　 ST D2
@@ -14439,8 +10862,7 @@
 /p 【フォーウェイ】X字ペア
 /p 〈内側誘導〉①北沼 ②無職近接 ③南沼 ④無職遠隔
 /p 【ツーウェイ】東西4:4
-/p 〈内側誘導〉西:反時計2人塔線無、東:時計2人塔線無
-</t>
+/p 〈内側誘導〉西:反時計2人塔線無、東:時計2人塔線無</t>
         </is>
       </c>
     </row>
@@ -14464,7 +10886,7 @@
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■リーサルスカージ　D側:MT組 B側:ST組
+          <t>/p ■リーサルスカージ　D側:MT組 B側:ST組
 /p H→近→遠→調整役　T/遠調整 (紫T)
 /p ■細胞付着：前期 左前タゲサ端で散開
 /p 〈頭割り:角〉扇外周
@@ -14478,8 +10900,7 @@
 /p ■細胞付着：後期　細胞中央向け
 /p 〈X字〉 DPS右上 TH左下
 /p 〈十字〉東西：DPS右上TH左下 南北：DPS左上TH右下
-/p 〈タン強〉無敵前捨て：D側MT　B側ST
-</t>
+/p 〈タン強〉無敵前捨て：D側MT　B側ST</t>
         </is>
       </c>
     </row>
@@ -14503,15 +10924,14 @@
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 〈散開〉T　　T
+          <t>/p 〈散開〉T　　T
 /p 　　★D1 HH D2 ★
 /p 　　　D3　　 D4
 /p ■細胞付着：終期　AoE左上から外周沿い捨て
 /p 線：中央集合→TH:西、D:東
 /p ■スローターシェッド　詠唱中集合：TH：A　DPS：タゲサ先
 /p 散会組：H1 MT | MT H1　D3 D1 | D1 D3
-/p 　 　　　H2 S T | S T H2　D4 D2 | D2 D4
-</t>
+/p 　 　　　H2 S T | S T H2　D4 D2 | D2 D4</t>
         </is>
       </c>
     </row>
@@ -14555,15 +10975,14 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"># 抜粋 (実際の本文は Lodestone を参照)
+          <t># 抜粋 (実際の本文は Lodestone を参照)
 /e -----
 /e [A] ●頭割り
 /e 入替ペア -&gt; [2]
 /e 頭割りは[3]
 /mk attack4 &lt;me&gt;
 /micon A fieldmarking
-# ... (続きは Lodestone URL を参照)
-</t>
+# ... (続きは Lodestone URL を参照)</t>
         </is>
       </c>
     </row>
@@ -14587,15 +11006,14 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"># 抜粋 (実際の本文は Lodestone を参照)
+          <t># 抜粋 (実際の本文は Lodestone を参照)
 /p -十字から-------------
 /p MT組：A→扇よけ→1→扇よけ
 /p ST組：D→扇よけ→4→扇よけ
 /p -X字から-------------
 /p MT組：1→扇よけ→A→扇よけ
 /p ST組：4→扇よけ→D→扇よけ
-# ... (続きは Lodestone URL を参照)
-</t>
+# ... (続きは Lodestone URL を参照)</t>
         </is>
       </c>
     </row>
@@ -14619,7 +11037,7 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 【ヴァンプストンプ】
+          <t>/p 【ヴァンプストンプ】
 /p 　D3　 MT 　 D4　近：コウモリ1後
 /p 　 　 D1 　D2
 /p 　H1　 ST　　H2
@@ -14633,8 +11051,7 @@
 /p 　 塔 塔 　 　　 塔 塔
 /p 　D ★ H　 　 　 ★
 /p 塔　 T　塔　 塔　全　塔
-/p 【バットデスマッチ】北西:MT組 南東:ST組
-</t>
+/p 【バットデスマッチ】北西:MT組 南東:ST組</t>
         </is>
       </c>
     </row>
@@ -14658,7 +11075,7 @@
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p 　【基本散開】 　 　｜【扇範囲誘導】(全てボス基準)
+          <t>/p 　【基本散開】 　 　｜【扇範囲誘導】(全てボス基準)
 /p 　D3 　MT 　D4 　 ｜ 　 　 　 MTD3
 /p 　H1　ボス　H2 　｜　H1D1 　ボス 　H2D4
 /p 　D1 　ST 　D2 　 ｜　 　 　 　STD2
@@ -14671,8 +11088,7 @@
 /p 　T 　 　D　 　H
 /p 【レイニングキャッツ】(タンク無敵)
 /p 　北西:MT→MT(無敵)→MT(無敵)→D1　南側タゲサ：H1D1D2
-/p 　北東:ST →ST(無敵) →ST(無敵) →D2 　 南側外周：H2D3D4
-</t>
+/p 　北東:ST →ST(無敵) →ST(無敵) →D2 　 南側外周：H2D3D4</t>
         </is>
       </c>
     </row>
@@ -14696,7 +11112,7 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■基本散開
+          <t>/p ■基本散開
 /p D3 MT D4　 　D3 D4 　 　MT/D3 　ST/D4
 /p H1 ☆ H2 　 　 MT ST 　 　 H1/D1 　 D2/H2
 /p D1 ST D2 　 　 D1 D2
@@ -14710,8 +11126,7 @@
 /p ■3rdライヴ
 /p デバフ捨て、塔踏みはペア割基準
 /p ■ブラックハート
-/p 8方向散開　HPが戻り次第、早いペア順に中央集合
-</t>
+/p 8方向散開　HPが戻り次第、早いペア順に中央集合</t>
         </is>
       </c>
     </row>
@@ -14735,7 +11150,7 @@
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■基本散開ーーーーーー■4ウェイーーーーーー
+          <t>/p ■基本散開ーーーーーー■4ウェイーーーーーー
 /p 　D3 MT D4 　 　 　 　MT/D3 　 　 H2/D4
 /p 　H1 ★ H2 　 　 　 　 　 　 　 　★
 /p 　D1 ST D2 　 　 　 　 H1/D1 　 　 ST/D2
@@ -14749,8 +11164,7 @@
 /p ■零式フューズボムー※単体の長ボムを北に見る
 /p 1回目短　 　北H1/D3 ┃H1/D3　MT/D1
 /p 　MT/D1 　 　 　 　 　┃ 　 　 　 　 　 ST/D2
-/p 　H2/D4 ST/D2 　 　 ┃ 2回目長 　 　 H2/D4
-</t>
+/p 　H2/D4 ST/D2 　 　 ┃ 2回目長 　 　 H2/D4</t>
         </is>
       </c>
     </row>
@@ -14774,7 +11188,7 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■フューズフィールドーーーーーーーーーーー
+          <t>/p ■フューズフィールドーーーーーーーーーーー
 /p 　Aから時計回りで探す 短→長
 /p 　MT→ST→H1→H2　D1→D2→D3→D4
 /p ■ボンバリアンスペシャルーーーーーーーーー
@@ -14783,8 +11197,7 @@
 /p ■極盛り式スピニングファイヤー(アタッチ)ーー
 /p 　D3　MT　D4
 /p 　D1 　★ 　D2
-/p 　H1　ST　 H2
-</t>
+/p 　H1　ST　 H2</t>
         </is>
       </c>
     </row>
@@ -14808,7 +11221,7 @@
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■縦散開ーーーー■円輪・輪円（DN式）ーーーーーー
+          <t>/p ■縦散開ーーーー■円輪・輪円（DN式）ーーーーーー
 /p D3 D4 　 　 　 　D3 MT D4
 /p MT ST 　 　 　 　D1 ☆ D2
 /p D1 D2 　 　 　 　H1 ST H2
@@ -14821,8 +11234,7 @@
 /p 基本散開 　 　 　|多 ■■■ 多 　 西：TH 東：DPS
 /p D3 MT D4 　 　|■ 　 ■ 　 ■ 　 22秒：3回 or 2回
 /p H1 ☆ H2 　 　 |少 　 ■ 　 少 　 42秒：2回 or 1回
-/p D1 ST D2 　 　 |■ ■ 他 ■ ■
-</t>
+/p D1 ST D2 　 　 |■ ■ 他 ■ ■</t>
         </is>
       </c>
     </row>
@@ -14846,7 +11258,7 @@
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ・ペア散開 　 　 　 　 　 　 ・散開(北基準)
+          <t>/p ・ペア散開 　 　 　 　 　 　 ・散開(北基準)
 /p TH多：B,D 　DPS多：中央 | 　 　 　D3
 /p TH少：A　 　DPS少：C 　 |　MT　 　 　H1
 /p 　 　 　 　 　 　 　 　 　 　|　☆D1　ST
@@ -14858,8 +11270,7 @@
 /p 青 　 　青 ※TH外側 　 　| 　 　 　 　☆
 /p 青 　 　青 ※DPS内側　 　| 　 H1/D1 　D2/H2
 /p 　誘電 　 　 　 　 　 　 ※時計→反時計で往復
-/p 　 紫
-</t>
+/p 　 紫</t>
         </is>
       </c>
     </row>
@@ -14883,7 +11294,7 @@
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/p ■ウィケッドブレイズ（エクサ）
+          <t>/p ■ウィケッドブレイズ（エクサ）
 /p 西 : MT組　東 : ST組
 /p ■マスタードボム
 /p D1 MT ST D2 　 　 　 　デバフ受取優先順位
@@ -14896,8 +11307,7 @@
 /p ■日出
 /p 　《塔》 　 　 　 　 　 《誘導》
 /p TH：南・西 　 　 　 　TH：11時から反時計
-/p DPS：北・東 　 　 　 DPS：12時から時計
-</t>
+/p DPS：北・東 　 　 　 DPS：12時から時計</t>
         </is>
       </c>
     </row>
@@ -15230,7 +11640,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">▼募集ジョブ
+          <t>▼募集ジョブ
 ● 活動DC: {{datacenter}}
 ● 言語: {{language}}
 ● ロール: {{recruitingRoles}}    # 注: 絶バハは H3構成 (ヒラ 3) が野良主流
@@ -15248,8 +11658,7 @@
 {{prohibitions}}
 ▼コンタクト
 Discord: {{discordHandle}}
-X: {{xHandle}}
-</t>
+X: {{xHandle}}</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -15266,7 +11675,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">▼募集ジョブ
+          <t>▼募集ジョブ
 ● 活動DC: {{datacenter}}
 ● 言語: {{language}}
 ● ロール: {{recruitingRoles}}    # 例: MT, ST, 近接, レンジ
@@ -15284,8 +11693,7 @@
 {{prohibitions}}
 ▼コンタクト
 Discord: {{discordHandle}}
-X: {{xHandle}}
-</t>
+X: {{xHandle}}</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -15302,7 +11710,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">▼募集ジョブ
+          <t>▼募集ジョブ
 ● 活動DC: {{datacenter}}
 ● 言語: {{language}}
 ● ロール: {{recruitingRoles}}
@@ -15320,8 +11728,7 @@
 {{prohibitions}}
 ▼コンタクト
 Discord: {{discordHandle}}
-X: {{xHandle}}
-</t>
+X: {{xHandle}}</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -15338,7 +11745,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: 結呪練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (ペア調整 / 氷火 MT・D3 交代式)
 ● 募集ロール: {{recruitingRoles}}
@@ -15346,8 +11753,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 辺獄1層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -15364,7 +11770,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: ハルマ練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (基本散開 / サイコロマーカー方式)
 ● 募集ロール: {{recruitingRoles}}
@@ -15372,8 +11778,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 辺獄2層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -15390,7 +11795,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: 闇の炎練 / 霊泉練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (基本犬丸 + 闇の炎X字 + 霊泉ハピおじ)
 ● 募集ロール: {{recruitingRoles}}
@@ -15398,8 +11803,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 辺獄3層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -15416,7 +11820,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: 前半 / 後半第二幕 / カーテンコール / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (前半 YPP / 後半 犬丸式)
 ● 募集ロール: {{recruitingRoles}}
@@ -15424,8 +11828,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 辺獄4層前後半
 ● 必須: {{requirements}}                # 例: 前半時間切れまで履修 / 後半動画予習
-● 備考: {{notes}}                       # 例: 後半ストップ可
-</t>
+● 備考: {{notes}}                       # 例: 後半ストップ可</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -15442,7 +11845,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">▼募集ジョブ
+          <t>▼募集ジョブ
 ● 活動DC: {{datacenter}}
 ● 言語: {{language}}
 ● ロール: {{recruitingRoles}}
@@ -15460,8 +11863,7 @@
 {{prohibitions}}
 ▼コンタクト
 Discord: {{discordHandle}}
-X: {{xHandle}}
-</t>
+X: {{xHandle}}</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -15478,7 +11880,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【絶竜詩戦争 攻略固定募集】
+          <t>【絶竜詩戦争 攻略固定募集】
 ● 活動DC: {{datacenter}}
 ● 募集ロール: {{recruitingRoles}}
 ● 進行度: {{progress}}    # 例: P1から / P5死刻練習中 / P7消化
@@ -15491,8 +11893,7 @@
 ● 複数ジョブ操作可能（ロール内）
 {{requirements}}
 【コンタクト】
-Discord: {{discordHandle}}
-</t>
+Discord: {{discordHandle}}</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -15509,7 +11910,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: 通し / 消化 / マウント周回
 ● 流派: {{strategy}}                    # 例: Game8 / ぬけまる式
 ● 募集ロール: {{recruitingRoles}}
@@ -15517,8 +11918,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 煉獄1層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}                       # 例: 周回、初見歓迎 等
-</t>
+● 備考: {{notes}}                       # 例: 周回、初見歓迎 等</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -15535,7 +11935,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: 通し / 消化 / 装備周回
 ● 流派: {{strategy}}                    # 例: Game8 / ぬけまる式
 ● 募集ロール: {{recruitingRoles}}
@@ -15543,8 +11943,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 煉獄2層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -15561,7 +11960,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: 通し / 消化 / 装備周回
 ● 流派: {{strategy}}                    # 例: Game8 / ぬけまる式 / 凶無敵
 ● 募集ロール: {{recruitingRoles}}
@@ -15569,8 +11968,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 煉獄3層 Ver1.5
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}                       # 例: 凶 無敵運用可
-</t>
+● 備考: {{notes}}                       # 例: 凶 無敵運用可</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -15587,7 +11985,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: 前半通し / 後半概念練 / 万象灰燼練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 / FFO式 / はいじあ式 / ビジョン式
 ● 募集ロール: {{recruitingRoles}}
@@ -15595,8 +11993,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 前半 + 後半 ビジョン式
 ● 必須: {{requirements}}                # 例: 概念タイムライン履修 / 万象灰燼動画予習
-● 備考: {{notes}}                       # 例: 万象前ストップ可、消化のみ
-</t>
+● 備考: {{notes}}                       # 例: 万象前ストップ可、消化のみ</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -15613,7 +12010,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">▼募集ジョブ
+          <t>▼募集ジョブ
 ● 活動DC: {{datacenter}}
 ● 言語: {{language}}
 ● ロール: {{recruitingRoles}}
@@ -15631,8 +12028,7 @@
 {{prohibitions}}
 ▼コンタクト
 Discord: {{discordHandle}}
-X: {{xHandle}}
-</t>
+X: {{xHandle}}</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -15649,7 +12045,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 通し練 / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (犬丸改FFO式) / ぬけまる震撃
 ● 募集ロール: {{recruitingRoles}}
@@ -15657,8 +12053,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 天獄編2層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}                       # 例: 震撃ぬけまる希望
-</t>
+● 備考: {{notes}}                       # 例: 震撃ぬけまる希望</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -15675,7 +12070,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 通し練 / 調停練 / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (ハムカツ+ジジー式) / しのしょー式
 ● 募集ロール: {{recruitingRoles}}
@@ -15683,8 +12078,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 天獄編3層
 ● 必須: {{requirements}}                # 例: タイムライン履修 / 動画予習
-● 備考: {{notes}}                       # 例: アップヘルド闇は十字
-</t>
+● 備考: {{notes}}                       # 例: アップヘルド闇は十字</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -15701,7 +12095,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: 前半通し / 後半パラスレイ練 / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (ぬけまる式 / パラスレイX処理)
 ● パラスレイ: {{parashasureProc}}       # X処理 / K処理 (1回目バリアント)
@@ -15710,8 +12104,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 天獄編4層 前半+後半
 ● 必須: {{requirements}}                # 例: タイムライン履修 / カロリック動画予習
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -15728,7 +12121,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 通し練 / 消化
 ● 流派: {{strategy}}                    # 例: Game8 / 無職マラソン式
 ● 募集ロール: {{recruitingRoles}}
@@ -15736,8 +12129,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 天獄編1層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -15754,7 +12146,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 通し練 / 消化
 ● 流派: {{strategy}}                    # 例: Game8 / ぬけまる式
 ● 募集ロール: {{recruitingRoles}}
@@ -15762,8 +12154,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 クルーザー級1層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -15780,7 +12171,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 雑魚練 / 山川練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (新FFO式 Ver.3.1)
 ● 募集ロール: {{recruitingRoles}}
@@ -15788,8 +12179,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 クルーザー級2層
 ● 必須: {{requirements}}                # 例: タイムライン履修 / 雑魚動画予習
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -15806,7 +12196,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: ビルディング練 / P3 ツイン練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (さり式 / ぽにこね式)
 ● 募集ロール: {{recruitingRoles}}
@@ -15814,8 +12204,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 クルーザー級3層
 ● 必須: {{requirements}}                # 例: タイムライン履修 / さり式動画予習
-● 備考: {{notes}}                       # 例: スプリント運用要習熟
-</t>
+● 備考: {{notes}}                       # 例: スプリント運用要習熟</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -15832,7 +12221,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 群狼剣練 / P2 孤狼の呪い練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (ぬけまる/IQ6000/Alice/81128)
 ● 募集ロール: {{recruitingRoles}}
@@ -15840,8 +12229,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 クルーザー級4層 (前半+後半)
 ● 必須: {{requirements}}                # 例: 千年の風化動画予習 / Alice式動画予習
-● 備考: {{notes}}                       # 例: 八連光弾の T 無敵順厳守
-</t>
+● 備考: {{notes}}                       # 例: 八連光弾の T 無敵順厳守</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -15858,7 +12246,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P2 練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (犬丸水牢ヒラ/炎AC)
 ● 募集ロール: {{recruitingRoles}}
@@ -15866,8 +12254,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 ヘビー級2層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -15884,7 +12271,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 / チャンピオンズメテオ練 / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (ぬけまる様式 / ジジ式 / DXA式)
 ● 募集ロール: {{recruitingRoles}}
@@ -15892,8 +12279,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 ヘビー級3層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -15910,7 +12296,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 練 / P2 ドリーム練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (位置固定/牛子式/ワンエース式)
 ● 募集ロール: {{recruitingRoles}}
@@ -15918,8 +12304,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 前半 + ぬけまる動画後半
 ● 必須: {{requirements}}                # 例: P1 ペアタイムライン履修 / ドリーム動画予習
-● 備考: {{notes}}                       # 例: ドリーム前ストップ可
-</t>
+● 備考: {{notes}}                       # 例: ドリーム前ストップ可</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -15936,7 +12321,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 通し練 / 消化
 ● 流派: {{strategy}}                    # 例: Game8 / ぬけまる式
 ● 募集ロール: {{recruitingRoles}}
@@ -15944,8 +12329,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 ヘビー級1層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -15962,7 +12346,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 通し練 / 消化
 ● 流派: {{strategy}}                    # 例: Game8 / 犬丸式
 ● 募集ロール: {{recruitingRoles}}
@@ -15970,8 +12354,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 ライトヘビー1層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -15988,7 +12371,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 / 2nd ライヴ練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (ぬけまる版)
 ● 募集ロール: {{recruitingRoles}}
@@ -15996,8 +12379,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 ライトヘビー2層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -16014,7 +12396,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 / 零式フューズ練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (ぬけまる版 Ver.2.0)
 ● 募集ロール: {{recruitingRoles}}
@@ -16022,8 +12404,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 ライトヘビー3層
 ● 必須: {{requirements}}                # 例: タイムライン履修
-● 備考: {{notes}}
-</t>
+● 備考: {{notes}}</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -16040,7 +12421,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">【FF14 零式募集】{{contentShort}}
+          <t>【FF14 零式募集】{{contentShort}}
 ● 進行度: {{progress}}                  # 例: P1 / 後半クロステイル練 / 通し / 消化
 ● 流派: {{strategy}}                    # 例: Game8 (ぬけまる版 + DN 式)
 ● 募集ロール: {{recruitingRoles}}
@@ -16048,8 +12429,7 @@
 ● VC: {{voiceChannel}}                  # 例: Discord 聞き専可
 ● マクロ: {{macroSource}}               # 例: Game8 前半 (Ver2.1) + 後半
 ● 必須: {{requirements}}                # 例: タイムライン履修 / 動画予習
-● 備考: {{notes}}                       # 例: 後半ストップ可
-</t>
+● 備考: {{notes}}                       # 例: 後半ストップ可</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
